--- a/source-excel/DATAPLANT.xlsx
+++ b/source-excel/DATAPLANT.xlsx
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI\รายงานการจัดระดับ\ข้อมูลทำ AI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI\รายงานการจัดระดับ\ข้อมูลทำ AI\newstarrating\source-excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{720F7EC5-1DA2-40E4-A6EC-05554319622E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F2500BB-6457-4941-BA42-D0463978BCEC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{22141E00-01BD-4411-8006-614C22989334}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="8130" xr2:uid="{22141E00-01BD-4411-8006-614C22989334}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$285</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$286</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2279" uniqueCount="791">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2287" uniqueCount="794">
   <si>
     <t>กิจการ</t>
   </si>
@@ -444,9 +444,6 @@
     <t>FC214</t>
   </si>
   <si>
-    <t>สระกระโจม</t>
-  </si>
-  <si>
     <t>FC248</t>
   </si>
   <si>
@@ -454,9 +451,6 @@
   </si>
   <si>
     <t>FC299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">เนินพระปรางค์ </t>
   </si>
   <si>
     <t>บจก.กอวัฒนาคอนกรีต</t>
@@ -2402,6 +2396,21 @@
   </si>
   <si>
     <t>กําธร ชูจักร์</t>
+  </si>
+  <si>
+    <t>FC018</t>
+  </si>
+  <si>
+    <t>บึงกาฬ</t>
+  </si>
+  <si>
+    <t>หจก.เซ็นจูรี่บึงกาฬ</t>
+  </si>
+  <si>
+    <t>ดอนเจดีย์</t>
+  </si>
+  <si>
+    <t>สองพี่น้อง 2</t>
   </si>
 </sst>
 </file>
@@ -2882,7 +2891,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5D3108B-0AC7-45F6-8395-B543209D3234}">
-  <dimension ref="A1:H285"/>
+  <dimension ref="A1:H286"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.6328125" style="17" customWidth="1"/>
@@ -2906,7 +2915,7 @@
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
@@ -2915,10 +2924,10 @@
         <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -2926,7 +2935,7 @@
         <v>7</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>5</v>
@@ -2941,10 +2950,10 @@
         <v>9</v>
       </c>
       <c r="G2" s="18" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="H2" s="18" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -2967,10 +2976,10 @@
         <v>13</v>
       </c>
       <c r="G3" s="18" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="H3" s="18" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -2978,7 +2987,7 @@
         <v>15</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>5</v>
@@ -2993,10 +3002,10 @@
         <v>16</v>
       </c>
       <c r="G4" s="18" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="H4" s="18" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3019,10 +3028,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="18" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="H5" s="18" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3045,10 +3054,10 @@
         <v>13</v>
       </c>
       <c r="G6" s="18" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="H6" s="18" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3071,10 +3080,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="18" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="H7" s="18" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3097,10 +3106,10 @@
         <v>13</v>
       </c>
       <c r="G8" s="18" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="H8" s="18" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3123,10 +3132,10 @@
         <v>13</v>
       </c>
       <c r="G9" s="18" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="H9" s="18" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3149,10 +3158,10 @@
         <v>16</v>
       </c>
       <c r="G10" s="18" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="H10" s="18" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3175,10 +3184,10 @@
         <v>9</v>
       </c>
       <c r="G11" s="18" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="H11" s="18" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3201,10 +3210,10 @@
         <v>9</v>
       </c>
       <c r="G12" s="18" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="H12" s="18" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3227,10 +3236,10 @@
         <v>9</v>
       </c>
       <c r="G13" s="18" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="H13" s="18" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3253,10 +3262,10 @@
         <v>9</v>
       </c>
       <c r="G14" s="18" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="H14" s="18" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3279,10 +3288,10 @@
         <v>9</v>
       </c>
       <c r="G15" s="18" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="H15" s="18" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3305,10 +3314,10 @@
         <v>9</v>
       </c>
       <c r="G16" s="18" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="H16" s="18" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3331,10 +3340,10 @@
         <v>9</v>
       </c>
       <c r="G17" s="18" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="H17" s="18" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3357,10 +3366,10 @@
         <v>13</v>
       </c>
       <c r="G18" s="18" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="H18" s="18" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3383,10 +3392,10 @@
         <v>13</v>
       </c>
       <c r="G19" s="18" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="H19" s="18" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3409,10 +3418,10 @@
         <v>13</v>
       </c>
       <c r="G20" s="18" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="H20" s="18" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3435,10 +3444,10 @@
         <v>13</v>
       </c>
       <c r="G21" s="18" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="H21" s="18" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3461,10 +3470,10 @@
         <v>13</v>
       </c>
       <c r="G22" s="18" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="H22" s="18" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3487,10 +3496,10 @@
         <v>13</v>
       </c>
       <c r="G23" s="18" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="H23" s="18" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3513,10 +3522,10 @@
         <v>13</v>
       </c>
       <c r="G24" s="18" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="H24" s="18" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3539,10 +3548,10 @@
         <v>13</v>
       </c>
       <c r="G25" s="18" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="H25" s="18" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3565,10 +3574,10 @@
         <v>13</v>
       </c>
       <c r="G26" s="18" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="H26" s="18" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3591,10 +3600,10 @@
         <v>13</v>
       </c>
       <c r="G27" s="18" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="H27" s="18" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3617,10 +3626,10 @@
         <v>13</v>
       </c>
       <c r="G28" s="18" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="H28" s="18" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3643,10 +3652,10 @@
         <v>9</v>
       </c>
       <c r="G29" s="18" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="H29" s="18" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3669,10 +3678,10 @@
         <v>9</v>
       </c>
       <c r="G30" s="18" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="H30" s="18" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3695,10 +3704,10 @@
         <v>13</v>
       </c>
       <c r="G31" s="18" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="H31" s="18" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3721,10 +3730,10 @@
         <v>13</v>
       </c>
       <c r="G32" s="18" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="H32" s="18" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3747,10 +3756,10 @@
         <v>13</v>
       </c>
       <c r="G33" s="18" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="H33" s="18" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3773,10 +3782,10 @@
         <v>13</v>
       </c>
       <c r="G34" s="18" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="H34" s="18" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3799,10 +3808,10 @@
         <v>93</v>
       </c>
       <c r="G35" s="18" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="H35" s="18" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3825,10 +3834,10 @@
         <v>93</v>
       </c>
       <c r="G36" s="18" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="H36" s="18" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3851,10 +3860,10 @@
         <v>9</v>
       </c>
       <c r="G37" s="18" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="H37" s="18" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3862,7 +3871,7 @@
         <v>102</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="C38" s="7" t="s">
         <v>21</v>
@@ -3877,10 +3886,10 @@
         <v>9</v>
       </c>
       <c r="G38" s="18" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="H38" s="18" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3888,7 +3897,7 @@
         <v>103</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="C39" s="7" t="s">
         <v>21</v>
@@ -3903,10 +3912,10 @@
         <v>9</v>
       </c>
       <c r="G39" s="18" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="H39" s="18" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3929,10 +3938,10 @@
         <v>13</v>
       </c>
       <c r="G40" s="18" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="H40" s="18" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3940,7 +3949,7 @@
         <v>108</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="C41" s="7" t="s">
         <v>21</v>
@@ -3955,10 +3964,10 @@
         <v>93</v>
       </c>
       <c r="G41" s="18" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="H41" s="18" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3966,7 +3975,7 @@
         <v>110</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="C42" s="7" t="s">
         <v>21</v>
@@ -3981,10 +3990,10 @@
         <v>16</v>
       </c>
       <c r="G42" s="18" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="H42" s="18" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3992,7 +4001,7 @@
         <v>112</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="C43" s="7" t="s">
         <v>21</v>
@@ -4007,10 +4016,10 @@
         <v>16</v>
       </c>
       <c r="G43" s="18" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="H43" s="18" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -4033,10 +4042,10 @@
         <v>93</v>
       </c>
       <c r="G44" s="18" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="H44" s="18" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -4059,10 +4068,10 @@
         <v>9</v>
       </c>
       <c r="G45" s="18" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="H45" s="18" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -4085,10 +4094,10 @@
         <v>9</v>
       </c>
       <c r="G46" s="18" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="H46" s="18" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -4111,10 +4120,10 @@
         <v>13</v>
       </c>
       <c r="G47" s="18" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="H47" s="18" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -4137,10 +4146,10 @@
         <v>93</v>
       </c>
       <c r="G48" s="18" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="H48" s="18" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -4163,10 +4172,10 @@
         <v>93</v>
       </c>
       <c r="G49" s="18" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="H49" s="18" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -4189,10 +4198,10 @@
         <v>93</v>
       </c>
       <c r="G50" s="18" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="H50" s="18" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -4215,10 +4224,10 @@
         <v>9</v>
       </c>
       <c r="G51" s="18" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="H51" s="18" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -4241,10 +4250,10 @@
         <v>9</v>
       </c>
       <c r="G52" s="18" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="H52" s="18" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -4252,7 +4261,7 @@
         <v>137</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>138</v>
+        <v>792</v>
       </c>
       <c r="C53" s="7" t="s">
         <v>119</v>
@@ -4267,18 +4276,18 @@
         <v>9</v>
       </c>
       <c r="G53" s="18" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="H53" s="18" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A54" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="B54" s="6" t="s">
         <v>139</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>140</v>
       </c>
       <c r="C54" s="7" t="s">
         <v>119</v>
@@ -4293,18 +4302,18 @@
         <v>9</v>
       </c>
       <c r="G54" s="18" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="H54" s="18" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A55" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>142</v>
+        <v>793</v>
       </c>
       <c r="C55" s="7" t="s">
         <v>119</v>
@@ -4319,24 +4328,24 @@
         <v>9</v>
       </c>
       <c r="G55" s="18" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="H55" s="18" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A56" s="5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C56" s="7" t="s">
         <v>119</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E56" s="7" t="s">
         <v>20</v>
@@ -4345,24 +4354,24 @@
         <v>93</v>
       </c>
       <c r="G56" s="18" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="H56" s="18" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A57" s="5" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="C57" s="7" t="s">
         <v>119</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E57" s="7" t="s">
         <v>20</v>
@@ -4371,24 +4380,24 @@
         <v>93</v>
       </c>
       <c r="G57" s="18" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="H57" s="18" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A58" s="5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C58" s="7" t="s">
         <v>119</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E58" s="7" t="s">
         <v>20</v>
@@ -4397,24 +4406,24 @@
         <v>93</v>
       </c>
       <c r="G58" s="18" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="H58" s="18" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A59" s="5" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C59" s="7" t="s">
         <v>119</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E59" s="7" t="s">
         <v>20</v>
@@ -4423,24 +4432,24 @@
         <v>93</v>
       </c>
       <c r="G59" s="18" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="H59" s="18" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A60" s="5" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C60" s="7" t="s">
         <v>119</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E60" s="7" t="s">
         <v>20</v>
@@ -4449,24 +4458,24 @@
         <v>16</v>
       </c>
       <c r="G60" s="18" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="H60" s="18" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A61" s="5" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C61" s="7" t="s">
         <v>119</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E61" s="7" t="s">
         <v>20</v>
@@ -4475,24 +4484,24 @@
         <v>93</v>
       </c>
       <c r="G61" s="18" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="H61" s="18" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A62" s="5" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C62" s="7" t="s">
         <v>119</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E62" s="7" t="s">
         <v>20</v>
@@ -4501,24 +4510,24 @@
         <v>13</v>
       </c>
       <c r="G62" s="18" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="H62" s="18" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A63" s="5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C63" s="7" t="s">
         <v>119</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E63" s="7" t="s">
         <v>20</v>
@@ -4527,24 +4536,24 @@
         <v>93</v>
       </c>
       <c r="G63" s="18" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="H63" s="18" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A64" s="5" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C64" s="7" t="s">
         <v>119</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E64" s="7" t="s">
         <v>20</v>
@@ -4553,24 +4562,24 @@
         <v>9</v>
       </c>
       <c r="G64" s="18" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="H64" s="18" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A65" s="5" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C65" s="7" t="s">
         <v>119</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E65" s="7" t="s">
         <v>20</v>
@@ -4579,24 +4588,24 @@
         <v>93</v>
       </c>
       <c r="G65" s="18" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="H65" s="18" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A66" s="5" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E66" s="7" t="s">
         <v>20</v>
@@ -4605,24 +4614,24 @@
         <v>13</v>
       </c>
       <c r="G66" s="18" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="H66" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A67" s="5" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E67" s="7" t="s">
         <v>20</v>
@@ -4631,24 +4640,24 @@
         <v>13</v>
       </c>
       <c r="G67" s="18" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="H67" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A68" s="5" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E68" s="7" t="s">
         <v>20</v>
@@ -4657,24 +4666,24 @@
         <v>13</v>
       </c>
       <c r="G68" s="18" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="H68" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A69" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E69" s="7" t="s">
         <v>20</v>
@@ -4683,24 +4692,24 @@
         <v>13</v>
       </c>
       <c r="G69" s="18" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="H69" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A70" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E70" s="7" t="s">
         <v>20</v>
@@ -4709,24 +4718,24 @@
         <v>16</v>
       </c>
       <c r="G70" s="18" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="H70" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A71" s="5" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E71" s="7" t="s">
         <v>20</v>
@@ -4735,24 +4744,24 @@
         <v>93</v>
       </c>
       <c r="G71" s="18" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="H71" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="72" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A72" s="5" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E72" s="7" t="s">
         <v>20</v>
@@ -4761,24 +4770,24 @@
         <v>93</v>
       </c>
       <c r="G72" s="18" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="H72" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A73" s="5" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E73" s="7" t="s">
         <v>20</v>
@@ -4787,24 +4796,24 @@
         <v>93</v>
       </c>
       <c r="G73" s="18" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="H73" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A74" s="5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E74" s="7" t="s">
         <v>20</v>
@@ -4813,24 +4822,24 @@
         <v>9</v>
       </c>
       <c r="G74" s="18" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="H74" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A75" s="5" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E75" s="7" t="s">
         <v>20</v>
@@ -4839,24 +4848,24 @@
         <v>9</v>
       </c>
       <c r="G75" s="18" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="H75" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A76" s="5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E76" s="7" t="s">
         <v>20</v>
@@ -4865,24 +4874,24 @@
         <v>9</v>
       </c>
       <c r="G76" s="18" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="H76" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A77" s="5" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E77" s="7" t="s">
         <v>20</v>
@@ -4891,24 +4900,24 @@
         <v>9</v>
       </c>
       <c r="G77" s="18" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="H77" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="78" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A78" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E78" s="7" t="s">
         <v>20</v>
@@ -4917,24 +4926,24 @@
         <v>9</v>
       </c>
       <c r="G78" s="18" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="H78" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="79" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A79" s="5" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E79" s="7" t="s">
         <v>20</v>
@@ -4943,24 +4952,24 @@
         <v>9</v>
       </c>
       <c r="G79" s="18" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="H79" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="80" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A80" s="5" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E80" s="7" t="s">
         <v>20</v>
@@ -4969,24 +4978,24 @@
         <v>9</v>
       </c>
       <c r="G80" s="18" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="H80" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="81" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A81" s="5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E81" s="7" t="s">
         <v>20</v>
@@ -4995,24 +5004,24 @@
         <v>13</v>
       </c>
       <c r="G81" s="18" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="H81" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="82" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A82" s="5" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E82" s="7" t="s">
         <v>20</v>
@@ -5021,24 +5030,24 @@
         <v>13</v>
       </c>
       <c r="G82" s="18" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="H82" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="83" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A83" s="5" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E83" s="7" t="s">
         <v>20</v>
@@ -5047,24 +5056,24 @@
         <v>13</v>
       </c>
       <c r="G83" s="18" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="H83" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="84" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A84" s="9" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B84" s="10" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E84" s="11" t="s">
         <v>20</v>
@@ -5073,24 +5082,24 @@
         <v>9</v>
       </c>
       <c r="G84" s="18" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="H84" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="85" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A85" s="5" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E85" s="7" t="s">
         <v>20</v>
@@ -5099,24 +5108,24 @@
         <v>93</v>
       </c>
       <c r="G85" s="18" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="H85" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="86" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A86" s="5" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E86" s="7" t="s">
         <v>20</v>
@@ -5125,24 +5134,24 @@
         <v>93</v>
       </c>
       <c r="G86" s="18" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="H86" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="87" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A87" s="5" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E87" s="7" t="s">
         <v>20</v>
@@ -5151,24 +5160,24 @@
         <v>9</v>
       </c>
       <c r="G87" s="18" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="H87" s="18" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="88" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A88" s="5" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E88" s="7" t="s">
         <v>20</v>
@@ -5177,24 +5186,24 @@
         <v>9</v>
       </c>
       <c r="G88" s="18" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="H88" s="18" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="89" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A89" s="9" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B89" s="10" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E89" s="11" t="s">
         <v>20</v>
@@ -5203,24 +5212,24 @@
         <v>93</v>
       </c>
       <c r="G89" s="18" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="H89" s="18" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="90" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A90" s="5" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E90" s="7" t="s">
         <v>20</v>
@@ -5229,24 +5238,24 @@
         <v>9</v>
       </c>
       <c r="G90" s="18" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="H90" s="18" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="91" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A91" s="5" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E91" s="7" t="s">
         <v>20</v>
@@ -5255,24 +5264,24 @@
         <v>16</v>
       </c>
       <c r="G91" s="18" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="H91" s="18" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="92" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A92" s="5" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D92" s="12" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E92" s="7" t="s">
         <v>20</v>
@@ -5281,24 +5290,24 @@
         <v>9</v>
       </c>
       <c r="G92" s="18" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="H92" s="18" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="93" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A93" s="5" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D93" s="12" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E93" s="7" t="s">
         <v>20</v>
@@ -5307,24 +5316,24 @@
         <v>9</v>
       </c>
       <c r="G93" s="18" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="H93" s="18" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="94" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A94" s="5" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E94" s="7" t="s">
         <v>20</v>
@@ -5333,24 +5342,24 @@
         <v>9</v>
       </c>
       <c r="G94" s="18" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="H94" s="18" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="95" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A95" s="5" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E95" s="7" t="s">
         <v>20</v>
@@ -5359,24 +5368,24 @@
         <v>9</v>
       </c>
       <c r="G95" s="18" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="H95" s="18" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="96" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A96" s="5" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E96" s="7" t="s">
         <v>20</v>
@@ -5385,24 +5394,24 @@
         <v>9</v>
       </c>
       <c r="G96" s="18" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="H96" s="18" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="97" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A97" s="5" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E97" s="7" t="s">
         <v>20</v>
@@ -5411,24 +5420,24 @@
         <v>9</v>
       </c>
       <c r="G97" s="18" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="H97" s="18" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="98" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A98" s="5" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E98" s="7" t="s">
         <v>20</v>
@@ -5437,24 +5446,24 @@
         <v>9</v>
       </c>
       <c r="G98" s="18" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="H98" s="18" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="99" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A99" s="5" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E99" s="7" t="s">
         <v>20</v>
@@ -5463,24 +5472,24 @@
         <v>93</v>
       </c>
       <c r="G99" s="18" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="H99" s="18" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="100" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A100" s="5" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E100" s="7" t="s">
         <v>20</v>
@@ -5489,24 +5498,24 @@
         <v>93</v>
       </c>
       <c r="G100" s="18" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="H100" s="18" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="101" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A101" s="5" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D101" s="5" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E101" s="7" t="s">
         <v>20</v>
@@ -5515,24 +5524,24 @@
         <v>9</v>
       </c>
       <c r="G101" s="18" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="H101" s="18" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="102" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A102" s="5" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C102" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D102" s="5" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E102" s="7" t="s">
         <v>20</v>
@@ -5541,24 +5550,24 @@
         <v>9</v>
       </c>
       <c r="G102" s="18" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="H102" s="18" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="103" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A103" s="5" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D103" s="12" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E103" s="7" t="s">
         <v>20</v>
@@ -5567,24 +5576,24 @@
         <v>13</v>
       </c>
       <c r="G103" s="18" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="H103" s="18" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="104" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A104" s="5" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D104" s="12" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E104" s="7" t="s">
         <v>20</v>
@@ -5593,24 +5602,24 @@
         <v>13</v>
       </c>
       <c r="G104" s="18" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="H104" s="18" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="105" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A105" s="5" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C105" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D105" s="12" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E105" s="7" t="s">
         <v>20</v>
@@ -5619,24 +5628,24 @@
         <v>13</v>
       </c>
       <c r="G105" s="18" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="H105" s="18" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="106" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A106" s="5" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D106" s="12" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E106" s="7" t="s">
         <v>20</v>
@@ -5645,24 +5654,24 @@
         <v>13</v>
       </c>
       <c r="G106" s="18" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="H106" s="18" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="107" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A107" s="5" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C107" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D107" s="5" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E107" s="7" t="s">
         <v>20</v>
@@ -5671,24 +5680,24 @@
         <v>9</v>
       </c>
       <c r="G107" s="18" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="H107" s="18" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="108" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A108" s="5" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C108" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D108" s="5" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E108" s="7" t="s">
         <v>20</v>
@@ -5697,24 +5706,24 @@
         <v>9</v>
       </c>
       <c r="G108" s="18" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="H108" s="18" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="109" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A109" s="5" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C109" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D109" s="5" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E109" s="7" t="s">
         <v>20</v>
@@ -5723,24 +5732,24 @@
         <v>9</v>
       </c>
       <c r="G109" s="18" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="H109" s="18" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="110" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A110" s="5" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C110" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D110" s="5" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E110" s="7" t="s">
         <v>20</v>
@@ -5749,24 +5758,24 @@
         <v>9</v>
       </c>
       <c r="G110" s="18" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="H110" s="18" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="111" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A111" s="5" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C111" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D111" s="5" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="E111" s="7" t="s">
         <v>20</v>
@@ -5775,24 +5784,24 @@
         <v>9</v>
       </c>
       <c r="G111" s="18" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="H111" s="18" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="112" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A112" s="5" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C112" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D112" s="5" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E112" s="7" t="s">
         <v>20</v>
@@ -5801,24 +5810,24 @@
         <v>13</v>
       </c>
       <c r="G112" s="18" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="H112" s="18" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="113" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A113" s="5" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C113" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E113" s="7" t="s">
         <v>20</v>
@@ -5827,24 +5836,24 @@
         <v>13</v>
       </c>
       <c r="G113" s="18" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="H113" s="18" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="114" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A114" s="5" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C114" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D114" s="5" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E114" s="7" t="s">
         <v>20</v>
@@ -5853,24 +5862,24 @@
         <v>13</v>
       </c>
       <c r="G114" s="18" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="H114" s="18" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="115" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A115" s="5" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C115" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E115" s="7" t="s">
         <v>20</v>
@@ -5879,24 +5888,24 @@
         <v>13</v>
       </c>
       <c r="G115" s="18" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="H115" s="18" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="116" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A116" s="5" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C116" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D116" s="5" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E116" s="7" t="s">
         <v>20</v>
@@ -5905,24 +5914,24 @@
         <v>13</v>
       </c>
       <c r="G116" s="18" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="H116" s="18" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="117" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A117" s="5" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C117" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D117" s="5" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="E117" s="7" t="s">
         <v>20</v>
@@ -5931,50 +5940,50 @@
         <v>9</v>
       </c>
       <c r="G117" s="18" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="H117" s="18" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="118" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A118" s="5" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C118" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D118" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="E118" s="7" t="s">
         <v>300</v>
-      </c>
-      <c r="E118" s="7" t="s">
-        <v>302</v>
       </c>
       <c r="F118" s="7" t="s">
         <v>16</v>
       </c>
       <c r="G118" s="18" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="H118" s="18" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="119" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A119" s="5" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C119" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="E119" s="7" t="s">
         <v>20</v>
@@ -5983,24 +5992,24 @@
         <v>13</v>
       </c>
       <c r="G119" s="18" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="H119" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="120" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A120" s="5" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C120" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D120" s="5" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E120" s="7" t="s">
         <v>20</v>
@@ -6009,102 +6018,102 @@
         <v>9</v>
       </c>
       <c r="G120" s="18" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="H120" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="121" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A121" s="5" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="C121" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="E121" s="7" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F121" s="7" t="s">
         <v>93</v>
       </c>
       <c r="G121" s="18" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="H121" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="122" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A122" s="5" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="C122" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D122" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E122" s="7" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F122" s="7" t="s">
         <v>9</v>
       </c>
       <c r="G122" s="18" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="H122" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="123" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A123" s="5" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="C123" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E123" s="7" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F123" s="7" t="s">
         <v>16</v>
       </c>
       <c r="G123" s="18" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="H123" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="124" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A124" s="5" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="C124" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D124" s="5" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E124" s="7" t="s">
         <v>20</v>
@@ -6113,232 +6122,232 @@
         <v>16</v>
       </c>
       <c r="G124" s="18" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="H124" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="125" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A125" s="5" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="C125" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E125" s="7" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F125" s="7" t="s">
         <v>9</v>
       </c>
       <c r="G125" s="18" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="H125" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="126" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A126" s="5" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="C126" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E126" s="7" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F126" s="7" t="s">
         <v>9</v>
       </c>
       <c r="G126" s="18" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="H126" s="18" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="127" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A127" s="5" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B127" s="6" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="C127" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E127" s="7" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F127" s="7" t="s">
         <v>16</v>
       </c>
       <c r="G127" s="18" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="H127" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="128" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A128" s="5" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="C128" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D128" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="E128" s="7" t="s">
         <v>322</v>
-      </c>
-      <c r="E128" s="7" t="s">
-        <v>324</v>
       </c>
       <c r="F128" s="7" t="s">
         <v>16</v>
       </c>
       <c r="G128" s="18" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="H128" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="129" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A129" s="5" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="C129" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E129" s="7" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F129" s="7" t="s">
         <v>16</v>
       </c>
       <c r="G129" s="18" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="H129" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="130" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A130" s="5" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="C130" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E130" s="7" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F130" s="7" t="s">
         <v>13</v>
       </c>
       <c r="G130" s="18" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="H130" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="131" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A131" s="5" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="C131" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E131" s="7" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="F131" s="7" t="s">
         <v>16</v>
       </c>
       <c r="G131" s="18" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="H131" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="132" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A132" s="5" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="C132" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D132" s="5" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E132" s="7" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="F132" s="7" t="s">
         <v>16</v>
       </c>
       <c r="G132" s="18" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="H132" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="133" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A133" s="5" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C133" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D133" s="5" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E133" s="7" t="s">
         <v>20</v>
@@ -6347,24 +6356,24 @@
         <v>16</v>
       </c>
       <c r="G133" s="18" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="H133" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="134" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A134" s="5" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C134" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E134" s="7" t="s">
         <v>20</v>
@@ -6373,76 +6382,76 @@
         <v>93</v>
       </c>
       <c r="G134" s="18" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="H134" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="135" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A135" s="5" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="C135" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E135" s="7" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="F135" s="7" t="s">
         <v>16</v>
       </c>
       <c r="G135" s="18" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="H135" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="136" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A136" s="5" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="C136" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="E136" s="7" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F136" s="7" t="s">
         <v>93</v>
       </c>
       <c r="G136" s="18" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="H136" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="137" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A137" s="5" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B137" s="6" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C137" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E137" s="7" t="s">
         <v>20</v>
@@ -6451,24 +6460,24 @@
         <v>93</v>
       </c>
       <c r="G137" s="18" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="H137" s="18" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
     </row>
     <row r="138" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A138" s="5" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B138" s="6" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C138" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D138" s="5" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E138" s="7" t="s">
         <v>20</v>
@@ -6477,24 +6486,24 @@
         <v>93</v>
       </c>
       <c r="G138" s="18" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="H138" s="18" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
     </row>
     <row r="139" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A139" s="5" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B139" s="6" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C139" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E139" s="7" t="s">
         <v>20</v>
@@ -6503,24 +6512,24 @@
         <v>9</v>
       </c>
       <c r="G139" s="18" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="H139" s="18" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
     </row>
     <row r="140" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A140" s="5" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B140" s="6" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C140" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D140" s="5" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E140" s="7" t="s">
         <v>20</v>
@@ -6529,24 +6538,24 @@
         <v>13</v>
       </c>
       <c r="G140" s="18" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="H140" s="18" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
     </row>
     <row r="141" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A141" s="5" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B141" s="6" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C141" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D141" s="5" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E141" s="7" t="s">
         <v>20</v>
@@ -6555,24 +6564,24 @@
         <v>13</v>
       </c>
       <c r="G141" s="18" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="H141" s="18" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
     </row>
     <row r="142" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A142" s="5" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B142" s="6" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C142" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D142" s="5" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E142" s="7" t="s">
         <v>20</v>
@@ -6581,24 +6590,24 @@
         <v>13</v>
       </c>
       <c r="G142" s="18" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="H142" s="18" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
     </row>
     <row r="143" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A143" s="5" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B143" s="6" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C143" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D143" s="5" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E143" s="7" t="s">
         <v>20</v>
@@ -6607,24 +6616,24 @@
         <v>13</v>
       </c>
       <c r="G143" s="18" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="H143" s="18" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
     </row>
     <row r="144" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A144" s="5" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B144" s="6" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C144" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D144" s="5" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E144" s="7" t="s">
         <v>20</v>
@@ -6633,24 +6642,24 @@
         <v>13</v>
       </c>
       <c r="G144" s="18" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="H144" s="18" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
     </row>
     <row r="145" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A145" s="5" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B145" s="6" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C145" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D145" s="5" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E145" s="7" t="s">
         <v>20</v>
@@ -6659,24 +6668,24 @@
         <v>13</v>
       </c>
       <c r="G145" s="18" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="H145" s="18" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
     </row>
     <row r="146" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A146" s="5" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B146" s="6" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C146" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D146" s="5" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E146" s="7" t="s">
         <v>20</v>
@@ -6685,24 +6694,24 @@
         <v>13</v>
       </c>
       <c r="G146" s="18" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="H146" s="18" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
     </row>
     <row r="147" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A147" s="5" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B147" s="6" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="C147" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D147" s="5" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E147" s="7" t="s">
         <v>20</v>
@@ -6711,24 +6720,24 @@
         <v>13</v>
       </c>
       <c r="G147" s="18" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="H147" s="18" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
     </row>
     <row r="148" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A148" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B148" s="6" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C148" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D148" s="5" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E148" s="7" t="s">
         <v>20</v>
@@ -6737,24 +6746,24 @@
         <v>13</v>
       </c>
       <c r="G148" s="18" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="H148" s="18" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
     </row>
     <row r="149" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A149" s="5" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B149" s="6" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C149" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D149" s="5" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="E149" s="7" t="s">
         <v>20</v>
@@ -6763,24 +6772,24 @@
         <v>9</v>
       </c>
       <c r="G149" s="18" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="H149" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="150" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A150" s="5" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B150" s="6" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C150" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D150" s="5" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="E150" s="7" t="s">
         <v>20</v>
@@ -6789,24 +6798,24 @@
         <v>9</v>
       </c>
       <c r="G150" s="18" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="H150" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="151" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A151" s="5" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B151" s="6" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="C151" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D151" s="5" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="E151" s="7" t="s">
         <v>8</v>
@@ -6815,24 +6824,24 @@
         <v>16</v>
       </c>
       <c r="G151" s="18" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="H151" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="152" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A152" s="5" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B152" s="6" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C152" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D152" s="5" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="E152" s="7" t="s">
         <v>20</v>
@@ -6841,24 +6850,24 @@
         <v>93</v>
       </c>
       <c r="G152" s="18" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="H152" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="153" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A153" s="5" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B153" s="6" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C153" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D153" s="5" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="E153" s="7" t="s">
         <v>20</v>
@@ -6867,24 +6876,24 @@
         <v>93</v>
       </c>
       <c r="G153" s="18" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="H153" s="18" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
     </row>
     <row r="154" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A154" s="5" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B154" s="6" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C154" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D154" s="5" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E154" s="7" t="s">
         <v>20</v>
@@ -6893,24 +6902,24 @@
         <v>9</v>
       </c>
       <c r="G154" s="18" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="H154" s="18" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
     </row>
     <row r="155" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A155" s="5" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B155" s="6" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C155" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="E155" s="7" t="s">
         <v>20</v>
@@ -6919,24 +6928,24 @@
         <v>16</v>
       </c>
       <c r="G155" s="18" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="H155" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="156" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A156" s="5" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B156" s="6" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="C156" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="E156" s="7" t="s">
         <v>100</v>
@@ -6945,24 +6954,24 @@
         <v>16</v>
       </c>
       <c r="G156" s="18" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="H156" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="157" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A157" s="5" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B157" s="6" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C157" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="E157" s="7" t="s">
         <v>20</v>
@@ -6971,24 +6980,24 @@
         <v>16</v>
       </c>
       <c r="G157" s="18" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="H157" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="158" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A158" s="5" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B158" s="6" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C158" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D158" s="5" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E158" s="7" t="s">
         <v>20</v>
@@ -6997,24 +7006,24 @@
         <v>9</v>
       </c>
       <c r="G158" s="18" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="H158" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="159" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A159" s="5" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B159" s="6" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C159" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E159" s="7" t="s">
         <v>20</v>
@@ -7023,24 +7032,24 @@
         <v>13</v>
       </c>
       <c r="G159" s="18" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="H159" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="160" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A160" s="5" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B160" s="6" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C160" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D160" s="5" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E160" s="7" t="s">
         <v>20</v>
@@ -7049,24 +7058,24 @@
         <v>13</v>
       </c>
       <c r="G160" s="18" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="H160" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="161" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A161" s="5" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B161" s="6" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C161" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D161" s="5" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E161" s="7" t="s">
         <v>20</v>
@@ -7075,24 +7084,24 @@
         <v>13</v>
       </c>
       <c r="G161" s="18" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="H161" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="162" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A162" s="5" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B162" s="6" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C162" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D162" s="5" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E162" s="7" t="s">
         <v>20</v>
@@ -7101,24 +7110,24 @@
         <v>13</v>
       </c>
       <c r="G162" s="18" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="H162" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="163" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A163" s="5" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B163" s="6" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="C163" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D163" s="5" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E163" s="7" t="s">
         <v>20</v>
@@ -7127,24 +7136,24 @@
         <v>13</v>
       </c>
       <c r="G163" s="18" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="H163" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="164" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A164" s="5" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B164" s="6" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C164" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D164" s="5" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E164" s="7" t="s">
         <v>8</v>
@@ -7153,24 +7162,24 @@
         <v>13</v>
       </c>
       <c r="G164" s="18" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="H164" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="165" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A165" s="5" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B165" s="6" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="C165" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D165" s="5" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="E165" s="7" t="s">
         <v>8</v>
@@ -7179,24 +7188,24 @@
         <v>93</v>
       </c>
       <c r="G165" s="18" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="H165" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="166" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A166" s="5" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B166" s="6" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C166" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D166" s="5" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="E166" s="7" t="s">
         <v>20</v>
@@ -7205,24 +7214,24 @@
         <v>13</v>
       </c>
       <c r="G166" s="18" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="H166" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="167" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A167" s="5" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B167" s="6" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C167" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D167" s="5" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="E167" s="7" t="s">
         <v>20</v>
@@ -7231,24 +7240,24 @@
         <v>13</v>
       </c>
       <c r="G167" s="18" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="H167" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="168" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A168" s="5" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B168" s="6" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C168" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D168" s="5" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="E168" s="7" t="s">
         <v>20</v>
@@ -7257,24 +7266,24 @@
         <v>13</v>
       </c>
       <c r="G168" s="18" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="H168" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="169" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A169" s="5" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B169" s="6" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C169" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D169" s="5" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="E169" s="7" t="s">
         <v>20</v>
@@ -7283,24 +7292,24 @@
         <v>13</v>
       </c>
       <c r="G169" s="18" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="H169" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="170" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A170" s="5" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B170" s="6" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C170" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D170" s="5" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="E170" s="7" t="s">
         <v>20</v>
@@ -7309,24 +7318,24 @@
         <v>13</v>
       </c>
       <c r="G170" s="18" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="H170" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="171" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A171" s="5" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B171" s="6" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C171" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D171" s="5" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="E171" s="7" t="s">
         <v>100</v>
@@ -7335,24 +7344,24 @@
         <v>93</v>
       </c>
       <c r="G171" s="18" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="H171" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="172" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A172" s="5" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B172" s="6" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C172" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D172" s="5" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="E172" s="7" t="s">
         <v>100</v>
@@ -7361,24 +7370,24 @@
         <v>93</v>
       </c>
       <c r="G172" s="18" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="H172" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="173" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A173" s="5" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B173" s="6" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C173" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D173" s="5" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="E173" s="7" t="s">
         <v>100</v>
@@ -7387,24 +7396,24 @@
         <v>93</v>
       </c>
       <c r="G173" s="18" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="H173" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="174" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A174" s="5" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B174" s="6" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C174" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D174" s="5" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="E174" s="7" t="s">
         <v>100</v>
@@ -7413,24 +7422,24 @@
         <v>93</v>
       </c>
       <c r="G174" s="18" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="H174" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="175" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A175" s="5" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B175" s="6" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C175" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D175" s="5" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="E175" s="7" t="s">
         <v>100</v>
@@ -7439,24 +7448,24 @@
         <v>93</v>
       </c>
       <c r="G175" s="18" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="H175" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="176" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A176" s="5" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B176" s="6" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="C176" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D176" s="5" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="E176" s="7" t="s">
         <v>100</v>
@@ -7465,24 +7474,24 @@
         <v>93</v>
       </c>
       <c r="G176" s="18" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="H176" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="177" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A177" s="5" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B177" s="6" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="C177" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D177" s="5" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="E177" s="7" t="s">
         <v>100</v>
@@ -7491,24 +7500,24 @@
         <v>93</v>
       </c>
       <c r="G177" s="18" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="H177" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="178" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A178" s="5" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B178" s="6" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C178" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D178" s="5" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="E178" s="7" t="s">
         <v>20</v>
@@ -7517,24 +7526,24 @@
         <v>9</v>
       </c>
       <c r="G178" s="18" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="H178" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="179" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A179" s="5" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B179" s="6" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="C179" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D179" s="5" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="E179" s="7" t="s">
         <v>20</v>
@@ -7543,24 +7552,24 @@
         <v>9</v>
       </c>
       <c r="G179" s="18" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="H179" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="180" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A180" s="5" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B180" s="6" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C180" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D180" s="5" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E180" s="7" t="s">
         <v>20</v>
@@ -7569,24 +7578,24 @@
         <v>9</v>
       </c>
       <c r="G180" s="18" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="H180" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="181" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A181" s="5" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B181" s="6" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C181" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D181" s="5" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E181" s="7" t="s">
         <v>20</v>
@@ -7595,24 +7604,24 @@
         <v>9</v>
       </c>
       <c r="G181" s="18" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="H181" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="182" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A182" s="5" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B182" s="6" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C182" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D182" s="5" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E182" s="7" t="s">
         <v>20</v>
@@ -7621,24 +7630,24 @@
         <v>13</v>
       </c>
       <c r="G182" s="18" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="H182" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="183" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A183" s="5" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B183" s="6" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C183" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D183" s="5" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E183" s="7" t="s">
         <v>20</v>
@@ -7647,24 +7656,24 @@
         <v>13</v>
       </c>
       <c r="G183" s="18" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="H183" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="184" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A184" s="5" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B184" s="6" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C184" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D184" s="5" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E184" s="7" t="s">
         <v>20</v>
@@ -7673,50 +7682,50 @@
         <v>13</v>
       </c>
       <c r="G184" s="18" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="H184" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="185" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A185" s="5" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B185" s="6" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="C185" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D185" s="5" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E185" s="7" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F185" s="7" t="s">
         <v>13</v>
       </c>
       <c r="G185" s="18" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="H185" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="186" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A186" s="5" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B186" s="6" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C186" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D186" s="5" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E186" s="7" t="s">
         <v>20</v>
@@ -7725,24 +7734,24 @@
         <v>13</v>
       </c>
       <c r="G186" s="18" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="H186" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="187" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A187" s="5" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B187" s="6" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="C187" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D187" s="5" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E187" s="7" t="s">
         <v>20</v>
@@ -7751,24 +7760,24 @@
         <v>13</v>
       </c>
       <c r="G187" s="18" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="H187" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="188" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A188" s="5" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B188" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C188" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D188" s="5" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E188" s="7" t="s">
         <v>20</v>
@@ -7777,24 +7786,24 @@
         <v>93</v>
       </c>
       <c r="G188" s="18" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="H188" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="189" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A189" s="5" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B189" s="6" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C189" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D189" s="5" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="E189" s="7" t="s">
         <v>20</v>
@@ -7803,24 +7812,24 @@
         <v>9</v>
       </c>
       <c r="G189" s="18" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="H189" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="190" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A190" s="5" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B190" s="6" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C190" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D190" s="5" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="E190" s="7" t="s">
         <v>20</v>
@@ -7829,24 +7838,24 @@
         <v>9</v>
       </c>
       <c r="G190" s="18" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="H190" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="191" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A191" s="5" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B191" s="6" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C191" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D191" s="5" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="E191" s="7" t="s">
         <v>20</v>
@@ -7855,24 +7864,24 @@
         <v>9</v>
       </c>
       <c r="G191" s="18" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="H191" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="192" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A192" s="5" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B192" s="6" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="C192" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D192" s="5" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="E192" s="7" t="s">
         <v>20</v>
@@ -7881,24 +7890,24 @@
         <v>9</v>
       </c>
       <c r="G192" s="18" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="H192" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="193" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A193" s="5" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B193" s="6" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C193" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D193" s="5" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E193" s="7" t="s">
         <v>20</v>
@@ -7907,24 +7916,24 @@
         <v>16</v>
       </c>
       <c r="G193" s="18" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="H193" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="194" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A194" s="5" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B194" s="6" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C194" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D194" s="5" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E194" s="7" t="s">
         <v>20</v>
@@ -7933,24 +7942,24 @@
         <v>16</v>
       </c>
       <c r="G194" s="18" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="H194" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="195" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A195" s="5" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B195" s="6" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C195" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D195" s="5" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="E195" s="7" t="s">
         <v>20</v>
@@ -7959,24 +7968,24 @@
         <v>9</v>
       </c>
       <c r="G195" s="18" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="H195" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="196" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A196" s="5" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B196" s="6" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C196" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D196" s="5" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="E196" s="7" t="s">
         <v>20</v>
@@ -7985,24 +7994,24 @@
         <v>9</v>
       </c>
       <c r="G196" s="18" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="H196" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="197" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A197" s="5" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B197" s="6" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C197" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D197" s="5" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="E197" s="7" t="s">
         <v>20</v>
@@ -8011,24 +8020,24 @@
         <v>9</v>
       </c>
       <c r="G197" s="18" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="H197" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="198" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A198" s="5" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="B198" s="6" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C198" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D198" s="5" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="E198" s="7" t="s">
         <v>20</v>
@@ -8037,24 +8046,24 @@
         <v>93</v>
       </c>
       <c r="G198" s="18" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="H198" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="199" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A199" s="5" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B199" s="6" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C199" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D199" s="5" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="E199" s="7" t="s">
         <v>20</v>
@@ -8063,24 +8072,24 @@
         <v>9</v>
       </c>
       <c r="G199" s="18" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="H199" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="200" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A200" s="5" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B200" s="6" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C200" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D200" s="5" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="E200" s="7" t="s">
         <v>20</v>
@@ -8089,24 +8098,24 @@
         <v>9</v>
       </c>
       <c r="G200" s="18" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="H200" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="201" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A201" s="5" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B201" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C201" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D201" s="5" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="E201" s="7" t="s">
         <v>20</v>
@@ -8115,24 +8124,24 @@
         <v>9</v>
       </c>
       <c r="G201" s="18" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="H201" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="202" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A202" s="5" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B202" s="6" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="C202" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D202" s="5" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="E202" s="7" t="s">
         <v>20</v>
@@ -8141,24 +8150,24 @@
         <v>9</v>
       </c>
       <c r="G202" s="18" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="H202" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="203" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A203" s="5" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B203" s="6" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C203" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D203" s="5" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E203" s="7" t="s">
         <v>20</v>
@@ -8167,24 +8176,24 @@
         <v>93</v>
       </c>
       <c r="G203" s="18" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="H203" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="204" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A204" s="5" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B204" s="6" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="C204" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D204" s="5" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E204" s="7" t="s">
         <v>8</v>
@@ -8193,50 +8202,50 @@
         <v>93</v>
       </c>
       <c r="G204" s="18" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="H204" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="205" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A205" s="5" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B205" s="6" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="C205" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D205" s="5" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E205" s="7" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F205" s="7" t="s">
         <v>93</v>
       </c>
       <c r="G205" s="18" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="H205" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="206" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A206" s="5" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B206" s="6" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C206" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D206" s="5" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="E206" s="7" t="s">
         <v>20</v>
@@ -8245,24 +8254,24 @@
         <v>9</v>
       </c>
       <c r="G206" s="18" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="H206" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="207" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A207" s="5" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B207" s="6" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C207" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D207" s="5" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="E207" s="7" t="s">
         <v>20</v>
@@ -8271,24 +8280,24 @@
         <v>93</v>
       </c>
       <c r="G207" s="18" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="H207" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="208" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A208" s="5" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="B208" s="6" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C208" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D208" s="5" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="E208" s="7" t="s">
         <v>20</v>
@@ -8297,24 +8306,24 @@
         <v>93</v>
       </c>
       <c r="G208" s="18" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="H208" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="209" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A209" s="5" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B209" s="6" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C209" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D209" s="5" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="E209" s="7" t="s">
         <v>20</v>
@@ -8323,24 +8332,24 @@
         <v>93</v>
       </c>
       <c r="G209" s="18" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="H209" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="210" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A210" s="5" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="B210" s="6" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="C210" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D210" s="5" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="E210" s="7" t="s">
         <v>100</v>
@@ -8349,24 +8358,24 @@
         <v>93</v>
       </c>
       <c r="G210" s="18" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="H210" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="211" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A211" s="5" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B211" s="6" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C211" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D211" s="5" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="E211" s="7" t="s">
         <v>20</v>
@@ -8375,24 +8384,24 @@
         <v>93</v>
       </c>
       <c r="G211" s="18" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="H211" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="212" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A212" s="5" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="B212" s="6" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C212" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D212" s="5" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="E212" s="7" t="s">
         <v>20</v>
@@ -8401,24 +8410,24 @@
         <v>9</v>
       </c>
       <c r="G212" s="18" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="H212" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="213" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A213" s="5" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="B213" s="6" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C213" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D213" s="5" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="E213" s="7" t="s">
         <v>20</v>
@@ -8427,24 +8436,24 @@
         <v>9</v>
       </c>
       <c r="G213" s="18" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="H213" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="214" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A214" s="5" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B214" s="6" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="C214" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D214" s="5" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="E214" s="7" t="s">
         <v>8</v>
@@ -8453,24 +8462,24 @@
         <v>16</v>
       </c>
       <c r="G214" s="18" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="H214" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="215" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A215" s="5" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B215" s="6" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C215" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D215" s="5" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="E215" s="7" t="s">
         <v>20</v>
@@ -8479,24 +8488,24 @@
         <v>13</v>
       </c>
       <c r="G215" s="18" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="H215" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="216" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A216" s="5" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="B216" s="6" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C216" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D216" s="5" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="E216" s="7" t="s">
         <v>20</v>
@@ -8505,24 +8514,24 @@
         <v>13</v>
       </c>
       <c r="G216" s="18" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="H216" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="217" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A217" s="5" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="B217" s="6" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C217" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D217" s="5" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="E217" s="7" t="s">
         <v>20</v>
@@ -8531,24 +8540,24 @@
         <v>9</v>
       </c>
       <c r="G217" s="18" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="H217" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="218" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A218" s="5" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="B218" s="6" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="C218" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D218" s="5" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="E218" s="7" t="s">
         <v>20</v>
@@ -8557,24 +8566,24 @@
         <v>93</v>
       </c>
       <c r="G218" s="18" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="H218" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="219" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A219" s="5" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B219" s="6" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C219" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D219" s="5" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="E219" s="7" t="s">
         <v>20</v>
@@ -8583,24 +8592,24 @@
         <v>9</v>
       </c>
       <c r="G219" s="18" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="H219" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="220" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A220" s="5" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="B220" s="6" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C220" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D220" s="5" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="E220" s="7" t="s">
         <v>20</v>
@@ -8609,24 +8618,24 @@
         <v>9</v>
       </c>
       <c r="G220" s="18" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="H220" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="221" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A221" s="5" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="B221" s="6" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="C221" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D221" s="5" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="E221" s="7" t="s">
         <v>8</v>
@@ -8635,24 +8644,24 @@
         <v>16</v>
       </c>
       <c r="G221" s="18" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="H221" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="222" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A222" s="5" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="B222" s="6" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="C222" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D222" s="5" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="E222" s="7" t="s">
         <v>20</v>
@@ -8661,24 +8670,24 @@
         <v>9</v>
       </c>
       <c r="G222" s="18" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="H222" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="223" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A223" s="5" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="B223" s="6" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C223" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D223" s="5" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="E223" s="7" t="s">
         <v>20</v>
@@ -8687,24 +8696,24 @@
         <v>9</v>
       </c>
       <c r="G223" s="18" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="H223" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="224" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A224" s="5" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="B224" s="6" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C224" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D224" s="5" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="E224" s="7" t="s">
         <v>20</v>
@@ -8713,24 +8722,24 @@
         <v>16</v>
       </c>
       <c r="G224" s="18" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="H224" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="225" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A225" s="5" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="B225" s="6" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="C225" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D225" s="5" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="E225" s="7" t="s">
         <v>8</v>
@@ -8739,24 +8748,24 @@
         <v>93</v>
       </c>
       <c r="G225" s="18" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="H225" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="226" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A226" s="5" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="B226" s="6" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="C226" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D226" s="5" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="E226" s="7" t="s">
         <v>20</v>
@@ -8765,24 +8774,24 @@
         <v>9</v>
       </c>
       <c r="G226" s="18" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="H226" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="227" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A227" s="5" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="B227" s="6" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="C227" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D227" s="5" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="E227" s="7" t="s">
         <v>20</v>
@@ -8791,24 +8800,24 @@
         <v>93</v>
       </c>
       <c r="G227" s="18" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="H227" s="18" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
     </row>
     <row r="228" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A228" s="5" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B228" s="6" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="C228" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D228" s="5" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="E228" s="7" t="s">
         <v>20</v>
@@ -8817,24 +8826,24 @@
         <v>93</v>
       </c>
       <c r="G228" s="18" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="H228" s="18" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
     </row>
     <row r="229" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A229" s="5" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="B229" s="6" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="C229" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D229" s="5" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="E229" s="7" t="s">
         <v>20</v>
@@ -8843,24 +8852,24 @@
         <v>93</v>
       </c>
       <c r="G229" s="18" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="H229" s="18" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
     </row>
     <row r="230" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A230" s="5" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B230" s="6" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="C230" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D230" s="5" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="E230" s="7" t="s">
         <v>20</v>
@@ -8869,24 +8878,24 @@
         <v>93</v>
       </c>
       <c r="G230" s="18" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="H230" s="18" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
     </row>
     <row r="231" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A231" s="5" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="B231" s="6" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="C231" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D231" s="5" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="E231" s="7" t="s">
         <v>20</v>
@@ -8895,50 +8904,50 @@
         <v>13</v>
       </c>
       <c r="G231" s="18" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="H231" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="232" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A232" s="5" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="B232" s="6" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="C232" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D232" s="5" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="E232" s="7" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F232" s="7" t="s">
         <v>93</v>
       </c>
       <c r="G232" s="18" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="H232" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="233" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A233" s="5" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="B233" s="6" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="C233" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D233" s="5" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="E233" s="7" t="s">
         <v>20</v>
@@ -8947,50 +8956,50 @@
         <v>93</v>
       </c>
       <c r="G233" s="18" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="H233" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="234" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A234" s="5" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="B234" s="6" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="C234" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D234" s="5" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="E234" s="7" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F234" s="7" t="s">
         <v>9</v>
       </c>
       <c r="G234" s="18" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="H234" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="235" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A235" s="5" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B235" s="6" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="C235" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D235" s="5" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="E235" s="7" t="s">
         <v>20</v>
@@ -8999,24 +9008,24 @@
         <v>9</v>
       </c>
       <c r="G235" s="18" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="H235" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="236" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A236" s="5" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="B236" s="6" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="C236" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D236" s="5" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="E236" s="7" t="s">
         <v>20</v>
@@ -9025,50 +9034,50 @@
         <v>16</v>
       </c>
       <c r="G236" s="18" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="H236" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="237" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A237" s="5" t="s">
-        <v>566</v>
+        <v>789</v>
       </c>
       <c r="B237" s="6" t="s">
-        <v>567</v>
+        <v>790</v>
       </c>
       <c r="C237" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D237" s="5" t="s">
-        <v>565</v>
+        <v>791</v>
       </c>
       <c r="E237" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F237" s="7" t="s">
-        <v>93</v>
+        <v>16</v>
       </c>
       <c r="G237" s="18" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="H237" s="18" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="238" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A238" s="5" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="B238" s="6" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="C238" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D238" s="5" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="E238" s="7" t="s">
         <v>20</v>
@@ -9077,24 +9086,24 @@
         <v>93</v>
       </c>
       <c r="G238" s="18" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="H238" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="239" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A239" s="5" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="B239" s="6" t="s">
-        <v>735</v>
+        <v>567</v>
       </c>
       <c r="C239" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D239" s="5" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="E239" s="7" t="s">
         <v>20</v>
@@ -9103,50 +9112,50 @@
         <v>93</v>
       </c>
       <c r="G239" s="18" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="H239" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="240" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A240" s="5" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="B240" s="6" t="s">
-        <v>753</v>
+        <v>733</v>
       </c>
       <c r="C240" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D240" s="5" t="s">
-        <v>571</v>
+        <v>563</v>
       </c>
       <c r="E240" s="7" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F240" s="7" t="s">
         <v>93</v>
       </c>
       <c r="G240" s="18" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="H240" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="241" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A241" s="5" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="B241" s="6" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="C241" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D241" s="5" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="E241" s="7" t="s">
         <v>8</v>
@@ -9155,102 +9164,102 @@
         <v>93</v>
       </c>
       <c r="G241" s="18" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="H241" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="242" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A242" s="5" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="B242" s="6" t="s">
-        <v>736</v>
+        <v>752</v>
       </c>
       <c r="C242" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D242" s="5" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="E242" s="7" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F242" s="7" t="s">
         <v>93</v>
       </c>
       <c r="G242" s="18" t="s">
-        <v>715</v>
+        <v>709</v>
       </c>
       <c r="H242" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="243" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A243" s="5" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="B243" s="6" t="s">
-        <v>755</v>
+        <v>734</v>
       </c>
       <c r="C243" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D243" s="5" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="E243" s="7" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F243" s="7" t="s">
         <v>93</v>
       </c>
       <c r="G243" s="18" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="H243" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="244" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A244" s="5" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="B244" s="6" t="s">
-        <v>578</v>
+        <v>753</v>
       </c>
       <c r="C244" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D244" s="5" t="s">
-        <v>576</v>
+        <v>569</v>
       </c>
       <c r="E244" s="7" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F244" s="7" t="s">
-        <v>13</v>
+        <v>93</v>
       </c>
       <c r="G244" s="18" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="H244" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="245" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A245" s="5" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="B245" s="6" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="C245" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D245" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E245" s="7" t="s">
         <v>20</v>
@@ -9259,24 +9268,24 @@
         <v>13</v>
       </c>
       <c r="G245" s="18" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="H245" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="246" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A246" s="5" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="B246" s="6" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="C246" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D246" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E246" s="7" t="s">
         <v>20</v>
@@ -9285,50 +9294,50 @@
         <v>13</v>
       </c>
       <c r="G246" s="18" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="H246" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="247" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A247" s="5" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="B247" s="6" t="s">
-        <v>586</v>
+        <v>580</v>
       </c>
       <c r="C247" s="7" t="s">
-        <v>583</v>
+        <v>338</v>
       </c>
       <c r="D247" s="5" t="s">
-        <v>584</v>
+        <v>574</v>
       </c>
       <c r="E247" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F247" s="7" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G247" s="18" t="s">
-        <v>716</v>
+        <v>706</v>
       </c>
       <c r="H247" s="18" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
     </row>
     <row r="248" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A248" s="5" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="B248" s="6" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="C248" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D248" s="5" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="E248" s="7" t="s">
         <v>20</v>
@@ -9337,76 +9346,76 @@
         <v>9</v>
       </c>
       <c r="G248" s="18" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="H248" s="18" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
     </row>
     <row r="249" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A249" s="5">
-        <v>3164</v>
+      <c r="A249" s="5" t="s">
+        <v>585</v>
       </c>
       <c r="B249" s="6" t="s">
-        <v>737</v>
+        <v>586</v>
       </c>
       <c r="C249" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D249" s="5" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="E249" s="7" t="s">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="F249" s="7" t="s">
         <v>9</v>
       </c>
       <c r="G249" s="18" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="H249" s="18" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
     </row>
     <row r="250" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A250" s="5" t="s">
-        <v>590</v>
+      <c r="A250" s="5">
+        <v>3164</v>
       </c>
       <c r="B250" s="6" t="s">
-        <v>591</v>
+        <v>735</v>
       </c>
       <c r="C250" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D250" s="5" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E250" s="7" t="s">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="F250" s="7" t="s">
         <v>9</v>
       </c>
       <c r="G250" s="18" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="H250" s="18" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
     </row>
     <row r="251" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A251" s="5" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="B251" s="6" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="C251" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D251" s="5" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="E251" s="7" t="s">
         <v>20</v>
@@ -9415,50 +9424,50 @@
         <v>9</v>
       </c>
       <c r="G251" s="18" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="H251" s="18" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
     </row>
     <row r="252" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A252" s="13" t="s">
-        <v>596</v>
+      <c r="A252" s="5" t="s">
+        <v>591</v>
       </c>
       <c r="B252" s="6" t="s">
-        <v>738</v>
+        <v>592</v>
       </c>
       <c r="C252" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D252" s="5" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="E252" s="7" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F252" s="7" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="G252" s="18" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="H252" s="18" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
     </row>
     <row r="253" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A253" s="13" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="B253" s="6" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="C253" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D253" s="5" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="E253" s="7" t="s">
         <v>8</v>
@@ -9467,102 +9476,102 @@
         <v>16</v>
       </c>
       <c r="G253" s="18" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="H253" s="18" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
     </row>
     <row r="254" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A254" s="5" t="s">
-        <v>599</v>
+      <c r="A254" s="13" t="s">
+        <v>595</v>
       </c>
       <c r="B254" s="6" t="s">
-        <v>600</v>
+        <v>737</v>
       </c>
       <c r="C254" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D254" s="5" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="E254" s="7" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F254" s="7" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="G254" s="18" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="H254" s="18" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
     </row>
     <row r="255" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A255" s="5" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="B255" s="6" t="s">
-        <v>740</v>
+        <v>598</v>
       </c>
       <c r="C255" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D255" s="5" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="E255" s="7" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F255" s="7" t="s">
         <v>9</v>
       </c>
       <c r="G255" s="18" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H255" s="18" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
     </row>
     <row r="256" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A256" s="5" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="B256" s="6" t="s">
-        <v>605</v>
+        <v>738</v>
       </c>
       <c r="C256" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D256" s="5" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="E256" s="7" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F256" s="7" t="s">
         <v>9</v>
       </c>
       <c r="G256" s="18" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="H256" s="18" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
     </row>
     <row r="257" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A257" s="5" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="B257" s="6" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="C257" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D257" s="5" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="E257" s="7" t="s">
         <v>20</v>
@@ -9571,24 +9580,24 @@
         <v>9</v>
       </c>
       <c r="G257" s="18" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="H257" s="18" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
     </row>
     <row r="258" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A258" s="5" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="B258" s="6" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="C258" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D258" s="5" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="E258" s="7" t="s">
         <v>20</v>
@@ -9597,24 +9606,24 @@
         <v>9</v>
       </c>
       <c r="G258" s="18" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="H258" s="18" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
     </row>
     <row r="259" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A259" s="5" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="B259" s="6" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="C259" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D259" s="5" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="E259" s="7" t="s">
         <v>20</v>
@@ -9623,24 +9632,24 @@
         <v>9</v>
       </c>
       <c r="G259" s="18" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="H259" s="18" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
     </row>
     <row r="260" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A260" s="5" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="B260" s="6" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="C260" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D260" s="5" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="E260" s="7" t="s">
         <v>20</v>
@@ -9649,50 +9658,50 @@
         <v>9</v>
       </c>
       <c r="G260" s="18" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="H260" s="18" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
     </row>
     <row r="261" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A261" s="5" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="B261" s="6" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="C261" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D261" s="5" t="s">
-        <v>614</v>
+        <v>601</v>
       </c>
       <c r="E261" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F261" s="7" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="G261" s="18" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="H261" s="18" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
     </row>
     <row r="262" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A262" s="5" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="B262" s="6" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="C262" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D262" s="5" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="E262" s="7" t="s">
         <v>20</v>
@@ -9701,24 +9710,24 @@
         <v>16</v>
       </c>
       <c r="G262" s="18" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="H262" s="18" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
     </row>
     <row r="263" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A263" s="5" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="B263" s="6" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="C263" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D263" s="5" t="s">
-        <v>619</v>
+        <v>612</v>
       </c>
       <c r="E263" s="7" t="s">
         <v>20</v>
@@ -9727,24 +9736,24 @@
         <v>16</v>
       </c>
       <c r="G263" s="18" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="H263" s="18" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
     </row>
     <row r="264" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A264" s="5" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="B264" s="6" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="C264" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D264" s="5" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="E264" s="7" t="s">
         <v>20</v>
@@ -9753,24 +9762,24 @@
         <v>16</v>
       </c>
       <c r="G264" s="18" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="H264" s="18" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
     </row>
     <row r="265" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A265" s="5" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="B265" s="6" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="C265" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D265" s="5" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="E265" s="7" t="s">
         <v>20</v>
@@ -9779,24 +9788,24 @@
         <v>16</v>
       </c>
       <c r="G265" s="18" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="H265" s="18" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
     </row>
     <row r="266" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A266" s="5" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="B266" s="6" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="C266" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D266" s="5" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="E266" s="7" t="s">
         <v>20</v>
@@ -9805,24 +9814,24 @@
         <v>16</v>
       </c>
       <c r="G266" s="18" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="H266" s="18" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
     </row>
     <row r="267" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A267" s="5" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="B267" s="6" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="C267" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D267" s="5" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="E267" s="7" t="s">
         <v>20</v>
@@ -9831,24 +9840,24 @@
         <v>16</v>
       </c>
       <c r="G267" s="18" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="H267" s="18" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
     </row>
     <row r="268" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A268" s="5" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="B268" s="6" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="C268" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D268" s="5" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="E268" s="7" t="s">
         <v>20</v>
@@ -9857,24 +9866,24 @@
         <v>16</v>
       </c>
       <c r="G268" s="18" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="H268" s="18" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
     </row>
     <row r="269" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A269" s="5" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="B269" s="6" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="C269" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D269" s="5" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="E269" s="7" t="s">
         <v>20</v>
@@ -9883,76 +9892,76 @@
         <v>16</v>
       </c>
       <c r="G269" s="18" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="H269" s="18" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
     </row>
     <row r="270" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A270" s="5" t="s">
-        <v>635</v>
+        <v>630</v>
       </c>
       <c r="B270" s="6" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="C270" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D270" s="5" t="s">
-        <v>634</v>
+        <v>617</v>
       </c>
       <c r="E270" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F270" s="7" t="s">
-        <v>93</v>
+        <v>16</v>
       </c>
       <c r="G270" s="18" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="H270" s="18" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
     </row>
     <row r="271" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A271" s="5" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="B271" s="6" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="C271" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D271" s="5" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="E271" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F271" s="7" t="s">
-        <v>9</v>
+        <v>93</v>
       </c>
       <c r="G271" s="18" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="H271" s="18" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="272" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A272" s="5" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="B272" s="6" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="C272" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D272" s="5" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="E272" s="7" t="s">
         <v>20</v>
@@ -9961,24 +9970,24 @@
         <v>9</v>
       </c>
       <c r="G272" s="18" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="H272" s="18" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
     </row>
     <row r="273" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A273" s="5" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="B273" s="6" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="C273" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D273" s="5" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="E273" s="7" t="s">
         <v>20</v>
@@ -9987,50 +9996,50 @@
         <v>9</v>
       </c>
       <c r="G273" s="18" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="H273" s="18" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
     </row>
     <row r="274" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A274" s="5" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="B274" s="6" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
       <c r="C274" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D274" s="5" t="s">
-        <v>644</v>
+        <v>635</v>
       </c>
       <c r="E274" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F274" s="7" t="s">
-        <v>93</v>
+        <v>9</v>
       </c>
       <c r="G274" s="18" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="H274" s="18" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
     </row>
     <row r="275" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A275" s="5" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="B275" s="6" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="C275" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D275" s="5" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="E275" s="7" t="s">
         <v>20</v>
@@ -10039,50 +10048,50 @@
         <v>93</v>
       </c>
       <c r="G275" s="18" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="H275" s="18" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
     </row>
     <row r="276" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A276" s="5" t="s">
-        <v>650</v>
+        <v>645</v>
       </c>
       <c r="B276" s="6" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="C276" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D276" s="5" t="s">
-        <v>649</v>
+        <v>642</v>
       </c>
       <c r="E276" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F276" s="7" t="s">
-        <v>13</v>
+        <v>93</v>
       </c>
       <c r="G276" s="18" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
       <c r="H276" s="18" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
     </row>
     <row r="277" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A277" s="5" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="B277" s="6" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="C277" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D277" s="5" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="E277" s="7" t="s">
         <v>20</v>
@@ -10091,128 +10100,128 @@
         <v>13</v>
       </c>
       <c r="G277" s="18" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="H277" s="18" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
     </row>
     <row r="278" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A278" s="5" t="s">
-        <v>655</v>
+        <v>650</v>
       </c>
       <c r="B278" s="6" t="s">
-        <v>656</v>
+        <v>651</v>
       </c>
       <c r="C278" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D278" s="5" t="s">
-        <v>654</v>
+        <v>647</v>
       </c>
       <c r="E278" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F278" s="7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G278" s="18" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="H278" s="18" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="279" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A279" s="5" t="s">
-        <v>658</v>
+        <v>653</v>
       </c>
       <c r="B279" s="6" t="s">
-        <v>773</v>
+        <v>654</v>
       </c>
       <c r="C279" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D279" s="5" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
       <c r="E279" s="7" t="s">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="F279" s="7" t="s">
-        <v>93</v>
+        <v>16</v>
       </c>
       <c r="G279" s="18" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="H279" s="18" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
     </row>
     <row r="280" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A280" s="5" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="B280" s="6" t="s">
-        <v>661</v>
+        <v>771</v>
       </c>
       <c r="C280" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D280" s="5" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="E280" s="7" t="s">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="F280" s="7" t="s">
-        <v>9</v>
+        <v>93</v>
       </c>
       <c r="G280" s="18" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
       <c r="H280" s="18" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
     </row>
     <row r="281" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A281" s="5" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="B281" s="6" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="C281" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D281" s="5" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="E281" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F281" s="7" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G281" s="18" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="H281" s="18" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
     </row>
     <row r="282" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A282" s="5" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="B282" s="6" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="C282" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D282" s="5" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="E282" s="7" t="s">
         <v>20</v>
@@ -10221,50 +10230,50 @@
         <v>13</v>
       </c>
       <c r="G282" s="18" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="H282" s="18" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
     </row>
     <row r="283" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A283" s="5" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="B283" s="6" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="C283" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D283" s="5" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="E283" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F283" s="7" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G283" s="18" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="H283" s="18" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
     </row>
     <row r="284" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A284" s="5" t="s">
-        <v>671</v>
-      </c>
-      <c r="B284" s="14" t="s">
-        <v>672</v>
+        <v>666</v>
+      </c>
+      <c r="B284" s="6" t="s">
+        <v>667</v>
       </c>
       <c r="C284" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D284" s="5" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="E284" s="7" t="s">
         <v>20</v>
@@ -10273,24 +10282,24 @@
         <v>9</v>
       </c>
       <c r="G284" s="18" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H284" s="18" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="285" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A285" s="5" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="B285" s="14" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="C285" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D285" s="5" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="E285" s="7" t="s">
         <v>20</v>
@@ -10299,14 +10308,40 @@
         <v>9</v>
       </c>
       <c r="G285" s="18" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="H285" s="18" t="s">
-        <v>789</v>
+        <v>787</v>
+      </c>
+    </row>
+    <row r="286" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A286" s="5" t="s">
+        <v>671</v>
+      </c>
+      <c r="B286" s="14" t="s">
+        <v>672</v>
+      </c>
+      <c r="C286" s="7" t="s">
+        <v>581</v>
+      </c>
+      <c r="D286" s="5" t="s">
+        <v>668</v>
+      </c>
+      <c r="E286" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F286" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G286" s="18" t="s">
+        <v>718</v>
+      </c>
+      <c r="H286" s="18" t="s">
+        <v>787</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H285" xr:uid="{446419A3-BB56-46D4-B296-D3867C4128DB}"/>
+  <autoFilter ref="A1:H286" xr:uid="{446419A3-BB56-46D4-B296-D3867C4128DB}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/source-excel/DATAPLANT.xlsx
+++ b/source-excel/DATAPLANT.xlsx
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI\รายงานการจัดระดับ\ข้อมูลทำ AI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI\รายงานการจัดระดับ\newstarrating\source-excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{720F7EC5-1DA2-40E4-A6EC-05554319622E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ECB9D3A-B662-4D04-9F59-2A5C74E4D79E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{22141E00-01BD-4411-8006-614C22989334}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="8130" xr2:uid="{22141E00-01BD-4411-8006-614C22989334}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$285</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$286</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2279" uniqueCount="791">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2287" uniqueCount="794">
   <si>
     <t>กิจการ</t>
   </si>
@@ -444,9 +444,6 @@
     <t>FC214</t>
   </si>
   <si>
-    <t>สระกระโจม</t>
-  </si>
-  <si>
     <t>FC248</t>
   </si>
   <si>
@@ -454,9 +451,6 @@
   </si>
   <si>
     <t>FC299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">เนินพระปรางค์ </t>
   </si>
   <si>
     <t>บจก.กอวัฒนาคอนกรีต</t>
@@ -2402,6 +2396,21 @@
   </si>
   <si>
     <t>กําธร ชูจักร์</t>
+  </si>
+  <si>
+    <t>FC018</t>
+  </si>
+  <si>
+    <t>บึงกาฬ</t>
+  </si>
+  <si>
+    <t>หจก.เซ็นจูรี่บึงกาฬ</t>
+  </si>
+  <si>
+    <t>ดอนเจดีย์</t>
+  </si>
+  <si>
+    <t>สองพี่น้อง 2</t>
   </si>
 </sst>
 </file>
@@ -2882,7 +2891,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5D3108B-0AC7-45F6-8395-B543209D3234}">
-  <dimension ref="A1:H285"/>
+  <dimension ref="A1:H286"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.6328125" style="17" customWidth="1"/>
@@ -2906,7 +2915,7 @@
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
@@ -2915,10 +2924,10 @@
         <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -2926,7 +2935,7 @@
         <v>7</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>5</v>
@@ -2941,10 +2950,10 @@
         <v>9</v>
       </c>
       <c r="G2" s="18" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="H2" s="18" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -2967,10 +2976,10 @@
         <v>13</v>
       </c>
       <c r="G3" s="18" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="H3" s="18" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -2978,7 +2987,7 @@
         <v>15</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>5</v>
@@ -2993,10 +3002,10 @@
         <v>16</v>
       </c>
       <c r="G4" s="18" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="H4" s="18" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3019,10 +3028,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="18" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="H5" s="18" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3045,10 +3054,10 @@
         <v>13</v>
       </c>
       <c r="G6" s="18" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="H6" s="18" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3071,10 +3080,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="18" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="H7" s="18" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3097,10 +3106,10 @@
         <v>13</v>
       </c>
       <c r="G8" s="18" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="H8" s="18" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3123,10 +3132,10 @@
         <v>13</v>
       </c>
       <c r="G9" s="18" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="H9" s="18" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3149,10 +3158,10 @@
         <v>16</v>
       </c>
       <c r="G10" s="18" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="H10" s="18" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3175,10 +3184,10 @@
         <v>9</v>
       </c>
       <c r="G11" s="18" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="H11" s="18" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3201,10 +3210,10 @@
         <v>9</v>
       </c>
       <c r="G12" s="18" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="H12" s="18" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3227,10 +3236,10 @@
         <v>9</v>
       </c>
       <c r="G13" s="18" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="H13" s="18" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3253,10 +3262,10 @@
         <v>9</v>
       </c>
       <c r="G14" s="18" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="H14" s="18" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3279,10 +3288,10 @@
         <v>9</v>
       </c>
       <c r="G15" s="18" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="H15" s="18" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3305,10 +3314,10 @@
         <v>9</v>
       </c>
       <c r="G16" s="18" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="H16" s="18" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3331,10 +3340,10 @@
         <v>9</v>
       </c>
       <c r="G17" s="18" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="H17" s="18" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3357,10 +3366,10 @@
         <v>13</v>
       </c>
       <c r="G18" s="18" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="H18" s="18" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3383,10 +3392,10 @@
         <v>13</v>
       </c>
       <c r="G19" s="18" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="H19" s="18" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3409,10 +3418,10 @@
         <v>13</v>
       </c>
       <c r="G20" s="18" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="H20" s="18" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3435,10 +3444,10 @@
         <v>13</v>
       </c>
       <c r="G21" s="18" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="H21" s="18" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3461,10 +3470,10 @@
         <v>13</v>
       </c>
       <c r="G22" s="18" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="H22" s="18" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3487,10 +3496,10 @@
         <v>13</v>
       </c>
       <c r="G23" s="18" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="H23" s="18" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3513,10 +3522,10 @@
         <v>13</v>
       </c>
       <c r="G24" s="18" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="H24" s="18" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3539,10 +3548,10 @@
         <v>13</v>
       </c>
       <c r="G25" s="18" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="H25" s="18" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3565,10 +3574,10 @@
         <v>13</v>
       </c>
       <c r="G26" s="18" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="H26" s="18" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3591,10 +3600,10 @@
         <v>13</v>
       </c>
       <c r="G27" s="18" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="H27" s="18" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3617,10 +3626,10 @@
         <v>13</v>
       </c>
       <c r="G28" s="18" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="H28" s="18" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3643,10 +3652,10 @@
         <v>9</v>
       </c>
       <c r="G29" s="18" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="H29" s="18" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3669,10 +3678,10 @@
         <v>9</v>
       </c>
       <c r="G30" s="18" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="H30" s="18" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3695,10 +3704,10 @@
         <v>13</v>
       </c>
       <c r="G31" s="18" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="H31" s="18" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3721,10 +3730,10 @@
         <v>13</v>
       </c>
       <c r="G32" s="18" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="H32" s="18" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3747,10 +3756,10 @@
         <v>13</v>
       </c>
       <c r="G33" s="18" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="H33" s="18" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3773,10 +3782,10 @@
         <v>13</v>
       </c>
       <c r="G34" s="18" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="H34" s="18" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3799,10 +3808,10 @@
         <v>93</v>
       </c>
       <c r="G35" s="18" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="H35" s="18" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3825,10 +3834,10 @@
         <v>93</v>
       </c>
       <c r="G36" s="18" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="H36" s="18" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3851,10 +3860,10 @@
         <v>9</v>
       </c>
       <c r="G37" s="18" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="H37" s="18" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3862,7 +3871,7 @@
         <v>102</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="C38" s="7" t="s">
         <v>21</v>
@@ -3877,10 +3886,10 @@
         <v>9</v>
       </c>
       <c r="G38" s="18" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="H38" s="18" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3888,7 +3897,7 @@
         <v>103</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="C39" s="7" t="s">
         <v>21</v>
@@ -3903,10 +3912,10 @@
         <v>9</v>
       </c>
       <c r="G39" s="18" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="H39" s="18" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3929,10 +3938,10 @@
         <v>13</v>
       </c>
       <c r="G40" s="18" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="H40" s="18" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3940,7 +3949,7 @@
         <v>108</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="C41" s="7" t="s">
         <v>21</v>
@@ -3955,10 +3964,10 @@
         <v>93</v>
       </c>
       <c r="G41" s="18" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="H41" s="18" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3966,7 +3975,7 @@
         <v>110</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="C42" s="7" t="s">
         <v>21</v>
@@ -3981,10 +3990,10 @@
         <v>16</v>
       </c>
       <c r="G42" s="18" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="H42" s="18" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -3992,7 +4001,7 @@
         <v>112</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="C43" s="7" t="s">
         <v>21</v>
@@ -4007,10 +4016,10 @@
         <v>16</v>
       </c>
       <c r="G43" s="18" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="H43" s="18" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -4033,10 +4042,10 @@
         <v>93</v>
       </c>
       <c r="G44" s="18" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="H44" s="18" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -4059,10 +4068,10 @@
         <v>9</v>
       </c>
       <c r="G45" s="18" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="H45" s="18" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -4085,10 +4094,10 @@
         <v>9</v>
       </c>
       <c r="G46" s="18" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="H46" s="18" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -4111,10 +4120,10 @@
         <v>13</v>
       </c>
       <c r="G47" s="18" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="H47" s="18" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -4137,10 +4146,10 @@
         <v>93</v>
       </c>
       <c r="G48" s="18" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="H48" s="18" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -4163,10 +4172,10 @@
         <v>93</v>
       </c>
       <c r="G49" s="18" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="H49" s="18" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -4189,10 +4198,10 @@
         <v>93</v>
       </c>
       <c r="G50" s="18" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="H50" s="18" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -4215,10 +4224,10 @@
         <v>9</v>
       </c>
       <c r="G51" s="18" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="H51" s="18" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -4241,10 +4250,10 @@
         <v>9</v>
       </c>
       <c r="G52" s="18" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="H52" s="18" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -4252,7 +4261,7 @@
         <v>137</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>138</v>
+        <v>792</v>
       </c>
       <c r="C53" s="7" t="s">
         <v>119</v>
@@ -4267,18 +4276,18 @@
         <v>9</v>
       </c>
       <c r="G53" s="18" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="H53" s="18" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A54" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="B54" s="6" t="s">
         <v>139</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>140</v>
       </c>
       <c r="C54" s="7" t="s">
         <v>119</v>
@@ -4293,18 +4302,18 @@
         <v>9</v>
       </c>
       <c r="G54" s="18" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="H54" s="18" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A55" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>142</v>
+        <v>793</v>
       </c>
       <c r="C55" s="7" t="s">
         <v>119</v>
@@ -4319,24 +4328,24 @@
         <v>9</v>
       </c>
       <c r="G55" s="18" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="H55" s="18" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A56" s="5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C56" s="7" t="s">
         <v>119</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E56" s="7" t="s">
         <v>20</v>
@@ -4345,24 +4354,24 @@
         <v>93</v>
       </c>
       <c r="G56" s="18" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="H56" s="18" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A57" s="5" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="C57" s="7" t="s">
         <v>119</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E57" s="7" t="s">
         <v>20</v>
@@ -4371,24 +4380,24 @@
         <v>93</v>
       </c>
       <c r="G57" s="18" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="H57" s="18" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A58" s="5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C58" s="7" t="s">
         <v>119</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E58" s="7" t="s">
         <v>20</v>
@@ -4397,24 +4406,24 @@
         <v>93</v>
       </c>
       <c r="G58" s="18" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="H58" s="18" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A59" s="5" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C59" s="7" t="s">
         <v>119</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E59" s="7" t="s">
         <v>20</v>
@@ -4423,24 +4432,24 @@
         <v>93</v>
       </c>
       <c r="G59" s="18" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="H59" s="18" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A60" s="5" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C60" s="7" t="s">
         <v>119</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E60" s="7" t="s">
         <v>20</v>
@@ -4449,24 +4458,24 @@
         <v>16</v>
       </c>
       <c r="G60" s="18" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="H60" s="18" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A61" s="5" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C61" s="7" t="s">
         <v>119</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E61" s="7" t="s">
         <v>20</v>
@@ -4475,24 +4484,24 @@
         <v>93</v>
       </c>
       <c r="G61" s="18" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="H61" s="18" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A62" s="5" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C62" s="7" t="s">
         <v>119</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E62" s="7" t="s">
         <v>20</v>
@@ -4501,24 +4510,24 @@
         <v>13</v>
       </c>
       <c r="G62" s="18" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="H62" s="18" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A63" s="5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C63" s="7" t="s">
         <v>119</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E63" s="7" t="s">
         <v>20</v>
@@ -4527,24 +4536,24 @@
         <v>93</v>
       </c>
       <c r="G63" s="18" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="H63" s="18" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A64" s="5" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C64" s="7" t="s">
         <v>119</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E64" s="7" t="s">
         <v>20</v>
@@ -4553,24 +4562,24 @@
         <v>9</v>
       </c>
       <c r="G64" s="18" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="H64" s="18" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A65" s="5" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C65" s="7" t="s">
         <v>119</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E65" s="7" t="s">
         <v>20</v>
@@ -4579,24 +4588,24 @@
         <v>93</v>
       </c>
       <c r="G65" s="18" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="H65" s="18" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A66" s="5" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E66" s="7" t="s">
         <v>20</v>
@@ -4605,24 +4614,24 @@
         <v>13</v>
       </c>
       <c r="G66" s="18" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="H66" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A67" s="5" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E67" s="7" t="s">
         <v>20</v>
@@ -4631,24 +4640,24 @@
         <v>13</v>
       </c>
       <c r="G67" s="18" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="H67" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A68" s="5" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E68" s="7" t="s">
         <v>20</v>
@@ -4657,24 +4666,24 @@
         <v>13</v>
       </c>
       <c r="G68" s="18" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="H68" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A69" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E69" s="7" t="s">
         <v>20</v>
@@ -4683,24 +4692,24 @@
         <v>13</v>
       </c>
       <c r="G69" s="18" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="H69" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A70" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E70" s="7" t="s">
         <v>20</v>
@@ -4709,24 +4718,24 @@
         <v>16</v>
       </c>
       <c r="G70" s="18" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="H70" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A71" s="5" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E71" s="7" t="s">
         <v>20</v>
@@ -4735,24 +4744,24 @@
         <v>93</v>
       </c>
       <c r="G71" s="18" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="H71" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="72" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A72" s="5" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E72" s="7" t="s">
         <v>20</v>
@@ -4761,24 +4770,24 @@
         <v>93</v>
       </c>
       <c r="G72" s="18" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="H72" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A73" s="5" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E73" s="7" t="s">
         <v>20</v>
@@ -4787,24 +4796,24 @@
         <v>93</v>
       </c>
       <c r="G73" s="18" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="H73" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A74" s="5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E74" s="7" t="s">
         <v>20</v>
@@ -4813,24 +4822,24 @@
         <v>9</v>
       </c>
       <c r="G74" s="18" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="H74" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A75" s="5" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E75" s="7" t="s">
         <v>20</v>
@@ -4839,24 +4848,24 @@
         <v>9</v>
       </c>
       <c r="G75" s="18" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="H75" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A76" s="5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E76" s="7" t="s">
         <v>20</v>
@@ -4865,24 +4874,24 @@
         <v>9</v>
       </c>
       <c r="G76" s="18" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="H76" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A77" s="5" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E77" s="7" t="s">
         <v>20</v>
@@ -4891,24 +4900,24 @@
         <v>9</v>
       </c>
       <c r="G77" s="18" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="H77" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="78" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A78" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E78" s="7" t="s">
         <v>20</v>
@@ -4917,24 +4926,24 @@
         <v>9</v>
       </c>
       <c r="G78" s="18" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="H78" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="79" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A79" s="5" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E79" s="7" t="s">
         <v>20</v>
@@ -4943,24 +4952,24 @@
         <v>9</v>
       </c>
       <c r="G79" s="18" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="H79" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="80" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A80" s="5" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E80" s="7" t="s">
         <v>20</v>
@@ -4969,24 +4978,24 @@
         <v>9</v>
       </c>
       <c r="G80" s="18" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="H80" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="81" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A81" s="5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E81" s="7" t="s">
         <v>20</v>
@@ -4995,24 +5004,24 @@
         <v>13</v>
       </c>
       <c r="G81" s="18" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="H81" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="82" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A82" s="5" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E82" s="7" t="s">
         <v>20</v>
@@ -5021,24 +5030,24 @@
         <v>13</v>
       </c>
       <c r="G82" s="18" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="H82" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="83" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A83" s="5" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E83" s="7" t="s">
         <v>20</v>
@@ -5047,24 +5056,24 @@
         <v>13</v>
       </c>
       <c r="G83" s="18" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="H83" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="84" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A84" s="9" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B84" s="10" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E84" s="11" t="s">
         <v>20</v>
@@ -5073,24 +5082,24 @@
         <v>9</v>
       </c>
       <c r="G84" s="18" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="H84" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="85" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A85" s="5" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E85" s="7" t="s">
         <v>20</v>
@@ -5099,24 +5108,24 @@
         <v>93</v>
       </c>
       <c r="G85" s="18" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="H85" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="86" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A86" s="5" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E86" s="7" t="s">
         <v>20</v>
@@ -5125,24 +5134,24 @@
         <v>93</v>
       </c>
       <c r="G86" s="18" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="H86" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="87" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A87" s="5" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E87" s="7" t="s">
         <v>20</v>
@@ -5151,24 +5160,24 @@
         <v>9</v>
       </c>
       <c r="G87" s="18" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="H87" s="18" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="88" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A88" s="5" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E88" s="7" t="s">
         <v>20</v>
@@ -5177,24 +5186,24 @@
         <v>9</v>
       </c>
       <c r="G88" s="18" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="H88" s="18" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="89" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A89" s="9" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B89" s="10" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E89" s="11" t="s">
         <v>20</v>
@@ -5203,24 +5212,24 @@
         <v>93</v>
       </c>
       <c r="G89" s="18" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="H89" s="18" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="90" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A90" s="5" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E90" s="7" t="s">
         <v>20</v>
@@ -5229,24 +5238,24 @@
         <v>9</v>
       </c>
       <c r="G90" s="18" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="H90" s="18" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="91" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A91" s="5" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E91" s="7" t="s">
         <v>20</v>
@@ -5255,24 +5264,24 @@
         <v>16</v>
       </c>
       <c r="G91" s="18" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="H91" s="18" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="92" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A92" s="5" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D92" s="12" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E92" s="7" t="s">
         <v>20</v>
@@ -5281,24 +5290,24 @@
         <v>9</v>
       </c>
       <c r="G92" s="18" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="H92" s="18" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="93" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A93" s="5" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D93" s="12" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E93" s="7" t="s">
         <v>20</v>
@@ -5307,24 +5316,24 @@
         <v>9</v>
       </c>
       <c r="G93" s="18" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="H93" s="18" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="94" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A94" s="5" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E94" s="7" t="s">
         <v>20</v>
@@ -5333,24 +5342,24 @@
         <v>9</v>
       </c>
       <c r="G94" s="18" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="H94" s="18" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="95" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A95" s="5" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E95" s="7" t="s">
         <v>20</v>
@@ -5359,24 +5368,24 @@
         <v>9</v>
       </c>
       <c r="G95" s="18" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="H95" s="18" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="96" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A96" s="5" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E96" s="7" t="s">
         <v>20</v>
@@ -5385,24 +5394,24 @@
         <v>9</v>
       </c>
       <c r="G96" s="18" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="H96" s="18" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="97" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A97" s="5" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E97" s="7" t="s">
         <v>20</v>
@@ -5411,24 +5420,24 @@
         <v>9</v>
       </c>
       <c r="G97" s="18" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="H97" s="18" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="98" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A98" s="5" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E98" s="7" t="s">
         <v>20</v>
@@ -5437,24 +5446,24 @@
         <v>9</v>
       </c>
       <c r="G98" s="18" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="H98" s="18" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="99" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A99" s="5" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E99" s="7" t="s">
         <v>20</v>
@@ -5463,24 +5472,24 @@
         <v>93</v>
       </c>
       <c r="G99" s="18" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="H99" s="18" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="100" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A100" s="5" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E100" s="7" t="s">
         <v>20</v>
@@ -5489,24 +5498,24 @@
         <v>93</v>
       </c>
       <c r="G100" s="18" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="H100" s="18" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="101" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A101" s="5" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D101" s="5" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E101" s="7" t="s">
         <v>20</v>
@@ -5515,24 +5524,24 @@
         <v>9</v>
       </c>
       <c r="G101" s="18" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="H101" s="18" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="102" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A102" s="5" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C102" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D102" s="5" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E102" s="7" t="s">
         <v>20</v>
@@ -5541,24 +5550,24 @@
         <v>9</v>
       </c>
       <c r="G102" s="18" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="H102" s="18" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="103" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A103" s="5" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D103" s="12" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E103" s="7" t="s">
         <v>20</v>
@@ -5567,24 +5576,24 @@
         <v>13</v>
       </c>
       <c r="G103" s="18" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="H103" s="18" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="104" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A104" s="5" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D104" s="12" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E104" s="7" t="s">
         <v>20</v>
@@ -5593,24 +5602,24 @@
         <v>13</v>
       </c>
       <c r="G104" s="18" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="H104" s="18" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="105" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A105" s="5" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C105" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D105" s="12" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E105" s="7" t="s">
         <v>20</v>
@@ -5619,24 +5628,24 @@
         <v>13</v>
       </c>
       <c r="G105" s="18" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="H105" s="18" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="106" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A106" s="5" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D106" s="12" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E106" s="7" t="s">
         <v>20</v>
@@ -5645,24 +5654,24 @@
         <v>13</v>
       </c>
       <c r="G106" s="18" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="H106" s="18" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="107" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A107" s="5" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C107" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D107" s="5" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E107" s="7" t="s">
         <v>20</v>
@@ -5671,24 +5680,24 @@
         <v>9</v>
       </c>
       <c r="G107" s="18" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="H107" s="18" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="108" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A108" s="5" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C108" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D108" s="5" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E108" s="7" t="s">
         <v>20</v>
@@ -5697,24 +5706,24 @@
         <v>9</v>
       </c>
       <c r="G108" s="18" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="H108" s="18" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="109" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A109" s="5" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C109" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D109" s="5" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E109" s="7" t="s">
         <v>20</v>
@@ -5723,24 +5732,24 @@
         <v>9</v>
       </c>
       <c r="G109" s="18" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="H109" s="18" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="110" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A110" s="5" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C110" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D110" s="5" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E110" s="7" t="s">
         <v>20</v>
@@ -5749,24 +5758,24 @@
         <v>9</v>
       </c>
       <c r="G110" s="18" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="H110" s="18" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="111" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A111" s="5" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C111" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D111" s="5" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="E111" s="7" t="s">
         <v>20</v>
@@ -5775,24 +5784,24 @@
         <v>9</v>
       </c>
       <c r="G111" s="18" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="H111" s="18" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="112" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A112" s="5" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C112" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D112" s="5" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E112" s="7" t="s">
         <v>20</v>
@@ -5801,24 +5810,24 @@
         <v>13</v>
       </c>
       <c r="G112" s="18" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="H112" s="18" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="113" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A113" s="5" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C113" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E113" s="7" t="s">
         <v>20</v>
@@ -5827,24 +5836,24 @@
         <v>13</v>
       </c>
       <c r="G113" s="18" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="H113" s="18" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="114" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A114" s="5" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C114" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D114" s="5" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E114" s="7" t="s">
         <v>20</v>
@@ -5853,24 +5862,24 @@
         <v>13</v>
       </c>
       <c r="G114" s="18" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="H114" s="18" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="115" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A115" s="5" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C115" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E115" s="7" t="s">
         <v>20</v>
@@ -5879,24 +5888,24 @@
         <v>13</v>
       </c>
       <c r="G115" s="18" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="H115" s="18" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="116" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A116" s="5" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C116" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D116" s="5" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E116" s="7" t="s">
         <v>20</v>
@@ -5905,24 +5914,24 @@
         <v>13</v>
       </c>
       <c r="G116" s="18" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="H116" s="18" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="117" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A117" s="5" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C117" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D117" s="5" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="E117" s="7" t="s">
         <v>20</v>
@@ -5931,50 +5940,50 @@
         <v>9</v>
       </c>
       <c r="G117" s="18" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="H117" s="18" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="118" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A118" s="5" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C118" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D118" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="E118" s="7" t="s">
         <v>300</v>
-      </c>
-      <c r="E118" s="7" t="s">
-        <v>302</v>
       </c>
       <c r="F118" s="7" t="s">
         <v>16</v>
       </c>
       <c r="G118" s="18" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="H118" s="18" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="119" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A119" s="5" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C119" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="E119" s="7" t="s">
         <v>20</v>
@@ -5983,24 +5992,24 @@
         <v>13</v>
       </c>
       <c r="G119" s="18" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="H119" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="120" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A120" s="5" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C120" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D120" s="5" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E120" s="7" t="s">
         <v>20</v>
@@ -6009,102 +6018,102 @@
         <v>9</v>
       </c>
       <c r="G120" s="18" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="H120" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="121" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A121" s="5" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="C121" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="E121" s="7" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F121" s="7" t="s">
         <v>93</v>
       </c>
       <c r="G121" s="18" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="H121" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="122" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A122" s="5" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="C122" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D122" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E122" s="7" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F122" s="7" t="s">
         <v>9</v>
       </c>
       <c r="G122" s="18" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="H122" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="123" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A123" s="5" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="C123" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E123" s="7" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F123" s="7" t="s">
         <v>16</v>
       </c>
       <c r="G123" s="18" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="H123" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="124" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A124" s="5" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="C124" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D124" s="5" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E124" s="7" t="s">
         <v>20</v>
@@ -6113,232 +6122,232 @@
         <v>16</v>
       </c>
       <c r="G124" s="18" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="H124" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="125" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A125" s="5" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="C125" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E125" s="7" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F125" s="7" t="s">
         <v>9</v>
       </c>
       <c r="G125" s="18" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="H125" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="126" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A126" s="5" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="C126" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E126" s="7" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F126" s="7" t="s">
         <v>9</v>
       </c>
       <c r="G126" s="18" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="H126" s="18" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="127" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A127" s="5" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B127" s="6" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="C127" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E127" s="7" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F127" s="7" t="s">
         <v>16</v>
       </c>
       <c r="G127" s="18" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="H127" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="128" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A128" s="5" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="C128" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D128" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="E128" s="7" t="s">
         <v>322</v>
-      </c>
-      <c r="E128" s="7" t="s">
-        <v>324</v>
       </c>
       <c r="F128" s="7" t="s">
         <v>16</v>
       </c>
       <c r="G128" s="18" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="H128" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="129" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A129" s="5" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="C129" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E129" s="7" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F129" s="7" t="s">
         <v>16</v>
       </c>
       <c r="G129" s="18" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="H129" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="130" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A130" s="5" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="C130" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E130" s="7" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F130" s="7" t="s">
         <v>13</v>
       </c>
       <c r="G130" s="18" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="H130" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="131" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A131" s="5" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="C131" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E131" s="7" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="F131" s="7" t="s">
         <v>16</v>
       </c>
       <c r="G131" s="18" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="H131" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="132" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A132" s="5" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="C132" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D132" s="5" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E132" s="7" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="F132" s="7" t="s">
         <v>16</v>
       </c>
       <c r="G132" s="18" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="H132" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="133" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A133" s="5" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C133" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D133" s="5" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E133" s="7" t="s">
         <v>20</v>
@@ -6347,24 +6356,24 @@
         <v>16</v>
       </c>
       <c r="G133" s="18" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="H133" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="134" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A134" s="5" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C134" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E134" s="7" t="s">
         <v>20</v>
@@ -6373,76 +6382,76 @@
         <v>93</v>
       </c>
       <c r="G134" s="18" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="H134" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="135" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A135" s="5" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="C135" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E135" s="7" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="F135" s="7" t="s">
         <v>16</v>
       </c>
       <c r="G135" s="18" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="H135" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="136" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A136" s="5" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="C136" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="E136" s="7" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F136" s="7" t="s">
         <v>93</v>
       </c>
       <c r="G136" s="18" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="H136" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="137" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A137" s="5" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B137" s="6" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C137" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E137" s="7" t="s">
         <v>20</v>
@@ -6451,24 +6460,24 @@
         <v>93</v>
       </c>
       <c r="G137" s="18" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="H137" s="18" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
     </row>
     <row r="138" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A138" s="5" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B138" s="6" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C138" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D138" s="5" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E138" s="7" t="s">
         <v>20</v>
@@ -6477,24 +6486,24 @@
         <v>93</v>
       </c>
       <c r="G138" s="18" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="H138" s="18" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
     </row>
     <row r="139" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A139" s="5" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B139" s="6" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C139" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E139" s="7" t="s">
         <v>20</v>
@@ -6503,24 +6512,24 @@
         <v>9</v>
       </c>
       <c r="G139" s="18" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="H139" s="18" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
     </row>
     <row r="140" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A140" s="5" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B140" s="6" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C140" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D140" s="5" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E140" s="7" t="s">
         <v>20</v>
@@ -6529,24 +6538,24 @@
         <v>13</v>
       </c>
       <c r="G140" s="18" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="H140" s="18" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
     </row>
     <row r="141" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A141" s="5" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B141" s="6" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C141" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D141" s="5" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E141" s="7" t="s">
         <v>20</v>
@@ -6555,24 +6564,24 @@
         <v>13</v>
       </c>
       <c r="G141" s="18" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="H141" s="18" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
     </row>
     <row r="142" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A142" s="5" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B142" s="6" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C142" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D142" s="5" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E142" s="7" t="s">
         <v>20</v>
@@ -6581,24 +6590,24 @@
         <v>13</v>
       </c>
       <c r="G142" s="18" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="H142" s="18" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
     </row>
     <row r="143" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A143" s="5" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B143" s="6" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C143" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D143" s="5" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E143" s="7" t="s">
         <v>20</v>
@@ -6607,24 +6616,24 @@
         <v>13</v>
       </c>
       <c r="G143" s="18" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="H143" s="18" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
     </row>
     <row r="144" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A144" s="5" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B144" s="6" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C144" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D144" s="5" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E144" s="7" t="s">
         <v>20</v>
@@ -6633,24 +6642,24 @@
         <v>13</v>
       </c>
       <c r="G144" s="18" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="H144" s="18" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
     </row>
     <row r="145" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A145" s="5" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B145" s="6" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C145" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D145" s="5" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E145" s="7" t="s">
         <v>20</v>
@@ -6659,24 +6668,24 @@
         <v>13</v>
       </c>
       <c r="G145" s="18" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="H145" s="18" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
     </row>
     <row r="146" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A146" s="5" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B146" s="6" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C146" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D146" s="5" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E146" s="7" t="s">
         <v>20</v>
@@ -6685,24 +6694,24 @@
         <v>13</v>
       </c>
       <c r="G146" s="18" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="H146" s="18" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
     </row>
     <row r="147" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A147" s="5" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B147" s="6" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="C147" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D147" s="5" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E147" s="7" t="s">
         <v>20</v>
@@ -6711,24 +6720,24 @@
         <v>13</v>
       </c>
       <c r="G147" s="18" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="H147" s="18" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
     </row>
     <row r="148" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A148" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B148" s="6" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C148" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D148" s="5" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E148" s="7" t="s">
         <v>20</v>
@@ -6737,24 +6746,24 @@
         <v>13</v>
       </c>
       <c r="G148" s="18" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="H148" s="18" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
     </row>
     <row r="149" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A149" s="5" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B149" s="6" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C149" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D149" s="5" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="E149" s="7" t="s">
         <v>20</v>
@@ -6763,24 +6772,24 @@
         <v>9</v>
       </c>
       <c r="G149" s="18" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="H149" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="150" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A150" s="5" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B150" s="6" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C150" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D150" s="5" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="E150" s="7" t="s">
         <v>20</v>
@@ -6789,24 +6798,24 @@
         <v>9</v>
       </c>
       <c r="G150" s="18" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="H150" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="151" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A151" s="5" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B151" s="6" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="C151" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D151" s="5" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="E151" s="7" t="s">
         <v>8</v>
@@ -6815,24 +6824,24 @@
         <v>16</v>
       </c>
       <c r="G151" s="18" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="H151" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="152" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A152" s="5" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B152" s="6" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C152" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D152" s="5" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="E152" s="7" t="s">
         <v>20</v>
@@ -6841,24 +6850,24 @@
         <v>93</v>
       </c>
       <c r="G152" s="18" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="H152" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="153" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A153" s="5" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B153" s="6" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C153" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D153" s="5" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="E153" s="7" t="s">
         <v>20</v>
@@ -6867,24 +6876,24 @@
         <v>93</v>
       </c>
       <c r="G153" s="18" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="H153" s="18" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
     </row>
     <row r="154" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A154" s="5" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B154" s="6" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C154" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D154" s="5" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E154" s="7" t="s">
         <v>20</v>
@@ -6893,24 +6902,24 @@
         <v>9</v>
       </c>
       <c r="G154" s="18" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="H154" s="18" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
     </row>
     <row r="155" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A155" s="5" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B155" s="6" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C155" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="E155" s="7" t="s">
         <v>20</v>
@@ -6919,24 +6928,24 @@
         <v>16</v>
       </c>
       <c r="G155" s="18" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="H155" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="156" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A156" s="5" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B156" s="6" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="C156" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="E156" s="7" t="s">
         <v>100</v>
@@ -6945,24 +6954,24 @@
         <v>16</v>
       </c>
       <c r="G156" s="18" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="H156" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="157" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A157" s="5" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B157" s="6" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C157" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="E157" s="7" t="s">
         <v>20</v>
@@ -6971,24 +6980,24 @@
         <v>16</v>
       </c>
       <c r="G157" s="18" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="H157" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="158" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A158" s="5" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B158" s="6" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C158" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D158" s="5" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E158" s="7" t="s">
         <v>20</v>
@@ -6997,24 +7006,24 @@
         <v>9</v>
       </c>
       <c r="G158" s="18" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="H158" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="159" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A159" s="5" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B159" s="6" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C159" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E159" s="7" t="s">
         <v>20</v>
@@ -7023,24 +7032,24 @@
         <v>13</v>
       </c>
       <c r="G159" s="18" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="H159" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="160" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A160" s="5" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B160" s="6" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C160" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D160" s="5" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E160" s="7" t="s">
         <v>20</v>
@@ -7049,24 +7058,24 @@
         <v>13</v>
       </c>
       <c r="G160" s="18" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="H160" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="161" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A161" s="5" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B161" s="6" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C161" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D161" s="5" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E161" s="7" t="s">
         <v>20</v>
@@ -7075,24 +7084,24 @@
         <v>13</v>
       </c>
       <c r="G161" s="18" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="H161" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="162" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A162" s="5" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B162" s="6" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C162" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D162" s="5" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E162" s="7" t="s">
         <v>20</v>
@@ -7101,24 +7110,24 @@
         <v>13</v>
       </c>
       <c r="G162" s="18" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="H162" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="163" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A163" s="5" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B163" s="6" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="C163" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D163" s="5" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E163" s="7" t="s">
         <v>20</v>
@@ -7127,24 +7136,24 @@
         <v>13</v>
       </c>
       <c r="G163" s="18" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="H163" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="164" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A164" s="5" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B164" s="6" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C164" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D164" s="5" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E164" s="7" t="s">
         <v>8</v>
@@ -7153,24 +7162,24 @@
         <v>13</v>
       </c>
       <c r="G164" s="18" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="H164" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="165" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A165" s="5" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B165" s="6" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="C165" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D165" s="5" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="E165" s="7" t="s">
         <v>8</v>
@@ -7179,24 +7188,24 @@
         <v>93</v>
       </c>
       <c r="G165" s="18" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="H165" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="166" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A166" s="5" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B166" s="6" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C166" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D166" s="5" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="E166" s="7" t="s">
         <v>20</v>
@@ -7205,24 +7214,24 @@
         <v>13</v>
       </c>
       <c r="G166" s="18" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="H166" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="167" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A167" s="5" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B167" s="6" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C167" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D167" s="5" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="E167" s="7" t="s">
         <v>20</v>
@@ -7231,24 +7240,24 @@
         <v>13</v>
       </c>
       <c r="G167" s="18" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="H167" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="168" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A168" s="5" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B168" s="6" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C168" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D168" s="5" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="E168" s="7" t="s">
         <v>20</v>
@@ -7257,24 +7266,24 @@
         <v>13</v>
       </c>
       <c r="G168" s="18" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="H168" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="169" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A169" s="5" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B169" s="6" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C169" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D169" s="5" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="E169" s="7" t="s">
         <v>20</v>
@@ -7283,24 +7292,24 @@
         <v>13</v>
       </c>
       <c r="G169" s="18" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="H169" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="170" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A170" s="5" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B170" s="6" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C170" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D170" s="5" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="E170" s="7" t="s">
         <v>20</v>
@@ -7309,24 +7318,24 @@
         <v>13</v>
       </c>
       <c r="G170" s="18" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="H170" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="171" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A171" s="5" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B171" s="6" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C171" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D171" s="5" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="E171" s="7" t="s">
         <v>100</v>
@@ -7335,24 +7344,24 @@
         <v>93</v>
       </c>
       <c r="G171" s="18" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="H171" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="172" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A172" s="5" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B172" s="6" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C172" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D172" s="5" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="E172" s="7" t="s">
         <v>100</v>
@@ -7361,24 +7370,24 @@
         <v>93</v>
       </c>
       <c r="G172" s="18" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="H172" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="173" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A173" s="5" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B173" s="6" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C173" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D173" s="5" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="E173" s="7" t="s">
         <v>100</v>
@@ -7387,24 +7396,24 @@
         <v>93</v>
       </c>
       <c r="G173" s="18" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="H173" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="174" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A174" s="5" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B174" s="6" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C174" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D174" s="5" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="E174" s="7" t="s">
         <v>100</v>
@@ -7413,24 +7422,24 @@
         <v>93</v>
       </c>
       <c r="G174" s="18" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="H174" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="175" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A175" s="5" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B175" s="6" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C175" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D175" s="5" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="E175" s="7" t="s">
         <v>100</v>
@@ -7439,24 +7448,24 @@
         <v>93</v>
       </c>
       <c r="G175" s="18" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="H175" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="176" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A176" s="5" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B176" s="6" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="C176" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D176" s="5" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="E176" s="7" t="s">
         <v>100</v>
@@ -7465,24 +7474,24 @@
         <v>93</v>
       </c>
       <c r="G176" s="18" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="H176" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="177" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A177" s="5" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B177" s="6" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="C177" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D177" s="5" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="E177" s="7" t="s">
         <v>100</v>
@@ -7491,24 +7500,24 @@
         <v>93</v>
       </c>
       <c r="G177" s="18" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="H177" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="178" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A178" s="5" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B178" s="6" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C178" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D178" s="5" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="E178" s="7" t="s">
         <v>20</v>
@@ -7517,24 +7526,24 @@
         <v>9</v>
       </c>
       <c r="G178" s="18" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="H178" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="179" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A179" s="5" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B179" s="6" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="C179" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D179" s="5" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="E179" s="7" t="s">
         <v>20</v>
@@ -7543,24 +7552,24 @@
         <v>9</v>
       </c>
       <c r="G179" s="18" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="H179" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="180" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A180" s="5" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B180" s="6" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C180" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D180" s="5" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E180" s="7" t="s">
         <v>20</v>
@@ -7569,24 +7578,24 @@
         <v>9</v>
       </c>
       <c r="G180" s="18" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="H180" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="181" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A181" s="5" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B181" s="6" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C181" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D181" s="5" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E181" s="7" t="s">
         <v>20</v>
@@ -7595,24 +7604,24 @@
         <v>9</v>
       </c>
       <c r="G181" s="18" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="H181" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="182" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A182" s="5" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B182" s="6" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C182" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D182" s="5" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E182" s="7" t="s">
         <v>20</v>
@@ -7621,24 +7630,24 @@
         <v>13</v>
       </c>
       <c r="G182" s="18" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="H182" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="183" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A183" s="5" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B183" s="6" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C183" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D183" s="5" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E183" s="7" t="s">
         <v>20</v>
@@ -7647,24 +7656,24 @@
         <v>13</v>
       </c>
       <c r="G183" s="18" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="H183" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="184" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A184" s="5" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B184" s="6" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C184" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D184" s="5" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E184" s="7" t="s">
         <v>20</v>
@@ -7673,50 +7682,50 @@
         <v>13</v>
       </c>
       <c r="G184" s="18" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="H184" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="185" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A185" s="5" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B185" s="6" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="C185" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D185" s="5" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E185" s="7" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F185" s="7" t="s">
         <v>13</v>
       </c>
       <c r="G185" s="18" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="H185" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="186" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A186" s="5" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B186" s="6" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C186" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D186" s="5" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E186" s="7" t="s">
         <v>20</v>
@@ -7725,24 +7734,24 @@
         <v>13</v>
       </c>
       <c r="G186" s="18" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="H186" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="187" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A187" s="5" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B187" s="6" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="C187" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D187" s="5" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E187" s="7" t="s">
         <v>20</v>
@@ -7751,24 +7760,24 @@
         <v>13</v>
       </c>
       <c r="G187" s="18" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="H187" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="188" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A188" s="5" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B188" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C188" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D188" s="5" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E188" s="7" t="s">
         <v>20</v>
@@ -7777,24 +7786,24 @@
         <v>93</v>
       </c>
       <c r="G188" s="18" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="H188" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="189" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A189" s="5" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B189" s="6" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C189" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D189" s="5" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="E189" s="7" t="s">
         <v>20</v>
@@ -7803,24 +7812,24 @@
         <v>9</v>
       </c>
       <c r="G189" s="18" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="H189" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="190" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A190" s="5" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B190" s="6" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C190" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D190" s="5" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="E190" s="7" t="s">
         <v>20</v>
@@ -7829,24 +7838,24 @@
         <v>9</v>
       </c>
       <c r="G190" s="18" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="H190" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="191" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A191" s="5" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B191" s="6" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C191" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D191" s="5" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="E191" s="7" t="s">
         <v>20</v>
@@ -7855,24 +7864,24 @@
         <v>9</v>
       </c>
       <c r="G191" s="18" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="H191" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="192" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A192" s="5" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B192" s="6" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="C192" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D192" s="5" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="E192" s="7" t="s">
         <v>20</v>
@@ -7881,24 +7890,24 @@
         <v>9</v>
       </c>
       <c r="G192" s="18" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="H192" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="193" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A193" s="5" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B193" s="6" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C193" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D193" s="5" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E193" s="7" t="s">
         <v>20</v>
@@ -7907,24 +7916,24 @@
         <v>16</v>
       </c>
       <c r="G193" s="18" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="H193" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="194" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A194" s="5" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B194" s="6" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C194" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D194" s="5" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E194" s="7" t="s">
         <v>20</v>
@@ -7933,24 +7942,24 @@
         <v>16</v>
       </c>
       <c r="G194" s="18" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="H194" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="195" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A195" s="5" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B195" s="6" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C195" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D195" s="5" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="E195" s="7" t="s">
         <v>20</v>
@@ -7959,24 +7968,24 @@
         <v>9</v>
       </c>
       <c r="G195" s="18" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="H195" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="196" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A196" s="5" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B196" s="6" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C196" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D196" s="5" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="E196" s="7" t="s">
         <v>20</v>
@@ -7985,24 +7994,24 @@
         <v>9</v>
       </c>
       <c r="G196" s="18" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="H196" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="197" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A197" s="5" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B197" s="6" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C197" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D197" s="5" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="E197" s="7" t="s">
         <v>20</v>
@@ -8011,24 +8020,24 @@
         <v>9</v>
       </c>
       <c r="G197" s="18" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="H197" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="198" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A198" s="5" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="B198" s="6" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C198" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D198" s="5" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="E198" s="7" t="s">
         <v>20</v>
@@ -8037,24 +8046,24 @@
         <v>93</v>
       </c>
       <c r="G198" s="18" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="H198" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="199" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A199" s="5" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B199" s="6" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C199" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D199" s="5" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="E199" s="7" t="s">
         <v>20</v>
@@ -8063,24 +8072,24 @@
         <v>9</v>
       </c>
       <c r="G199" s="18" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="H199" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="200" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A200" s="5" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B200" s="6" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C200" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D200" s="5" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="E200" s="7" t="s">
         <v>20</v>
@@ -8089,24 +8098,24 @@
         <v>9</v>
       </c>
       <c r="G200" s="18" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="H200" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="201" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A201" s="5" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B201" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C201" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D201" s="5" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="E201" s="7" t="s">
         <v>20</v>
@@ -8115,24 +8124,24 @@
         <v>9</v>
       </c>
       <c r="G201" s="18" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="H201" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="202" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A202" s="5" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B202" s="6" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="C202" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D202" s="5" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="E202" s="7" t="s">
         <v>20</v>
@@ -8141,24 +8150,24 @@
         <v>9</v>
       </c>
       <c r="G202" s="18" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="H202" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="203" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A203" s="5" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B203" s="6" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C203" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D203" s="5" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E203" s="7" t="s">
         <v>20</v>
@@ -8167,24 +8176,24 @@
         <v>93</v>
       </c>
       <c r="G203" s="18" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="H203" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="204" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A204" s="5" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B204" s="6" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="C204" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D204" s="5" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E204" s="7" t="s">
         <v>8</v>
@@ -8193,50 +8202,50 @@
         <v>93</v>
       </c>
       <c r="G204" s="18" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="H204" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="205" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A205" s="5" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B205" s="6" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="C205" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D205" s="5" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E205" s="7" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F205" s="7" t="s">
         <v>93</v>
       </c>
       <c r="G205" s="18" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="H205" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="206" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A206" s="5" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B206" s="6" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C206" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D206" s="5" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="E206" s="7" t="s">
         <v>20</v>
@@ -8245,24 +8254,24 @@
         <v>9</v>
       </c>
       <c r="G206" s="18" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="H206" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="207" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A207" s="5" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B207" s="6" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C207" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D207" s="5" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="E207" s="7" t="s">
         <v>20</v>
@@ -8271,24 +8280,24 @@
         <v>93</v>
       </c>
       <c r="G207" s="18" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="H207" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="208" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A208" s="5" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="B208" s="6" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C208" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D208" s="5" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="E208" s="7" t="s">
         <v>20</v>
@@ -8297,24 +8306,24 @@
         <v>93</v>
       </c>
       <c r="G208" s="18" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="H208" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="209" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A209" s="5" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B209" s="6" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C209" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D209" s="5" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="E209" s="7" t="s">
         <v>20</v>
@@ -8323,24 +8332,24 @@
         <v>93</v>
       </c>
       <c r="G209" s="18" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="H209" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="210" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A210" s="5" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="B210" s="6" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="C210" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D210" s="5" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="E210" s="7" t="s">
         <v>100</v>
@@ -8349,24 +8358,24 @@
         <v>93</v>
       </c>
       <c r="G210" s="18" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="H210" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="211" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A211" s="5" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B211" s="6" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C211" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D211" s="5" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="E211" s="7" t="s">
         <v>20</v>
@@ -8375,24 +8384,24 @@
         <v>93</v>
       </c>
       <c r="G211" s="18" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="H211" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="212" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A212" s="5" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="B212" s="6" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C212" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D212" s="5" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="E212" s="7" t="s">
         <v>20</v>
@@ -8401,24 +8410,24 @@
         <v>9</v>
       </c>
       <c r="G212" s="18" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="H212" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="213" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A213" s="5" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="B213" s="6" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C213" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D213" s="5" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="E213" s="7" t="s">
         <v>20</v>
@@ -8427,24 +8436,24 @@
         <v>9</v>
       </c>
       <c r="G213" s="18" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="H213" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="214" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A214" s="5" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B214" s="6" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="C214" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D214" s="5" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="E214" s="7" t="s">
         <v>8</v>
@@ -8453,24 +8462,24 @@
         <v>16</v>
       </c>
       <c r="G214" s="18" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="H214" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="215" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A215" s="5" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B215" s="6" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C215" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D215" s="5" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="E215" s="7" t="s">
         <v>20</v>
@@ -8479,24 +8488,24 @@
         <v>13</v>
       </c>
       <c r="G215" s="18" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="H215" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="216" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A216" s="5" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="B216" s="6" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C216" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D216" s="5" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="E216" s="7" t="s">
         <v>20</v>
@@ -8505,24 +8514,24 @@
         <v>13</v>
       </c>
       <c r="G216" s="18" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="H216" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="217" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A217" s="5" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="B217" s="6" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C217" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D217" s="5" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="E217" s="7" t="s">
         <v>20</v>
@@ -8531,24 +8540,24 @@
         <v>9</v>
       </c>
       <c r="G217" s="18" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="H217" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="218" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A218" s="5" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="B218" s="6" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="C218" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D218" s="5" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="E218" s="7" t="s">
         <v>20</v>
@@ -8557,24 +8566,24 @@
         <v>93</v>
       </c>
       <c r="G218" s="18" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="H218" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="219" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A219" s="5" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B219" s="6" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C219" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D219" s="5" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="E219" s="7" t="s">
         <v>20</v>
@@ -8583,24 +8592,24 @@
         <v>9</v>
       </c>
       <c r="G219" s="18" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="H219" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="220" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A220" s="5" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="B220" s="6" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C220" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D220" s="5" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="E220" s="7" t="s">
         <v>20</v>
@@ -8609,24 +8618,24 @@
         <v>9</v>
       </c>
       <c r="G220" s="18" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="H220" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="221" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A221" s="5" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="B221" s="6" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="C221" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D221" s="5" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="E221" s="7" t="s">
         <v>8</v>
@@ -8635,24 +8644,24 @@
         <v>16</v>
       </c>
       <c r="G221" s="18" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="H221" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="222" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A222" s="5" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="B222" s="6" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="C222" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D222" s="5" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="E222" s="7" t="s">
         <v>20</v>
@@ -8661,24 +8670,24 @@
         <v>9</v>
       </c>
       <c r="G222" s="18" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="H222" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="223" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A223" s="5" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="B223" s="6" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C223" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D223" s="5" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="E223" s="7" t="s">
         <v>20</v>
@@ -8687,24 +8696,24 @@
         <v>9</v>
       </c>
       <c r="G223" s="18" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="H223" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="224" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A224" s="5" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="B224" s="6" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C224" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D224" s="5" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="E224" s="7" t="s">
         <v>20</v>
@@ -8713,24 +8722,24 @@
         <v>16</v>
       </c>
       <c r="G224" s="18" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="H224" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="225" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A225" s="5" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="B225" s="6" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="C225" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D225" s="5" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="E225" s="7" t="s">
         <v>8</v>
@@ -8739,24 +8748,24 @@
         <v>93</v>
       </c>
       <c r="G225" s="18" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="H225" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="226" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A226" s="5" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="B226" s="6" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="C226" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D226" s="5" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="E226" s="7" t="s">
         <v>20</v>
@@ -8765,24 +8774,24 @@
         <v>9</v>
       </c>
       <c r="G226" s="18" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="H226" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="227" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A227" s="5" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="B227" s="6" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="C227" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D227" s="5" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="E227" s="7" t="s">
         <v>20</v>
@@ -8791,24 +8800,24 @@
         <v>93</v>
       </c>
       <c r="G227" s="18" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="H227" s="18" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
     </row>
     <row r="228" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A228" s="5" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B228" s="6" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="C228" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D228" s="5" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="E228" s="7" t="s">
         <v>20</v>
@@ -8817,24 +8826,24 @@
         <v>93</v>
       </c>
       <c r="G228" s="18" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="H228" s="18" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
     </row>
     <row r="229" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A229" s="5" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="B229" s="6" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="C229" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D229" s="5" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="E229" s="7" t="s">
         <v>20</v>
@@ -8843,24 +8852,24 @@
         <v>93</v>
       </c>
       <c r="G229" s="18" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="H229" s="18" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
     </row>
     <row r="230" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A230" s="5" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B230" s="6" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="C230" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D230" s="5" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="E230" s="7" t="s">
         <v>20</v>
@@ -8869,24 +8878,24 @@
         <v>93</v>
       </c>
       <c r="G230" s="18" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="H230" s="18" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
     </row>
     <row r="231" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A231" s="5" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="B231" s="6" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="C231" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D231" s="5" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="E231" s="7" t="s">
         <v>20</v>
@@ -8895,50 +8904,50 @@
         <v>13</v>
       </c>
       <c r="G231" s="18" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="H231" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="232" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A232" s="5" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="B232" s="6" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="C232" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D232" s="5" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="E232" s="7" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F232" s="7" t="s">
         <v>93</v>
       </c>
       <c r="G232" s="18" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="H232" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="233" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A233" s="5" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="B233" s="6" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="C233" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D233" s="5" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="E233" s="7" t="s">
         <v>20</v>
@@ -8947,50 +8956,50 @@
         <v>93</v>
       </c>
       <c r="G233" s="18" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="H233" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="234" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A234" s="5" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="B234" s="6" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="C234" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D234" s="5" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="E234" s="7" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F234" s="7" t="s">
         <v>9</v>
       </c>
       <c r="G234" s="18" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="H234" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="235" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A235" s="5" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B235" s="6" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="C235" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D235" s="5" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="E235" s="7" t="s">
         <v>20</v>
@@ -8999,24 +9008,24 @@
         <v>9</v>
       </c>
       <c r="G235" s="18" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="H235" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="236" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A236" s="5" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="B236" s="6" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="C236" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D236" s="5" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="E236" s="7" t="s">
         <v>20</v>
@@ -9025,50 +9034,50 @@
         <v>16</v>
       </c>
       <c r="G236" s="18" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="H236" s="18" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="237" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A237" s="5" t="s">
-        <v>566</v>
+        <v>789</v>
       </c>
       <c r="B237" s="6" t="s">
-        <v>567</v>
+        <v>790</v>
       </c>
       <c r="C237" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D237" s="5" t="s">
-        <v>565</v>
+        <v>791</v>
       </c>
       <c r="E237" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F237" s="7" t="s">
-        <v>93</v>
+        <v>16</v>
       </c>
       <c r="G237" s="18" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="H237" s="18" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="238" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A238" s="5" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="B238" s="6" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="C238" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D238" s="5" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="E238" s="7" t="s">
         <v>20</v>
@@ -9077,24 +9086,24 @@
         <v>93</v>
       </c>
       <c r="G238" s="18" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="H238" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="239" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A239" s="5" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="B239" s="6" t="s">
-        <v>735</v>
+        <v>567</v>
       </c>
       <c r="C239" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D239" s="5" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="E239" s="7" t="s">
         <v>20</v>
@@ -9103,50 +9112,50 @@
         <v>93</v>
       </c>
       <c r="G239" s="18" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="H239" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="240" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A240" s="5" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="B240" s="6" t="s">
-        <v>753</v>
+        <v>733</v>
       </c>
       <c r="C240" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D240" s="5" t="s">
-        <v>571</v>
+        <v>563</v>
       </c>
       <c r="E240" s="7" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F240" s="7" t="s">
         <v>93</v>
       </c>
       <c r="G240" s="18" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="H240" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="241" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A241" s="5" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="B241" s="6" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="C241" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D241" s="5" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="E241" s="7" t="s">
         <v>8</v>
@@ -9155,102 +9164,102 @@
         <v>93</v>
       </c>
       <c r="G241" s="18" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="H241" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="242" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A242" s="5" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="B242" s="6" t="s">
-        <v>736</v>
+        <v>752</v>
       </c>
       <c r="C242" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D242" s="5" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="E242" s="7" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F242" s="7" t="s">
         <v>93</v>
       </c>
       <c r="G242" s="18" t="s">
-        <v>715</v>
+        <v>709</v>
       </c>
       <c r="H242" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="243" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A243" s="5" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="B243" s="6" t="s">
-        <v>755</v>
+        <v>734</v>
       </c>
       <c r="C243" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D243" s="5" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="E243" s="7" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F243" s="7" t="s">
         <v>93</v>
       </c>
       <c r="G243" s="18" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="H243" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="244" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A244" s="5" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="B244" s="6" t="s">
-        <v>578</v>
+        <v>753</v>
       </c>
       <c r="C244" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D244" s="5" t="s">
-        <v>576</v>
+        <v>569</v>
       </c>
       <c r="E244" s="7" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F244" s="7" t="s">
-        <v>13</v>
+        <v>93</v>
       </c>
       <c r="G244" s="18" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="H244" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="245" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A245" s="5" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="B245" s="6" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="C245" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D245" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E245" s="7" t="s">
         <v>20</v>
@@ -9259,24 +9268,24 @@
         <v>13</v>
       </c>
       <c r="G245" s="18" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="H245" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="246" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A246" s="5" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="B246" s="6" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="C246" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D246" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E246" s="7" t="s">
         <v>20</v>
@@ -9285,50 +9294,50 @@
         <v>13</v>
       </c>
       <c r="G246" s="18" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="H246" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="247" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A247" s="5" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="B247" s="6" t="s">
-        <v>586</v>
+        <v>580</v>
       </c>
       <c r="C247" s="7" t="s">
-        <v>583</v>
+        <v>338</v>
       </c>
       <c r="D247" s="5" t="s">
-        <v>584</v>
+        <v>574</v>
       </c>
       <c r="E247" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F247" s="7" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G247" s="18" t="s">
-        <v>716</v>
+        <v>706</v>
       </c>
       <c r="H247" s="18" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
     </row>
     <row r="248" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A248" s="5" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="B248" s="6" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="C248" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D248" s="5" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="E248" s="7" t="s">
         <v>20</v>
@@ -9337,76 +9346,76 @@
         <v>9</v>
       </c>
       <c r="G248" s="18" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="H248" s="18" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
     </row>
     <row r="249" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A249" s="5">
-        <v>3164</v>
+      <c r="A249" s="5" t="s">
+        <v>585</v>
       </c>
       <c r="B249" s="6" t="s">
-        <v>737</v>
+        <v>586</v>
       </c>
       <c r="C249" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D249" s="5" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="E249" s="7" t="s">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="F249" s="7" t="s">
         <v>9</v>
       </c>
       <c r="G249" s="18" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="H249" s="18" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
     </row>
     <row r="250" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A250" s="5" t="s">
-        <v>590</v>
+      <c r="A250" s="5">
+        <v>3164</v>
       </c>
       <c r="B250" s="6" t="s">
-        <v>591</v>
+        <v>735</v>
       </c>
       <c r="C250" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D250" s="5" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E250" s="7" t="s">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="F250" s="7" t="s">
         <v>9</v>
       </c>
       <c r="G250" s="18" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="H250" s="18" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
     </row>
     <row r="251" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A251" s="5" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="B251" s="6" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="C251" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D251" s="5" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="E251" s="7" t="s">
         <v>20</v>
@@ -9415,50 +9424,50 @@
         <v>9</v>
       </c>
       <c r="G251" s="18" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="H251" s="18" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
     </row>
     <row r="252" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A252" s="13" t="s">
-        <v>596</v>
+      <c r="A252" s="5" t="s">
+        <v>591</v>
       </c>
       <c r="B252" s="6" t="s">
-        <v>738</v>
+        <v>592</v>
       </c>
       <c r="C252" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D252" s="5" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="E252" s="7" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F252" s="7" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="G252" s="18" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="H252" s="18" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
     </row>
     <row r="253" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A253" s="13" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="B253" s="6" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="C253" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D253" s="5" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="E253" s="7" t="s">
         <v>8</v>
@@ -9467,102 +9476,102 @@
         <v>16</v>
       </c>
       <c r="G253" s="18" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="H253" s="18" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
     </row>
     <row r="254" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A254" s="5" t="s">
-        <v>599</v>
+      <c r="A254" s="13" t="s">
+        <v>595</v>
       </c>
       <c r="B254" s="6" t="s">
-        <v>600</v>
+        <v>737</v>
       </c>
       <c r="C254" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D254" s="5" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="E254" s="7" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F254" s="7" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="G254" s="18" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="H254" s="18" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
     </row>
     <row r="255" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A255" s="5" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="B255" s="6" t="s">
-        <v>740</v>
+        <v>598</v>
       </c>
       <c r="C255" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D255" s="5" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="E255" s="7" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F255" s="7" t="s">
         <v>9</v>
       </c>
       <c r="G255" s="18" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H255" s="18" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
     </row>
     <row r="256" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A256" s="5" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="B256" s="6" t="s">
-        <v>605</v>
+        <v>738</v>
       </c>
       <c r="C256" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D256" s="5" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="E256" s="7" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F256" s="7" t="s">
         <v>9</v>
       </c>
       <c r="G256" s="18" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="H256" s="18" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
     </row>
     <row r="257" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A257" s="5" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="B257" s="6" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="C257" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D257" s="5" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="E257" s="7" t="s">
         <v>20</v>
@@ -9571,24 +9580,24 @@
         <v>9</v>
       </c>
       <c r="G257" s="18" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="H257" s="18" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
     </row>
     <row r="258" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A258" s="5" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="B258" s="6" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="C258" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D258" s="5" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="E258" s="7" t="s">
         <v>20</v>
@@ -9597,24 +9606,24 @@
         <v>9</v>
       </c>
       <c r="G258" s="18" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="H258" s="18" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
     </row>
     <row r="259" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A259" s="5" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="B259" s="6" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="C259" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D259" s="5" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="E259" s="7" t="s">
         <v>20</v>
@@ -9623,24 +9632,24 @@
         <v>9</v>
       </c>
       <c r="G259" s="18" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="H259" s="18" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
     </row>
     <row r="260" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A260" s="5" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="B260" s="6" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="C260" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D260" s="5" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="E260" s="7" t="s">
         <v>20</v>
@@ -9649,50 +9658,50 @@
         <v>9</v>
       </c>
       <c r="G260" s="18" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="H260" s="18" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
     </row>
     <row r="261" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A261" s="5" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="B261" s="6" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="C261" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D261" s="5" t="s">
-        <v>614</v>
+        <v>601</v>
       </c>
       <c r="E261" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F261" s="7" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="G261" s="18" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="H261" s="18" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
     </row>
     <row r="262" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A262" s="5" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="B262" s="6" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="C262" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D262" s="5" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="E262" s="7" t="s">
         <v>20</v>
@@ -9701,24 +9710,24 @@
         <v>16</v>
       </c>
       <c r="G262" s="18" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="H262" s="18" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
     </row>
     <row r="263" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A263" s="5" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="B263" s="6" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="C263" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D263" s="5" t="s">
-        <v>619</v>
+        <v>612</v>
       </c>
       <c r="E263" s="7" t="s">
         <v>20</v>
@@ -9727,24 +9736,24 @@
         <v>16</v>
       </c>
       <c r="G263" s="18" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="H263" s="18" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
     </row>
     <row r="264" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A264" s="5" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="B264" s="6" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="C264" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D264" s="5" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="E264" s="7" t="s">
         <v>20</v>
@@ -9753,24 +9762,24 @@
         <v>16</v>
       </c>
       <c r="G264" s="18" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="H264" s="18" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
     </row>
     <row r="265" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A265" s="5" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="B265" s="6" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="C265" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D265" s="5" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="E265" s="7" t="s">
         <v>20</v>
@@ -9779,24 +9788,24 @@
         <v>16</v>
       </c>
       <c r="G265" s="18" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="H265" s="18" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
     </row>
     <row r="266" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A266" s="5" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="B266" s="6" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="C266" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D266" s="5" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="E266" s="7" t="s">
         <v>20</v>
@@ -9805,24 +9814,24 @@
         <v>16</v>
       </c>
       <c r="G266" s="18" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="H266" s="18" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
     </row>
     <row r="267" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A267" s="5" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="B267" s="6" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="C267" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D267" s="5" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="E267" s="7" t="s">
         <v>20</v>
@@ -9831,24 +9840,24 @@
         <v>16</v>
       </c>
       <c r="G267" s="18" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="H267" s="18" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
     </row>
     <row r="268" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A268" s="5" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="B268" s="6" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="C268" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D268" s="5" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="E268" s="7" t="s">
         <v>20</v>
@@ -9857,24 +9866,24 @@
         <v>16</v>
       </c>
       <c r="G268" s="18" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="H268" s="18" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
     </row>
     <row r="269" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A269" s="5" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="B269" s="6" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="C269" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D269" s="5" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="E269" s="7" t="s">
         <v>20</v>
@@ -9883,76 +9892,76 @@
         <v>16</v>
       </c>
       <c r="G269" s="18" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="H269" s="18" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
     </row>
     <row r="270" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A270" s="5" t="s">
-        <v>635</v>
+        <v>630</v>
       </c>
       <c r="B270" s="6" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="C270" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D270" s="5" t="s">
-        <v>634</v>
+        <v>617</v>
       </c>
       <c r="E270" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F270" s="7" t="s">
-        <v>93</v>
+        <v>16</v>
       </c>
       <c r="G270" s="18" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="H270" s="18" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
     </row>
     <row r="271" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A271" s="5" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="B271" s="6" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="C271" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D271" s="5" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="E271" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F271" s="7" t="s">
-        <v>9</v>
+        <v>93</v>
       </c>
       <c r="G271" s="18" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="H271" s="18" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="272" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A272" s="5" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="B272" s="6" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="C272" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D272" s="5" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="E272" s="7" t="s">
         <v>20</v>
@@ -9961,24 +9970,24 @@
         <v>9</v>
       </c>
       <c r="G272" s="18" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="H272" s="18" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
     </row>
     <row r="273" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A273" s="5" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="B273" s="6" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="C273" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D273" s="5" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="E273" s="7" t="s">
         <v>20</v>
@@ -9987,50 +9996,50 @@
         <v>9</v>
       </c>
       <c r="G273" s="18" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="H273" s="18" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
     </row>
     <row r="274" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A274" s="5" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="B274" s="6" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
       <c r="C274" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D274" s="5" t="s">
-        <v>644</v>
+        <v>635</v>
       </c>
       <c r="E274" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F274" s="7" t="s">
-        <v>93</v>
+        <v>9</v>
       </c>
       <c r="G274" s="18" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="H274" s="18" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
     </row>
     <row r="275" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A275" s="5" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="B275" s="6" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="C275" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D275" s="5" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="E275" s="7" t="s">
         <v>20</v>
@@ -10039,50 +10048,50 @@
         <v>93</v>
       </c>
       <c r="G275" s="18" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="H275" s="18" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
     </row>
     <row r="276" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A276" s="5" t="s">
-        <v>650</v>
+        <v>645</v>
       </c>
       <c r="B276" s="6" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="C276" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D276" s="5" t="s">
-        <v>649</v>
+        <v>642</v>
       </c>
       <c r="E276" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F276" s="7" t="s">
-        <v>13</v>
+        <v>93</v>
       </c>
       <c r="G276" s="18" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
       <c r="H276" s="18" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
     </row>
     <row r="277" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A277" s="5" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="B277" s="6" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="C277" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D277" s="5" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="E277" s="7" t="s">
         <v>20</v>
@@ -10091,128 +10100,128 @@
         <v>13</v>
       </c>
       <c r="G277" s="18" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="H277" s="18" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
     </row>
     <row r="278" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A278" s="5" t="s">
-        <v>655</v>
+        <v>650</v>
       </c>
       <c r="B278" s="6" t="s">
-        <v>656</v>
+        <v>651</v>
       </c>
       <c r="C278" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D278" s="5" t="s">
-        <v>654</v>
+        <v>647</v>
       </c>
       <c r="E278" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F278" s="7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G278" s="18" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="H278" s="18" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="279" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A279" s="5" t="s">
-        <v>658</v>
+        <v>653</v>
       </c>
       <c r="B279" s="6" t="s">
-        <v>773</v>
+        <v>654</v>
       </c>
       <c r="C279" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D279" s="5" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
       <c r="E279" s="7" t="s">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="F279" s="7" t="s">
-        <v>93</v>
+        <v>16</v>
       </c>
       <c r="G279" s="18" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="H279" s="18" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
     </row>
     <row r="280" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A280" s="5" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="B280" s="6" t="s">
-        <v>661</v>
+        <v>771</v>
       </c>
       <c r="C280" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D280" s="5" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="E280" s="7" t="s">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="F280" s="7" t="s">
-        <v>9</v>
+        <v>93</v>
       </c>
       <c r="G280" s="18" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
       <c r="H280" s="18" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
     </row>
     <row r="281" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A281" s="5" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="B281" s="6" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="C281" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D281" s="5" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="E281" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F281" s="7" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G281" s="18" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="H281" s="18" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
     </row>
     <row r="282" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A282" s="5" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="B282" s="6" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="C282" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D282" s="5" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="E282" s="7" t="s">
         <v>20</v>
@@ -10221,50 +10230,50 @@
         <v>13</v>
       </c>
       <c r="G282" s="18" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="H282" s="18" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
     </row>
     <row r="283" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A283" s="5" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="B283" s="6" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="C283" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D283" s="5" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="E283" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F283" s="7" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G283" s="18" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="H283" s="18" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
     </row>
     <row r="284" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A284" s="5" t="s">
-        <v>671</v>
-      </c>
-      <c r="B284" s="14" t="s">
-        <v>672</v>
+        <v>666</v>
+      </c>
+      <c r="B284" s="6" t="s">
+        <v>667</v>
       </c>
       <c r="C284" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D284" s="5" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="E284" s="7" t="s">
         <v>20</v>
@@ -10273,24 +10282,24 @@
         <v>9</v>
       </c>
       <c r="G284" s="18" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H284" s="18" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="285" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A285" s="5" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="B285" s="14" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="C285" s="7" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D285" s="5" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="E285" s="7" t="s">
         <v>20</v>
@@ -10299,14 +10308,40 @@
         <v>9</v>
       </c>
       <c r="G285" s="18" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="H285" s="18" t="s">
-        <v>789</v>
+        <v>787</v>
+      </c>
+    </row>
+    <row r="286" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A286" s="5" t="s">
+        <v>671</v>
+      </c>
+      <c r="B286" s="14" t="s">
+        <v>672</v>
+      </c>
+      <c r="C286" s="7" t="s">
+        <v>581</v>
+      </c>
+      <c r="D286" s="5" t="s">
+        <v>668</v>
+      </c>
+      <c r="E286" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F286" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G286" s="18" t="s">
+        <v>718</v>
+      </c>
+      <c r="H286" s="18" t="s">
+        <v>787</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H285" xr:uid="{446419A3-BB56-46D4-B296-D3867C4128DB}"/>
+  <autoFilter ref="A1:H286" xr:uid="{446419A3-BB56-46D4-B296-D3867C4128DB}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/source-excel/DATAPLANT.xlsx
+++ b/source-excel/DATAPLANT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI\รายงานการจัดระดับ\newstarrating\source-excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ECB9D3A-B662-4D04-9F59-2A5C74E4D79E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBD0646E-F0BF-4F93-BE54-43C7D6F58240}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="8130" xr2:uid="{22141E00-01BD-4411-8006-614C22989334}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$286</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$288</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2287" uniqueCount="794">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2303" uniqueCount="798">
   <si>
     <t>กิจการ</t>
   </si>
@@ -2411,6 +2411,18 @@
   </si>
   <si>
     <t>สองพี่น้อง 2</t>
+  </si>
+  <si>
+    <t>FC414</t>
+  </si>
+  <si>
+    <t>ทับปุด 2</t>
+  </si>
+  <si>
+    <t>13O9</t>
+  </si>
+  <si>
+    <t>วี.เอส.คอนกรีต 3 ลาดตะเคียน (Type X)</t>
   </si>
 </sst>
 </file>
@@ -2891,7 +2903,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5D3108B-0AC7-45F6-8395-B543209D3234}">
-  <dimension ref="A1:H286"/>
+  <dimension ref="A1:H288"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.6328125" style="17" customWidth="1"/>
@@ -3920,25 +3932,25 @@
     </row>
     <row r="40" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A40" s="5" t="s">
-        <v>105</v>
+        <v>796</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>106</v>
+        <v>797</v>
       </c>
       <c r="C40" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G40" s="18" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="H40" s="18" t="s">
         <v>778</v>
@@ -3946,68 +3958,68 @@
     </row>
     <row r="41" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A41" s="5" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>770</v>
+        <v>106</v>
       </c>
       <c r="C41" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>93</v>
+        <v>13</v>
       </c>
       <c r="G41" s="18" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="H41" s="18" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A42" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>763</v>
+        <v>770</v>
       </c>
       <c r="C42" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E42" s="7" t="s">
         <v>100</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>16</v>
+        <v>93</v>
       </c>
       <c r="G42" s="18" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="H42" s="18" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A43" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="C43" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E43" s="7" t="s">
         <v>100</v>
@@ -4016,33 +4028,33 @@
         <v>16</v>
       </c>
       <c r="G43" s="18" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="H43" s="18" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A44" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>115</v>
+        <v>764</v>
       </c>
       <c r="C44" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>93</v>
+        <v>16</v>
       </c>
       <c r="G44" s="18" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="H44" s="18" t="s">
         <v>779</v>
@@ -4050,39 +4062,39 @@
     </row>
     <row r="45" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A45" s="5" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C45" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E45" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>9</v>
+        <v>93</v>
       </c>
       <c r="G45" s="18" t="s">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="H45" s="18" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A46" s="5" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>119</v>
+        <v>21</v>
       </c>
       <c r="D46" s="5" t="s">
         <v>116</v>
@@ -4094,33 +4106,33 @@
         <v>9</v>
       </c>
       <c r="G46" s="18" t="s">
-        <v>687</v>
+        <v>677</v>
       </c>
       <c r="H46" s="18" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A47" s="5" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C47" s="7" t="s">
         <v>119</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="E47" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G47" s="18" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="H47" s="18" t="s">
         <v>780</v>
@@ -4128,25 +4140,25 @@
     </row>
     <row r="48" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A48" s="5" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C48" s="7" t="s">
         <v>119</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E48" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>93</v>
+        <v>13</v>
       </c>
       <c r="G48" s="18" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="H48" s="18" t="s">
         <v>780</v>
@@ -4154,10 +4166,10 @@
     </row>
     <row r="49" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A49" s="5" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C49" s="7" t="s">
         <v>119</v>
@@ -4180,10 +4192,10 @@
     </row>
     <row r="50" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A50" s="5" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C50" s="7" t="s">
         <v>119</v>
@@ -4206,22 +4218,22 @@
     </row>
     <row r="51" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A51" s="5" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C51" s="7" t="s">
         <v>119</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="E51" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>9</v>
+        <v>93</v>
       </c>
       <c r="G51" s="18" t="s">
         <v>687</v>
@@ -4232,10 +4244,10 @@
     </row>
     <row r="52" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A52" s="5" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C52" s="7" t="s">
         <v>119</v>
@@ -4258,10 +4270,10 @@
     </row>
     <row r="53" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A53" s="5" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>792</v>
+        <v>136</v>
       </c>
       <c r="C53" s="7" t="s">
         <v>119</v>
@@ -4284,10 +4296,10 @@
     </row>
     <row r="54" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A54" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>139</v>
+        <v>792</v>
       </c>
       <c r="C54" s="7" t="s">
         <v>119</v>
@@ -4310,10 +4322,10 @@
     </row>
     <row r="55" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A55" s="5" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>793</v>
+        <v>139</v>
       </c>
       <c r="C55" s="7" t="s">
         <v>119</v>
@@ -4336,36 +4348,36 @@
     </row>
     <row r="56" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A56" s="5" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>143</v>
+        <v>793</v>
       </c>
       <c r="C56" s="7" t="s">
         <v>119</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="E56" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>93</v>
+        <v>9</v>
       </c>
       <c r="G56" s="18" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="H56" s="18" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A57" s="5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>722</v>
+        <v>143</v>
       </c>
       <c r="C57" s="7" t="s">
         <v>119</v>
@@ -4388,10 +4400,10 @@
     </row>
     <row r="58" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A58" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>146</v>
+        <v>722</v>
       </c>
       <c r="C58" s="7" t="s">
         <v>119</v>
@@ -4414,10 +4426,10 @@
     </row>
     <row r="59" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A59" s="5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C59" s="7" t="s">
         <v>119</v>
@@ -4440,22 +4452,22 @@
     </row>
     <row r="60" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A60" s="5" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C60" s="7" t="s">
         <v>119</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="E60" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>16</v>
+        <v>93</v>
       </c>
       <c r="G60" s="18" t="s">
         <v>689</v>
@@ -4466,25 +4478,25 @@
     </row>
     <row r="61" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A61" s="5" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C61" s="7" t="s">
         <v>119</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E61" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>93</v>
+        <v>16</v>
       </c>
       <c r="G61" s="18" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="H61" s="18" t="s">
         <v>781</v>
@@ -4492,22 +4504,22 @@
     </row>
     <row r="62" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A62" s="5" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C62" s="7" t="s">
         <v>119</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="E62" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>13</v>
+        <v>93</v>
       </c>
       <c r="G62" s="18" t="s">
         <v>690</v>
@@ -4518,22 +4530,22 @@
     </row>
     <row r="63" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A63" s="5" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C63" s="7" t="s">
         <v>119</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E63" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>93</v>
+        <v>13</v>
       </c>
       <c r="G63" s="18" t="s">
         <v>690</v>
@@ -4544,22 +4556,22 @@
     </row>
     <row r="64" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A64" s="5" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C64" s="7" t="s">
         <v>119</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E64" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>9</v>
+        <v>93</v>
       </c>
       <c r="G64" s="18" t="s">
         <v>690</v>
@@ -4570,22 +4582,22 @@
     </row>
     <row r="65" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A65" s="5" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C65" s="7" t="s">
         <v>119</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E65" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>93</v>
+        <v>9</v>
       </c>
       <c r="G65" s="18" t="s">
         <v>690</v>
@@ -4596,36 +4608,36 @@
     </row>
     <row r="66" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A66" s="5" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>167</v>
+        <v>119</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E66" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>13</v>
+        <v>93</v>
       </c>
       <c r="G66" s="18" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="H66" s="18" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A67" s="5" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C67" s="7" t="s">
         <v>167</v>
@@ -4648,10 +4660,10 @@
     </row>
     <row r="68" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A68" s="5" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C68" s="7" t="s">
         <v>167</v>
@@ -4674,16 +4686,16 @@
     </row>
     <row r="69" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A69" s="5" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C69" s="7" t="s">
         <v>167</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="E69" s="7" t="s">
         <v>20</v>
@@ -4700,25 +4712,25 @@
     </row>
     <row r="70" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A70" s="5" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C70" s="7" t="s">
         <v>167</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="E70" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G70" s="18" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="H70" s="18" t="s">
         <v>782</v>
@@ -4726,25 +4738,25 @@
     </row>
     <row r="71" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A71" s="5" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C71" s="7" t="s">
         <v>167</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E71" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>93</v>
+        <v>16</v>
       </c>
       <c r="G71" s="18" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="H71" s="18" t="s">
         <v>782</v>
@@ -4752,16 +4764,16 @@
     </row>
     <row r="72" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A72" s="5" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C72" s="7" t="s">
         <v>167</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="E72" s="7" t="s">
         <v>20</v>
@@ -4770,7 +4782,7 @@
         <v>93</v>
       </c>
       <c r="G72" s="18" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="H72" s="18" t="s">
         <v>782</v>
@@ -4778,10 +4790,10 @@
     </row>
     <row r="73" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A73" s="5" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C73" s="7" t="s">
         <v>167</v>
@@ -4804,25 +4816,25 @@
     </row>
     <row r="74" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A74" s="5" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C74" s="7" t="s">
         <v>167</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="E74" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F74" s="7" t="s">
-        <v>9</v>
+        <v>93</v>
       </c>
       <c r="G74" s="18" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="H74" s="18" t="s">
         <v>782</v>
@@ -4830,10 +4842,10 @@
     </row>
     <row r="75" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A75" s="5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C75" s="7" t="s">
         <v>167</v>
@@ -4856,10 +4868,10 @@
     </row>
     <row r="76" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A76" s="5" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C76" s="7" t="s">
         <v>167</v>
@@ -4882,10 +4894,10 @@
     </row>
     <row r="77" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A77" s="5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C77" s="7" t="s">
         <v>167</v>
@@ -4900,7 +4912,7 @@
         <v>9</v>
       </c>
       <c r="G77" s="18" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="H77" s="18" t="s">
         <v>782</v>
@@ -4908,10 +4920,10 @@
     </row>
     <row r="78" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A78" s="5" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C78" s="7" t="s">
         <v>167</v>
@@ -4934,10 +4946,10 @@
     </row>
     <row r="79" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A79" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C79" s="7" t="s">
         <v>167</v>
@@ -4960,16 +4972,16 @@
     </row>
     <row r="80" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A80" s="5" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C80" s="7" t="s">
         <v>167</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="E80" s="7" t="s">
         <v>20</v>
@@ -4986,22 +4998,22 @@
     </row>
     <row r="81" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A81" s="5" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C81" s="7" t="s">
         <v>167</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E81" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G81" s="18" t="s">
         <v>693</v>
@@ -5012,10 +5024,10 @@
     </row>
     <row r="82" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A82" s="5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C82" s="7" t="s">
         <v>167</v>
@@ -5038,10 +5050,10 @@
     </row>
     <row r="83" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A83" s="5" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C83" s="7" t="s">
         <v>167</v>
@@ -5063,49 +5075,49 @@
       </c>
     </row>
     <row r="84" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A84" s="9" t="s">
-        <v>213</v>
-      </c>
-      <c r="B84" s="10" t="s">
-        <v>214</v>
+      <c r="A84" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="B84" s="6" t="s">
+        <v>211</v>
       </c>
       <c r="C84" s="7" t="s">
         <v>167</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="E84" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="F84" s="11" t="s">
-        <v>9</v>
+        <v>205</v>
+      </c>
+      <c r="E84" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F84" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G84" s="18" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="H84" s="18" t="s">
         <v>782</v>
       </c>
     </row>
     <row r="85" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A85" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="B85" s="6" t="s">
-        <v>217</v>
+      <c r="A85" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="B85" s="10" t="s">
+        <v>214</v>
       </c>
       <c r="C85" s="7" t="s">
         <v>167</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="E85" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="F85" s="7" t="s">
-        <v>93</v>
+        <v>212</v>
+      </c>
+      <c r="E85" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="F85" s="11" t="s">
+        <v>9</v>
       </c>
       <c r="G85" s="18" t="s">
         <v>694</v>
@@ -5116,16 +5128,16 @@
     </row>
     <row r="86" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A86" s="5" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C86" s="7" t="s">
         <v>167</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="E86" s="7" t="s">
         <v>20</v>
@@ -5134,7 +5146,7 @@
         <v>93</v>
       </c>
       <c r="G86" s="18" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H86" s="18" t="s">
         <v>782</v>
@@ -5142,42 +5154,42 @@
     </row>
     <row r="87" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A87" s="5" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C87" s="7" t="s">
         <v>167</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E87" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F87" s="7" t="s">
-        <v>9</v>
+        <v>93</v>
       </c>
       <c r="G87" s="18" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H87" s="18" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="88" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A88" s="5" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C88" s="7" t="s">
         <v>167</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="E88" s="7" t="s">
         <v>20</v>
@@ -5186,59 +5198,59 @@
         <v>9</v>
       </c>
       <c r="G88" s="18" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H88" s="18" t="s">
         <v>783</v>
       </c>
     </row>
     <row r="89" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A89" s="9" t="s">
-        <v>228</v>
-      </c>
-      <c r="B89" s="10" t="s">
-        <v>229</v>
+      <c r="A89" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="B89" s="6" t="s">
+        <v>226</v>
       </c>
       <c r="C89" s="7" t="s">
         <v>167</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="E89" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="F89" s="11" t="s">
-        <v>93</v>
+        <v>224</v>
+      </c>
+      <c r="E89" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F89" s="7" t="s">
+        <v>9</v>
       </c>
       <c r="G89" s="18" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H89" s="18" t="s">
         <v>783</v>
       </c>
     </row>
     <row r="90" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A90" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="B90" s="6" t="s">
-        <v>232</v>
+      <c r="A90" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="B90" s="10" t="s">
+        <v>229</v>
       </c>
       <c r="C90" s="7" t="s">
         <v>167</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="E90" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="F90" s="7" t="s">
-        <v>9</v>
+        <v>227</v>
+      </c>
+      <c r="E90" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="F90" s="11" t="s">
+        <v>93</v>
       </c>
       <c r="G90" s="18" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H90" s="18" t="s">
         <v>783</v>
@@ -5246,25 +5258,25 @@
     </row>
     <row r="91" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A91" s="5" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C91" s="7" t="s">
         <v>167</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="E91" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F91" s="7" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="G91" s="18" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="H91" s="18" t="s">
         <v>783</v>
@@ -5272,22 +5284,22 @@
     </row>
     <row r="92" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A92" s="5" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C92" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="D92" s="12" t="s">
-        <v>236</v>
+      <c r="D92" s="5" t="s">
+        <v>233</v>
       </c>
       <c r="E92" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F92" s="7" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="G92" s="18" t="s">
         <v>697</v>
@@ -5298,10 +5310,10 @@
     </row>
     <row r="93" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A93" s="5" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C93" s="7" t="s">
         <v>167</v>
@@ -5324,16 +5336,16 @@
     </row>
     <row r="94" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A94" s="5" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C94" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="D94" s="5" t="s">
-        <v>241</v>
+      <c r="D94" s="12" t="s">
+        <v>236</v>
       </c>
       <c r="E94" s="7" t="s">
         <v>20</v>
@@ -5342,7 +5354,7 @@
         <v>9</v>
       </c>
       <c r="G94" s="18" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H94" s="18" t="s">
         <v>783</v>
@@ -5350,16 +5362,16 @@
     </row>
     <row r="95" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A95" s="5" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C95" s="7" t="s">
         <v>167</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="E95" s="7" t="s">
         <v>20</v>
@@ -5368,7 +5380,7 @@
         <v>9</v>
       </c>
       <c r="G95" s="18" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="H95" s="18" t="s">
         <v>783</v>
@@ -5376,10 +5388,10 @@
     </row>
     <row r="96" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A96" s="5" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C96" s="7" t="s">
         <v>167</v>
@@ -5402,10 +5414,10 @@
     </row>
     <row r="97" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A97" s="5" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C97" s="7" t="s">
         <v>167</v>
@@ -5428,10 +5440,10 @@
     </row>
     <row r="98" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A98" s="5" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C98" s="7" t="s">
         <v>167</v>
@@ -5454,25 +5466,25 @@
     </row>
     <row r="99" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A99" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C99" s="7" t="s">
         <v>167</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="E99" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F99" s="7" t="s">
-        <v>93</v>
+        <v>9</v>
       </c>
       <c r="G99" s="18" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="H99" s="18" t="s">
         <v>783</v>
@@ -5480,10 +5492,10 @@
     </row>
     <row r="100" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A100" s="5" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C100" s="7" t="s">
         <v>167</v>
@@ -5506,25 +5518,25 @@
     </row>
     <row r="101" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A101" s="5" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="C101" s="7" t="s">
         <v>167</v>
       </c>
       <c r="D101" s="5" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="E101" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>9</v>
+        <v>93</v>
       </c>
       <c r="G101" s="18" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H101" s="18" t="s">
         <v>783</v>
@@ -5532,10 +5544,10 @@
     </row>
     <row r="102" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A102" s="5" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C102" s="7" t="s">
         <v>167</v>
@@ -5558,25 +5570,25 @@
     </row>
     <row r="103" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A103" s="5" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C103" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="D103" s="12" t="s">
-        <v>263</v>
+      <c r="D103" s="5" t="s">
+        <v>258</v>
       </c>
       <c r="E103" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F103" s="7" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G103" s="18" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="H103" s="18" t="s">
         <v>783</v>
@@ -5584,10 +5596,10 @@
     </row>
     <row r="104" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A104" s="5" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C104" s="7" t="s">
         <v>167</v>
@@ -5610,10 +5622,10 @@
     </row>
     <row r="105" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A105" s="5" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C105" s="7" t="s">
         <v>167</v>
@@ -5636,10 +5648,10 @@
     </row>
     <row r="106" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A106" s="5" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C106" s="7" t="s">
         <v>167</v>
@@ -5662,25 +5674,25 @@
     </row>
     <row r="107" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A107" s="5" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C107" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="D107" s="5" t="s">
-        <v>272</v>
+      <c r="D107" s="12" t="s">
+        <v>263</v>
       </c>
       <c r="E107" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F107" s="7" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G107" s="18" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="H107" s="18" t="s">
         <v>783</v>
@@ -5688,10 +5700,10 @@
     </row>
     <row r="108" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A108" s="5" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C108" s="7" t="s">
         <v>167</v>
@@ -5714,10 +5726,10 @@
     </row>
     <row r="109" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A109" s="5" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C109" s="7" t="s">
         <v>167</v>
@@ -5740,10 +5752,10 @@
     </row>
     <row r="110" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A110" s="5" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C110" s="7" t="s">
         <v>167</v>
@@ -5766,16 +5778,16 @@
     </row>
     <row r="111" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A111" s="5" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C111" s="7" t="s">
         <v>167</v>
       </c>
       <c r="D111" s="5" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="E111" s="7" t="s">
         <v>20</v>
@@ -5784,7 +5796,7 @@
         <v>9</v>
       </c>
       <c r="G111" s="18" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H111" s="18" t="s">
         <v>783</v>
@@ -5792,25 +5804,25 @@
     </row>
     <row r="112" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A112" s="5" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="C112" s="7" t="s">
         <v>167</v>
       </c>
       <c r="D112" s="5" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="E112" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F112" s="7" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G112" s="18" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H112" s="18" t="s">
         <v>783</v>
@@ -5818,10 +5830,10 @@
     </row>
     <row r="113" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A113" s="5" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C113" s="7" t="s">
         <v>167</v>
@@ -5844,10 +5856,10 @@
     </row>
     <row r="114" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A114" s="5" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C114" s="7" t="s">
         <v>167</v>
@@ -5870,10 +5882,10 @@
     </row>
     <row r="115" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A115" s="5" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C115" s="7" t="s">
         <v>167</v>
@@ -5896,10 +5908,10 @@
     </row>
     <row r="116" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A116" s="5" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C116" s="7" t="s">
         <v>167</v>
@@ -5922,25 +5934,25 @@
     </row>
     <row r="117" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A117" s="5" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="C117" s="7" t="s">
         <v>167</v>
       </c>
       <c r="D117" s="5" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="E117" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F117" s="7" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G117" s="18" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H117" s="18" t="s">
         <v>783</v>
@@ -5948,22 +5960,22 @@
     </row>
     <row r="118" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A118" s="5" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>739</v>
+        <v>297</v>
       </c>
       <c r="C118" s="7" t="s">
         <v>167</v>
       </c>
       <c r="D118" s="5" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="E118" s="7" t="s">
-        <v>300</v>
+        <v>20</v>
       </c>
       <c r="F118" s="7" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="G118" s="18" t="s">
         <v>698</v>
@@ -5974,51 +5986,51 @@
     </row>
     <row r="119" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A119" s="5" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>303</v>
+        <v>739</v>
       </c>
       <c r="C119" s="7" t="s">
         <v>167</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="E119" s="7" t="s">
-        <v>20</v>
+        <v>300</v>
       </c>
       <c r="F119" s="7" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G119" s="18" t="s">
-        <v>691</v>
+        <v>698</v>
       </c>
       <c r="H119" s="18" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
     </row>
     <row r="120" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A120" s="5" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C120" s="7" t="s">
         <v>167</v>
       </c>
       <c r="D120" s="5" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="E120" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F120" s="7" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G120" s="18" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="H120" s="18" t="s">
         <v>782</v>
@@ -6026,25 +6038,25 @@
     </row>
     <row r="121" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A121" s="5" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>754</v>
+        <v>306</v>
       </c>
       <c r="C121" s="7" t="s">
         <v>167</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="E121" s="7" t="s">
-        <v>300</v>
+        <v>20</v>
       </c>
       <c r="F121" s="7" t="s">
-        <v>93</v>
+        <v>9</v>
       </c>
       <c r="G121" s="18" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H121" s="18" t="s">
         <v>782</v>
@@ -6052,22 +6064,22 @@
     </row>
     <row r="122" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A122" s="5" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C122" s="7" t="s">
         <v>167</v>
       </c>
       <c r="D122" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="E122" s="7" t="s">
         <v>300</v>
       </c>
       <c r="F122" s="7" t="s">
-        <v>9</v>
+        <v>93</v>
       </c>
       <c r="G122" s="18" t="s">
         <v>694</v>
@@ -6078,25 +6090,25 @@
     </row>
     <row r="123" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A123" s="5" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C123" s="7" t="s">
         <v>167</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E123" s="7" t="s">
         <v>300</v>
       </c>
       <c r="F123" s="7" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="G123" s="18" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="H123" s="18" t="s">
         <v>782</v>
@@ -6104,10 +6116,10 @@
     </row>
     <row r="124" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A124" s="5" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="C124" s="7" t="s">
         <v>167</v>
@@ -6116,7 +6128,7 @@
         <v>311</v>
       </c>
       <c r="E124" s="7" t="s">
-        <v>20</v>
+        <v>300</v>
       </c>
       <c r="F124" s="7" t="s">
         <v>16</v>
@@ -6130,25 +6142,25 @@
     </row>
     <row r="125" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A125" s="5" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C125" s="7" t="s">
         <v>167</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="E125" s="7" t="s">
-        <v>300</v>
+        <v>20</v>
       </c>
       <c r="F125" s="7" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="G125" s="18" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="H125" s="18" t="s">
         <v>782</v>
@@ -6156,16 +6168,16 @@
     </row>
     <row r="126" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A126" s="5" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="C126" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="D126" s="4" t="s">
-        <v>316</v>
+      <c r="D126" s="5" t="s">
+        <v>314</v>
       </c>
       <c r="E126" s="7" t="s">
         <v>300</v>
@@ -6174,59 +6186,59 @@
         <v>9</v>
       </c>
       <c r="G126" s="18" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="H126" s="18" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="127" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A127" s="5" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B127" s="6" t="s">
-        <v>772</v>
+        <v>759</v>
       </c>
       <c r="C127" s="7" t="s">
         <v>167</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E127" s="7" t="s">
         <v>300</v>
       </c>
       <c r="F127" s="7" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="G127" s="18" t="s">
-        <v>691</v>
+        <v>698</v>
       </c>
       <c r="H127" s="18" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
     </row>
     <row r="128" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A128" s="5" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>766</v>
+        <v>772</v>
       </c>
       <c r="C128" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="D128" s="5" t="s">
-        <v>320</v>
+      <c r="D128" s="4" t="s">
+        <v>318</v>
       </c>
       <c r="E128" s="7" t="s">
-        <v>322</v>
+        <v>300</v>
       </c>
       <c r="F128" s="7" t="s">
         <v>16</v>
       </c>
       <c r="G128" s="18" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="H128" s="18" t="s">
         <v>782</v>
@@ -6234,10 +6246,10 @@
     </row>
     <row r="129" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A129" s="5" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="C129" s="7" t="s">
         <v>167</v>
@@ -6246,7 +6258,7 @@
         <v>320</v>
       </c>
       <c r="E129" s="7" t="s">
-        <v>300</v>
+        <v>322</v>
       </c>
       <c r="F129" s="7" t="s">
         <v>16</v>
@@ -6260,25 +6272,25 @@
     </row>
     <row r="130" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A130" s="5" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="C130" s="7" t="s">
         <v>167</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="E130" s="7" t="s">
         <v>300</v>
       </c>
       <c r="F130" s="7" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G130" s="18" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H130" s="18" t="s">
         <v>782</v>
@@ -6286,25 +6298,25 @@
     </row>
     <row r="131" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A131" s="5" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>767</v>
+        <v>760</v>
       </c>
       <c r="C131" s="7" t="s">
         <v>167</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E131" s="7" t="s">
-        <v>322</v>
+        <v>300</v>
       </c>
       <c r="F131" s="7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G131" s="18" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="H131" s="18" t="s">
         <v>782</v>
@@ -6312,10 +6324,10 @@
     </row>
     <row r="132" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A132" s="5" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C132" s="7" t="s">
         <v>167</v>
@@ -6338,10 +6350,10 @@
     </row>
     <row r="133" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A133" s="5" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>330</v>
+        <v>768</v>
       </c>
       <c r="C133" s="7" t="s">
         <v>167</v>
@@ -6350,7 +6362,7 @@
         <v>326</v>
       </c>
       <c r="E133" s="7" t="s">
-        <v>20</v>
+        <v>322</v>
       </c>
       <c r="F133" s="7" t="s">
         <v>16</v>
@@ -6364,22 +6376,22 @@
     </row>
     <row r="134" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A134" s="5" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C134" s="7" t="s">
         <v>167</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="E134" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F134" s="7" t="s">
-        <v>93</v>
+        <v>16</v>
       </c>
       <c r="G134" s="18" t="s">
         <v>695</v>
@@ -6390,22 +6402,22 @@
     </row>
     <row r="135" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A135" s="5" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>773</v>
+        <v>333</v>
       </c>
       <c r="C135" s="7" t="s">
         <v>167</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="E135" s="7" t="s">
-        <v>322</v>
+        <v>20</v>
       </c>
       <c r="F135" s="7" t="s">
-        <v>16</v>
+        <v>93</v>
       </c>
       <c r="G135" s="18" t="s">
         <v>695</v>
@@ -6416,25 +6428,25 @@
     </row>
     <row r="136" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A136" s="5" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>761</v>
+        <v>773</v>
       </c>
       <c r="C136" s="7" t="s">
         <v>167</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E136" s="7" t="s">
-        <v>300</v>
+        <v>322</v>
       </c>
       <c r="F136" s="7" t="s">
-        <v>93</v>
+        <v>16</v>
       </c>
       <c r="G136" s="18" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
       <c r="H136" s="18" t="s">
         <v>782</v>
@@ -6442,36 +6454,36 @@
     </row>
     <row r="137" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A137" s="5" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="B137" s="6" t="s">
-        <v>341</v>
+        <v>761</v>
       </c>
       <c r="C137" s="7" t="s">
-        <v>338</v>
+        <v>167</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="E137" s="7" t="s">
-        <v>20</v>
+        <v>300</v>
       </c>
       <c r="F137" s="7" t="s">
         <v>93</v>
       </c>
       <c r="G137" s="18" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H137" s="18" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="138" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A138" s="5" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B138" s="6" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C138" s="7" t="s">
         <v>338</v>
@@ -6494,22 +6506,22 @@
     </row>
     <row r="139" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A139" s="5" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="B139" s="6" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C139" s="7" t="s">
         <v>338</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="E139" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F139" s="7" t="s">
-        <v>9</v>
+        <v>93</v>
       </c>
       <c r="G139" s="18" t="s">
         <v>702</v>
@@ -6520,25 +6532,25 @@
     </row>
     <row r="140" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A140" s="5" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="B140" s="6" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C140" s="7" t="s">
         <v>338</v>
       </c>
       <c r="D140" s="5" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="E140" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F140" s="7" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G140" s="18" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H140" s="18" t="s">
         <v>784</v>
@@ -6546,10 +6558,10 @@
     </row>
     <row r="141" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A141" s="5" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B141" s="6" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C141" s="7" t="s">
         <v>338</v>
@@ -6572,10 +6584,10 @@
     </row>
     <row r="142" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A142" s="5" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B142" s="6" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C142" s="7" t="s">
         <v>338</v>
@@ -6598,10 +6610,10 @@
     </row>
     <row r="143" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A143" s="5" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B143" s="6" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C143" s="7" t="s">
         <v>338</v>
@@ -6616,7 +6628,7 @@
         <v>13</v>
       </c>
       <c r="G143" s="18" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H143" s="18" t="s">
         <v>784</v>
@@ -6624,10 +6636,10 @@
     </row>
     <row r="144" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A144" s="5" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B144" s="6" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C144" s="7" t="s">
         <v>338</v>
@@ -6650,10 +6662,10 @@
     </row>
     <row r="145" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A145" s="5" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B145" s="6" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C145" s="7" t="s">
         <v>338</v>
@@ -6676,10 +6688,10 @@
     </row>
     <row r="146" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A146" s="5" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B146" s="6" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C146" s="7" t="s">
         <v>338</v>
@@ -6702,10 +6714,10 @@
     </row>
     <row r="147" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A147" s="5" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B147" s="6" t="s">
-        <v>723</v>
+        <v>361</v>
       </c>
       <c r="C147" s="7" t="s">
         <v>338</v>
@@ -6728,10 +6740,10 @@
     </row>
     <row r="148" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A148" s="5" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B148" s="6" t="s">
-        <v>364</v>
+        <v>723</v>
       </c>
       <c r="C148" s="7" t="s">
         <v>338</v>
@@ -6746,7 +6758,7 @@
         <v>13</v>
       </c>
       <c r="G148" s="18" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H148" s="18" t="s">
         <v>784</v>
@@ -6754,36 +6766,36 @@
     </row>
     <row r="149" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A149" s="5" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="B149" s="6" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="C149" s="7" t="s">
         <v>338</v>
       </c>
       <c r="D149" s="5" t="s">
-        <v>365</v>
+        <v>347</v>
       </c>
       <c r="E149" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F149" s="7" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G149" s="18" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="H149" s="18" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="150" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A150" s="5" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B150" s="6" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C150" s="7" t="s">
         <v>338</v>
@@ -6806,22 +6818,22 @@
     </row>
     <row r="151" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A151" s="5" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="B151" s="6" t="s">
-        <v>743</v>
+        <v>369</v>
       </c>
       <c r="C151" s="7" t="s">
         <v>338</v>
       </c>
       <c r="D151" s="5" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="E151" s="7" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F151" s="7" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="G151" s="18" t="s">
         <v>705</v>
@@ -6832,25 +6844,25 @@
     </row>
     <row r="152" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A152" s="5" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B152" s="6" t="s">
-        <v>374</v>
+        <v>743</v>
       </c>
       <c r="C152" s="7" t="s">
         <v>338</v>
       </c>
       <c r="D152" s="5" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="E152" s="7" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F152" s="7" t="s">
-        <v>93</v>
+        <v>16</v>
       </c>
       <c r="G152" s="18" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="H152" s="18" t="s">
         <v>785</v>
@@ -6858,10 +6870,10 @@
     </row>
     <row r="153" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A153" s="5" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B153" s="6" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C153" s="7" t="s">
         <v>338</v>
@@ -6876,30 +6888,30 @@
         <v>93</v>
       </c>
       <c r="G153" s="18" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="H153" s="18" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
     </row>
     <row r="154" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A154" s="5" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="B154" s="6" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="C154" s="7" t="s">
         <v>338</v>
       </c>
       <c r="D154" s="5" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="E154" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F154" s="7" t="s">
-        <v>9</v>
+        <v>93</v>
       </c>
       <c r="G154" s="18" t="s">
         <v>704</v>
@@ -6910,36 +6922,36 @@
     </row>
     <row r="155" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A155" s="5" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="B155" s="6" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="C155" s="7" t="s">
         <v>338</v>
       </c>
-      <c r="D155" s="4" t="s">
-        <v>380</v>
+      <c r="D155" s="5" t="s">
+        <v>377</v>
       </c>
       <c r="E155" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F155" s="7" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="G155" s="18" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="H155" s="18" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="156" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A156" s="5" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B156" s="6" t="s">
-        <v>744</v>
+        <v>382</v>
       </c>
       <c r="C156" s="7" t="s">
         <v>338</v>
@@ -6948,7 +6960,7 @@
         <v>380</v>
       </c>
       <c r="E156" s="7" t="s">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="F156" s="7" t="s">
         <v>16</v>
@@ -6962,10 +6974,10 @@
     </row>
     <row r="157" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A157" s="5" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B157" s="6" t="s">
-        <v>385</v>
+        <v>744</v>
       </c>
       <c r="C157" s="7" t="s">
         <v>338</v>
@@ -6974,13 +6986,13 @@
         <v>380</v>
       </c>
       <c r="E157" s="7" t="s">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="F157" s="7" t="s">
         <v>16</v>
       </c>
       <c r="G157" s="18" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H157" s="18" t="s">
         <v>785</v>
@@ -6988,48 +7000,48 @@
     </row>
     <row r="158" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A158" s="5" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B158" s="6" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C158" s="7" t="s">
         <v>338</v>
       </c>
-      <c r="D158" s="5" t="s">
-        <v>386</v>
+      <c r="D158" s="4" t="s">
+        <v>380</v>
       </c>
       <c r="E158" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F158" s="7" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="G158" s="18" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H158" s="18" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="159" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A159" s="5" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B159" s="6" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="C159" s="7" t="s">
         <v>338</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="E159" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F159" s="7" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G159" s="18" t="s">
         <v>708</v>
@@ -7040,10 +7052,10 @@
     </row>
     <row r="160" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A160" s="5" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B160" s="6" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C160" s="7" t="s">
         <v>338</v>
@@ -7066,10 +7078,10 @@
     </row>
     <row r="161" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A161" s="5" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B161" s="6" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C161" s="7" t="s">
         <v>338</v>
@@ -7092,10 +7104,10 @@
     </row>
     <row r="162" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A162" s="5" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B162" s="6" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C162" s="7" t="s">
         <v>338</v>
@@ -7118,10 +7130,10 @@
     </row>
     <row r="163" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A163" s="5" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B163" s="6" t="s">
-        <v>724</v>
+        <v>397</v>
       </c>
       <c r="C163" s="7" t="s">
         <v>338</v>
@@ -7144,10 +7156,10 @@
     </row>
     <row r="164" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A164" s="5" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B164" s="6" t="s">
-        <v>774</v>
+        <v>724</v>
       </c>
       <c r="C164" s="7" t="s">
         <v>338</v>
@@ -7156,36 +7168,36 @@
         <v>389</v>
       </c>
       <c r="E164" s="7" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F164" s="7" t="s">
         <v>13</v>
       </c>
       <c r="G164" s="18" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H164" s="18" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
     </row>
     <row r="165" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A165" s="5" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B165" s="6" t="s">
-        <v>745</v>
+        <v>774</v>
       </c>
       <c r="C165" s="7" t="s">
         <v>338</v>
       </c>
       <c r="D165" s="5" t="s">
-        <v>400</v>
+        <v>389</v>
       </c>
       <c r="E165" s="7" t="s">
         <v>8</v>
       </c>
       <c r="F165" s="7" t="s">
-        <v>93</v>
+        <v>13</v>
       </c>
       <c r="G165" s="18" t="s">
         <v>709</v>
@@ -7196,36 +7208,36 @@
     </row>
     <row r="166" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A166" s="5" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B166" s="6" t="s">
-        <v>404</v>
+        <v>745</v>
       </c>
       <c r="C166" s="7" t="s">
         <v>338</v>
       </c>
       <c r="D166" s="5" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="E166" s="7" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F166" s="7" t="s">
-        <v>13</v>
+        <v>93</v>
       </c>
       <c r="G166" s="18" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H166" s="18" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="167" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A167" s="5" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B167" s="6" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C167" s="7" t="s">
         <v>338</v>
@@ -7248,10 +7260,10 @@
     </row>
     <row r="168" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A168" s="5" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B168" s="6" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C168" s="7" t="s">
         <v>338</v>
@@ -7274,10 +7286,10 @@
     </row>
     <row r="169" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A169" s="5" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B169" s="6" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C169" s="7" t="s">
         <v>338</v>
@@ -7300,10 +7312,10 @@
     </row>
     <row r="170" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A170" s="5" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B170" s="6" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C170" s="7" t="s">
         <v>338</v>
@@ -7326,36 +7338,36 @@
     </row>
     <row r="171" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A171" s="5" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="B171" s="6" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="C171" s="7" t="s">
         <v>338</v>
       </c>
       <c r="D171" s="5" t="s">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="E171" s="7" t="s">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="F171" s="7" t="s">
-        <v>93</v>
+        <v>13</v>
       </c>
       <c r="G171" s="18" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="H171" s="18" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
     </row>
     <row r="172" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A172" s="5" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B172" s="6" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C172" s="7" t="s">
         <v>338</v>
@@ -7370,7 +7382,7 @@
         <v>93</v>
       </c>
       <c r="G172" s="18" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H172" s="18" t="s">
         <v>785</v>
@@ -7378,10 +7390,10 @@
     </row>
     <row r="173" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A173" s="5" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B173" s="6" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C173" s="7" t="s">
         <v>338</v>
@@ -7404,10 +7416,10 @@
     </row>
     <row r="174" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A174" s="5" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B174" s="6" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C174" s="7" t="s">
         <v>338</v>
@@ -7430,10 +7442,10 @@
     </row>
     <row r="175" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A175" s="5" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B175" s="6" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C175" s="7" t="s">
         <v>338</v>
@@ -7448,7 +7460,7 @@
         <v>93</v>
       </c>
       <c r="G175" s="18" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="H175" s="18" t="s">
         <v>785</v>
@@ -7456,10 +7468,10 @@
     </row>
     <row r="176" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A176" s="5" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B176" s="6" t="s">
-        <v>746</v>
+        <v>423</v>
       </c>
       <c r="C176" s="7" t="s">
         <v>338</v>
@@ -7474,7 +7486,7 @@
         <v>93</v>
       </c>
       <c r="G176" s="18" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="H176" s="18" t="s">
         <v>785</v>
@@ -7482,10 +7494,10 @@
     </row>
     <row r="177" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A177" s="5" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B177" s="6" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="C177" s="7" t="s">
         <v>338</v>
@@ -7500,7 +7512,7 @@
         <v>93</v>
       </c>
       <c r="G177" s="18" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="H177" s="18" t="s">
         <v>785</v>
@@ -7508,36 +7520,36 @@
     </row>
     <row r="178" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A178" s="5" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B178" s="6" t="s">
-        <v>428</v>
+        <v>747</v>
       </c>
       <c r="C178" s="7" t="s">
         <v>338</v>
       </c>
       <c r="D178" s="5" t="s">
-        <v>426</v>
+        <v>413</v>
       </c>
       <c r="E178" s="7" t="s">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="F178" s="7" t="s">
-        <v>9</v>
+        <v>93</v>
       </c>
       <c r="G178" s="18" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="H178" s="18" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="179" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A179" s="5" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B179" s="6" t="s">
-        <v>725</v>
+        <v>428</v>
       </c>
       <c r="C179" s="7" t="s">
         <v>338</v>
@@ -7560,16 +7572,16 @@
     </row>
     <row r="180" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A180" s="5" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B180" s="6" t="s">
-        <v>432</v>
+        <v>725</v>
       </c>
       <c r="C180" s="7" t="s">
         <v>338</v>
       </c>
       <c r="D180" s="5" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="E180" s="7" t="s">
         <v>20</v>
@@ -7578,7 +7590,7 @@
         <v>9</v>
       </c>
       <c r="G180" s="18" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="H180" s="18" t="s">
         <v>786</v>
@@ -7586,10 +7598,10 @@
     </row>
     <row r="181" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A181" s="5" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B181" s="6" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C181" s="7" t="s">
         <v>338</v>
@@ -7612,25 +7624,25 @@
     </row>
     <row r="182" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A182" s="5" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="B182" s="6" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="C182" s="7" t="s">
         <v>338</v>
       </c>
       <c r="D182" s="5" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="E182" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F182" s="7" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G182" s="18" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H182" s="18" t="s">
         <v>786</v>
@@ -7638,10 +7650,10 @@
     </row>
     <row r="183" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A183" s="5" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B183" s="6" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C183" s="7" t="s">
         <v>338</v>
@@ -7664,10 +7676,10 @@
     </row>
     <row r="184" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A184" s="5" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B184" s="6" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C184" s="7" t="s">
         <v>338</v>
@@ -7690,10 +7702,10 @@
     </row>
     <row r="185" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A185" s="5" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B185" s="6" t="s">
-        <v>765</v>
+        <v>441</v>
       </c>
       <c r="C185" s="7" t="s">
         <v>338</v>
@@ -7702,7 +7714,7 @@
         <v>435</v>
       </c>
       <c r="E185" s="7" t="s">
-        <v>300</v>
+        <v>20</v>
       </c>
       <c r="F185" s="7" t="s">
         <v>13</v>
@@ -7716,10 +7728,10 @@
     </row>
     <row r="186" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A186" s="5" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B186" s="6" t="s">
-        <v>444</v>
+        <v>765</v>
       </c>
       <c r="C186" s="7" t="s">
         <v>338</v>
@@ -7728,7 +7740,7 @@
         <v>435</v>
       </c>
       <c r="E186" s="7" t="s">
-        <v>20</v>
+        <v>300</v>
       </c>
       <c r="F186" s="7" t="s">
         <v>13</v>
@@ -7742,10 +7754,10 @@
     </row>
     <row r="187" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A187" s="5" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B187" s="6" t="s">
-        <v>726</v>
+        <v>444</v>
       </c>
       <c r="C187" s="7" t="s">
         <v>338</v>
@@ -7768,22 +7780,22 @@
     </row>
     <row r="188" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A188" s="5" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B188" s="6" t="s">
-        <v>448</v>
+        <v>726</v>
       </c>
       <c r="C188" s="7" t="s">
         <v>338</v>
       </c>
       <c r="D188" s="5" t="s">
-        <v>446</v>
+        <v>435</v>
       </c>
       <c r="E188" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F188" s="7" t="s">
-        <v>93</v>
+        <v>13</v>
       </c>
       <c r="G188" s="18" t="s">
         <v>711</v>
@@ -7794,25 +7806,25 @@
     </row>
     <row r="189" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A189" s="5" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="B189" s="6" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="C189" s="7" t="s">
         <v>338</v>
       </c>
       <c r="D189" s="5" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="E189" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F189" s="7" t="s">
-        <v>9</v>
+        <v>93</v>
       </c>
       <c r="G189" s="18" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H189" s="18" t="s">
         <v>786</v>
@@ -7820,10 +7832,10 @@
     </row>
     <row r="190" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A190" s="5" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B190" s="6" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C190" s="7" t="s">
         <v>338</v>
@@ -7846,10 +7858,10 @@
     </row>
     <row r="191" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A191" s="5" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B191" s="6" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C191" s="7" t="s">
         <v>338</v>
@@ -7872,10 +7884,10 @@
     </row>
     <row r="192" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A192" s="5" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B192" s="6" t="s">
-        <v>727</v>
+        <v>455</v>
       </c>
       <c r="C192" s="7" t="s">
         <v>338</v>
@@ -7898,22 +7910,22 @@
     </row>
     <row r="193" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A193" s="5" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B193" s="6" t="s">
-        <v>459</v>
+        <v>727</v>
       </c>
       <c r="C193" s="7" t="s">
         <v>338</v>
       </c>
       <c r="D193" s="5" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
       <c r="E193" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F193" s="7" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="G193" s="18" t="s">
         <v>712</v>
@@ -7924,10 +7936,10 @@
     </row>
     <row r="194" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A194" s="5" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B194" s="6" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C194" s="7" t="s">
         <v>338</v>
@@ -7950,22 +7962,22 @@
     </row>
     <row r="195" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A195" s="5" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="B195" s="6" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="C195" s="7" t="s">
         <v>338</v>
       </c>
       <c r="D195" s="5" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="E195" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F195" s="7" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="G195" s="18" t="s">
         <v>712</v>
@@ -7976,10 +7988,10 @@
     </row>
     <row r="196" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A196" s="5" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B196" s="6" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C196" s="7" t="s">
         <v>338</v>
@@ -8002,10 +8014,10 @@
     </row>
     <row r="197" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A197" s="5" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B197" s="6" t="s">
-        <v>728</v>
+        <v>466</v>
       </c>
       <c r="C197" s="7" t="s">
         <v>338</v>
@@ -8028,51 +8040,51 @@
     </row>
     <row r="198" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A198" s="5" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B198" s="6" t="s">
-        <v>470</v>
+        <v>728</v>
       </c>
       <c r="C198" s="7" t="s">
         <v>338</v>
       </c>
       <c r="D198" s="5" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="E198" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F198" s="7" t="s">
-        <v>93</v>
+        <v>9</v>
       </c>
       <c r="G198" s="18" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="H198" s="18" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
     </row>
     <row r="199" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A199" s="5" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="B199" s="6" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="C199" s="7" t="s">
         <v>338</v>
       </c>
       <c r="D199" s="5" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="E199" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F199" s="7" t="s">
-        <v>9</v>
+        <v>93</v>
       </c>
       <c r="G199" s="18" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="H199" s="18" t="s">
         <v>785</v>
@@ -8080,10 +8092,10 @@
     </row>
     <row r="200" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A200" s="5" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B200" s="6" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C200" s="7" t="s">
         <v>338</v>
@@ -8106,10 +8118,10 @@
     </row>
     <row r="201" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A201" s="5" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B201" s="6" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C201" s="7" t="s">
         <v>338</v>
@@ -8124,7 +8136,7 @@
         <v>9</v>
       </c>
       <c r="G201" s="18" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="H201" s="18" t="s">
         <v>785</v>
@@ -8132,10 +8144,10 @@
     </row>
     <row r="202" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A202" s="5" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B202" s="6" t="s">
-        <v>729</v>
+        <v>477</v>
       </c>
       <c r="C202" s="7" t="s">
         <v>338</v>
@@ -8158,25 +8170,25 @@
     </row>
     <row r="203" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A203" s="5" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B203" s="6" t="s">
-        <v>481</v>
+        <v>729</v>
       </c>
       <c r="C203" s="7" t="s">
         <v>338</v>
       </c>
       <c r="D203" s="5" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="E203" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F203" s="7" t="s">
-        <v>93</v>
+        <v>9</v>
       </c>
       <c r="G203" s="18" t="s">
-        <v>713</v>
+        <v>706</v>
       </c>
       <c r="H203" s="18" t="s">
         <v>785</v>
@@ -8184,10 +8196,10 @@
     </row>
     <row r="204" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A204" s="5" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B204" s="6" t="s">
-        <v>748</v>
+        <v>481</v>
       </c>
       <c r="C204" s="7" t="s">
         <v>338</v>
@@ -8196,7 +8208,7 @@
         <v>479</v>
       </c>
       <c r="E204" s="7" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F204" s="7" t="s">
         <v>93</v>
@@ -8210,10 +8222,10 @@
     </row>
     <row r="205" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A205" s="5" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B205" s="6" t="s">
-        <v>740</v>
+        <v>748</v>
       </c>
       <c r="C205" s="7" t="s">
         <v>338</v>
@@ -8222,7 +8234,7 @@
         <v>479</v>
       </c>
       <c r="E205" s="7" t="s">
-        <v>300</v>
+        <v>8</v>
       </c>
       <c r="F205" s="7" t="s">
         <v>93</v>
@@ -8236,25 +8248,25 @@
     </row>
     <row r="206" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A206" s="5" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B206" s="6" t="s">
-        <v>486</v>
+        <v>740</v>
       </c>
       <c r="C206" s="7" t="s">
         <v>338</v>
       </c>
       <c r="D206" s="5" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="E206" s="7" t="s">
-        <v>20</v>
+        <v>300</v>
       </c>
       <c r="F206" s="7" t="s">
-        <v>9</v>
+        <v>93</v>
       </c>
       <c r="G206" s="18" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="H206" s="18" t="s">
         <v>785</v>
@@ -8262,25 +8274,25 @@
     </row>
     <row r="207" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A207" s="5" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="B207" s="6" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="C207" s="7" t="s">
         <v>338</v>
       </c>
       <c r="D207" s="5" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="E207" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F207" s="7" t="s">
-        <v>93</v>
+        <v>9</v>
       </c>
       <c r="G207" s="18" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="H207" s="18" t="s">
         <v>785</v>
@@ -8288,10 +8300,10 @@
     </row>
     <row r="208" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A208" s="5" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B208" s="6" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C208" s="7" t="s">
         <v>338</v>
@@ -8314,10 +8326,10 @@
     </row>
     <row r="209" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A209" s="5" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="B209" s="6" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C209" s="7" t="s">
         <v>338</v>
@@ -8340,10 +8352,10 @@
     </row>
     <row r="210" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A210" s="5" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B210" s="6" t="s">
-        <v>749</v>
+        <v>493</v>
       </c>
       <c r="C210" s="7" t="s">
         <v>338</v>
@@ -8352,7 +8364,7 @@
         <v>487</v>
       </c>
       <c r="E210" s="7" t="s">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="F210" s="7" t="s">
         <v>93</v>
@@ -8366,19 +8378,19 @@
     </row>
     <row r="211" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A211" s="5" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="B211" s="6" t="s">
-        <v>497</v>
+        <v>749</v>
       </c>
       <c r="C211" s="7" t="s">
         <v>338</v>
       </c>
       <c r="D211" s="5" t="s">
-        <v>495</v>
+        <v>487</v>
       </c>
       <c r="E211" s="7" t="s">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="F211" s="7" t="s">
         <v>93</v>
@@ -8392,42 +8404,42 @@
     </row>
     <row r="212" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A212" s="5" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="B212" s="6" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="C212" s="7" t="s">
         <v>338</v>
       </c>
       <c r="D212" s="5" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="E212" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F212" s="7" t="s">
-        <v>9</v>
+        <v>93</v>
       </c>
       <c r="G212" s="18" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="H212" s="18" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="213" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A213" s="5" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="B213" s="6" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="C213" s="7" t="s">
         <v>338</v>
       </c>
       <c r="D213" s="5" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="E213" s="7" t="s">
         <v>20</v>
@@ -8436,30 +8448,30 @@
         <v>9</v>
       </c>
       <c r="G213" s="18" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="H213" s="18" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
     </row>
     <row r="214" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A214" s="5" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="B214" s="6" t="s">
-        <v>776</v>
+        <v>504</v>
       </c>
       <c r="C214" s="7" t="s">
         <v>338</v>
       </c>
       <c r="D214" s="5" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E214" s="7" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F214" s="7" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="G214" s="18" t="s">
         <v>707</v>
@@ -8470,36 +8482,36 @@
     </row>
     <row r="215" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A215" s="5" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B215" s="6" t="s">
-        <v>508</v>
+        <v>776</v>
       </c>
       <c r="C215" s="7" t="s">
         <v>338</v>
       </c>
       <c r="D215" s="5" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="E215" s="7" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F215" s="7" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G215" s="18" t="s">
-        <v>712</v>
+        <v>707</v>
       </c>
       <c r="H215" s="18" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="216" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A216" s="5" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B216" s="6" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C216" s="7" t="s">
         <v>338</v>
@@ -8522,51 +8534,51 @@
     </row>
     <row r="217" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A217" s="5" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="B217" s="6" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="C217" s="7" t="s">
         <v>338</v>
       </c>
       <c r="D217" s="5" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="E217" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F217" s="7" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G217" s="18" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="H217" s="18" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
     </row>
     <row r="218" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A218" s="5" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="B218" s="6" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="C218" s="7" t="s">
         <v>338</v>
       </c>
       <c r="D218" s="5" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="E218" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F218" s="7" t="s">
-        <v>93</v>
+        <v>9</v>
       </c>
       <c r="G218" s="18" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="H218" s="18" t="s">
         <v>785</v>
@@ -8574,22 +8586,22 @@
     </row>
     <row r="219" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A219" s="5" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B219" s="6" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="C219" s="7" t="s">
         <v>338</v>
       </c>
       <c r="D219" s="5" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="E219" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F219" s="7" t="s">
-        <v>9</v>
+        <v>93</v>
       </c>
       <c r="G219" s="18" t="s">
         <v>706</v>
@@ -8600,16 +8612,16 @@
     </row>
     <row r="220" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A220" s="5" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="B220" s="6" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="C220" s="7" t="s">
         <v>338</v>
       </c>
       <c r="D220" s="5" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="E220" s="7" t="s">
         <v>20</v>
@@ -8618,7 +8630,7 @@
         <v>9</v>
       </c>
       <c r="G220" s="18" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H220" s="18" t="s">
         <v>785</v>
@@ -8626,68 +8638,68 @@
     </row>
     <row r="221" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A221" s="5" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="B221" s="6" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="C221" s="7" t="s">
         <v>338</v>
       </c>
       <c r="D221" s="5" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="E221" s="7" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F221" s="7" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="G221" s="18" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H221" s="18" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="222" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A222" s="5" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="B222" s="6" t="s">
-        <v>730</v>
+        <v>525</v>
       </c>
       <c r="C222" s="7" t="s">
         <v>338</v>
       </c>
       <c r="D222" s="5" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="E222" s="7" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F222" s="7" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="G222" s="18" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H222" s="18" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
     </row>
     <row r="223" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A223" s="5" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="B223" s="6" t="s">
-        <v>530</v>
+        <v>730</v>
       </c>
       <c r="C223" s="7" t="s">
         <v>338</v>
       </c>
       <c r="D223" s="5" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="E223" s="7" t="s">
         <v>20</v>
@@ -8696,59 +8708,59 @@
         <v>9</v>
       </c>
       <c r="G223" s="18" t="s">
-        <v>712</v>
+        <v>707</v>
       </c>
       <c r="H223" s="18" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="224" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A224" s="5" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="B224" s="6" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="C224" s="7" t="s">
         <v>338</v>
       </c>
       <c r="D224" s="5" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="E224" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F224" s="7" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="G224" s="18" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="H224" s="18" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
     </row>
     <row r="225" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A225" s="5" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="B225" s="6" t="s">
-        <v>750</v>
+        <v>533</v>
       </c>
       <c r="C225" s="7" t="s">
         <v>338</v>
       </c>
       <c r="D225" s="5" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="E225" s="7" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F225" s="7" t="s">
-        <v>93</v>
+        <v>16</v>
       </c>
       <c r="G225" s="18" t="s">
-        <v>706</v>
+        <v>713</v>
       </c>
       <c r="H225" s="18" t="s">
         <v>785</v>
@@ -8756,25 +8768,25 @@
     </row>
     <row r="226" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A226" s="5" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="B226" s="6" t="s">
-        <v>538</v>
+        <v>750</v>
       </c>
       <c r="C226" s="7" t="s">
         <v>338</v>
       </c>
       <c r="D226" s="5" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="E226" s="7" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F226" s="7" t="s">
-        <v>9</v>
+        <v>93</v>
       </c>
       <c r="G226" s="18" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H226" s="18" t="s">
         <v>785</v>
@@ -8782,42 +8794,42 @@
     </row>
     <row r="227" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A227" s="5" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="B227" s="6" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="C227" s="7" t="s">
         <v>338</v>
       </c>
       <c r="D227" s="5" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="E227" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F227" s="7" t="s">
-        <v>93</v>
+        <v>9</v>
       </c>
       <c r="G227" s="18" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="H227" s="18" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
     </row>
     <row r="228" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A228" s="5" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="B228" s="6" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="C228" s="7" t="s">
         <v>338</v>
       </c>
       <c r="D228" s="5" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="E228" s="7" t="s">
         <v>20</v>
@@ -8826,7 +8838,7 @@
         <v>93</v>
       </c>
       <c r="G228" s="18" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H228" s="18" t="s">
         <v>784</v>
@@ -8834,10 +8846,10 @@
     </row>
     <row r="229" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A229" s="5" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B229" s="6" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="C229" s="7" t="s">
         <v>338</v>
@@ -8852,7 +8864,7 @@
         <v>93</v>
       </c>
       <c r="G229" s="18" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="H229" s="18" t="s">
         <v>784</v>
@@ -8860,10 +8872,10 @@
     </row>
     <row r="230" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A230" s="5" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="B230" s="6" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="C230" s="7" t="s">
         <v>338</v>
@@ -8878,7 +8890,7 @@
         <v>93</v>
       </c>
       <c r="G230" s="18" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="H230" s="18" t="s">
         <v>784</v>
@@ -8886,51 +8898,51 @@
     </row>
     <row r="231" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A231" s="5" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="B231" s="6" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="C231" s="7" t="s">
         <v>338</v>
       </c>
       <c r="D231" s="5" t="s">
-        <v>549</v>
+        <v>542</v>
       </c>
       <c r="E231" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F231" s="7" t="s">
-        <v>13</v>
+        <v>93</v>
       </c>
       <c r="G231" s="18" t="s">
-        <v>713</v>
+        <v>702</v>
       </c>
       <c r="H231" s="18" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="232" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A232" s="5" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="B232" s="6" t="s">
-        <v>741</v>
+        <v>551</v>
       </c>
       <c r="C232" s="7" t="s">
         <v>338</v>
       </c>
       <c r="D232" s="5" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="E232" s="7" t="s">
-        <v>300</v>
+        <v>20</v>
       </c>
       <c r="F232" s="7" t="s">
-        <v>93</v>
+        <v>13</v>
       </c>
       <c r="G232" s="18" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="H232" s="18" t="s">
         <v>785</v>
@@ -8938,103 +8950,103 @@
     </row>
     <row r="233" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A233" s="5" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="B233" s="6" t="s">
-        <v>556</v>
+        <v>741</v>
       </c>
       <c r="C233" s="7" t="s">
         <v>338</v>
       </c>
       <c r="D233" s="5" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="E233" s="7" t="s">
-        <v>20</v>
+        <v>300</v>
       </c>
       <c r="F233" s="7" t="s">
         <v>93</v>
       </c>
       <c r="G233" s="18" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="H233" s="18" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="234" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A234" s="5" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="B234" s="6" t="s">
-        <v>742</v>
+        <v>556</v>
       </c>
       <c r="C234" s="7" t="s">
         <v>338</v>
       </c>
       <c r="D234" s="5" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="E234" s="7" t="s">
-        <v>300</v>
+        <v>20</v>
       </c>
       <c r="F234" s="7" t="s">
-        <v>9</v>
+        <v>93</v>
       </c>
       <c r="G234" s="18" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="H234" s="18" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
     </row>
     <row r="235" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A235" s="5" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="B235" s="6" t="s">
-        <v>731</v>
+        <v>742</v>
       </c>
       <c r="C235" s="7" t="s">
         <v>338</v>
       </c>
       <c r="D235" s="5" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="E235" s="7" t="s">
-        <v>20</v>
+        <v>300</v>
       </c>
       <c r="F235" s="7" t="s">
         <v>9</v>
       </c>
       <c r="G235" s="18" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="H235" s="18" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="236" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A236" s="5" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B236" s="6" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="C236" s="7" t="s">
         <v>338</v>
       </c>
       <c r="D236" s="5" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="E236" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F236" s="7" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="G236" s="18" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H236" s="18" t="s">
         <v>786</v>
@@ -9042,16 +9054,16 @@
     </row>
     <row r="237" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A237" s="5" t="s">
-        <v>789</v>
+        <v>562</v>
       </c>
       <c r="B237" s="6" t="s">
-        <v>790</v>
+        <v>732</v>
       </c>
       <c r="C237" s="7" t="s">
         <v>338</v>
       </c>
       <c r="D237" s="5" t="s">
-        <v>791</v>
+        <v>561</v>
       </c>
       <c r="E237" s="7" t="s">
         <v>20</v>
@@ -9068,36 +9080,36 @@
     </row>
     <row r="238" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A238" s="5" t="s">
-        <v>564</v>
+        <v>789</v>
       </c>
       <c r="B238" s="6" t="s">
-        <v>565</v>
+        <v>790</v>
       </c>
       <c r="C238" s="7" t="s">
         <v>338</v>
       </c>
       <c r="D238" s="5" t="s">
-        <v>563</v>
+        <v>791</v>
       </c>
       <c r="E238" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F238" s="7" t="s">
-        <v>93</v>
+        <v>16</v>
       </c>
       <c r="G238" s="18" t="s">
-        <v>707</v>
+        <v>712</v>
       </c>
       <c r="H238" s="18" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
     </row>
     <row r="239" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A239" s="5" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="B239" s="6" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C239" s="7" t="s">
         <v>338</v>
@@ -9120,10 +9132,10 @@
     </row>
     <row r="240" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A240" s="5" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="B240" s="6" t="s">
-        <v>733</v>
+        <v>567</v>
       </c>
       <c r="C240" s="7" t="s">
         <v>338</v>
@@ -9146,25 +9158,25 @@
     </row>
     <row r="241" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A241" s="5" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="B241" s="6" t="s">
-        <v>751</v>
+        <v>733</v>
       </c>
       <c r="C241" s="7" t="s">
         <v>338</v>
       </c>
       <c r="D241" s="5" t="s">
-        <v>569</v>
+        <v>563</v>
       </c>
       <c r="E241" s="7" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F241" s="7" t="s">
         <v>93</v>
       </c>
       <c r="G241" s="18" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="H241" s="18" t="s">
         <v>785</v>
@@ -9172,10 +9184,10 @@
     </row>
     <row r="242" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A242" s="5" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B242" s="6" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C242" s="7" t="s">
         <v>338</v>
@@ -9198,10 +9210,10 @@
     </row>
     <row r="243" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A243" s="5" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B243" s="6" t="s">
-        <v>734</v>
+        <v>752</v>
       </c>
       <c r="C243" s="7" t="s">
         <v>338</v>
@@ -9210,13 +9222,13 @@
         <v>569</v>
       </c>
       <c r="E243" s="7" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F243" s="7" t="s">
         <v>93</v>
       </c>
       <c r="G243" s="18" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="H243" s="18" t="s">
         <v>785</v>
@@ -9224,10 +9236,10 @@
     </row>
     <row r="244" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A244" s="5" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B244" s="6" t="s">
-        <v>753</v>
+        <v>734</v>
       </c>
       <c r="C244" s="7" t="s">
         <v>338</v>
@@ -9236,13 +9248,13 @@
         <v>569</v>
       </c>
       <c r="E244" s="7" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F244" s="7" t="s">
         <v>93</v>
       </c>
       <c r="G244" s="18" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="H244" s="18" t="s">
         <v>785</v>
@@ -9250,25 +9262,25 @@
     </row>
     <row r="245" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A245" s="5" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="B245" s="6" t="s">
-        <v>576</v>
+        <v>753</v>
       </c>
       <c r="C245" s="7" t="s">
         <v>338</v>
       </c>
       <c r="D245" s="5" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="E245" s="7" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F245" s="7" t="s">
-        <v>13</v>
+        <v>93</v>
       </c>
       <c r="G245" s="18" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="H245" s="18" t="s">
         <v>785</v>
@@ -9276,10 +9288,10 @@
     </row>
     <row r="246" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A246" s="5" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="B246" s="6" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="C246" s="7" t="s">
         <v>338</v>
@@ -9302,10 +9314,10 @@
     </row>
     <row r="247" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A247" s="5" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="B247" s="6" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="C247" s="7" t="s">
         <v>338</v>
@@ -9328,36 +9340,36 @@
     </row>
     <row r="248" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A248" s="5" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="B248" s="6" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="C248" s="7" t="s">
-        <v>581</v>
+        <v>338</v>
       </c>
       <c r="D248" s="5" t="s">
-        <v>582</v>
+        <v>574</v>
       </c>
       <c r="E248" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F248" s="7" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G248" s="18" t="s">
-        <v>714</v>
+        <v>706</v>
       </c>
       <c r="H248" s="18" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="249" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A249" s="5" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B249" s="6" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="C249" s="7" t="s">
         <v>581</v>
@@ -9379,20 +9391,20 @@
       </c>
     </row>
     <row r="250" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A250" s="5">
-        <v>3164</v>
+      <c r="A250" s="5" t="s">
+        <v>585</v>
       </c>
       <c r="B250" s="6" t="s">
-        <v>735</v>
+        <v>586</v>
       </c>
       <c r="C250" s="7" t="s">
         <v>581</v>
       </c>
       <c r="D250" s="5" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="E250" s="7" t="s">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="F250" s="7" t="s">
         <v>9</v>
@@ -9405,11 +9417,11 @@
       </c>
     </row>
     <row r="251" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A251" s="5" t="s">
-        <v>588</v>
+      <c r="A251" s="5">
+        <v>3164</v>
       </c>
       <c r="B251" s="6" t="s">
-        <v>589</v>
+        <v>735</v>
       </c>
       <c r="C251" s="7" t="s">
         <v>581</v>
@@ -9418,7 +9430,7 @@
         <v>587</v>
       </c>
       <c r="E251" s="7" t="s">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="F251" s="7" t="s">
         <v>9</v>
@@ -9432,16 +9444,16 @@
     </row>
     <row r="252" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A252" s="5" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="B252" s="6" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="C252" s="7" t="s">
         <v>581</v>
       </c>
       <c r="D252" s="5" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="E252" s="7" t="s">
         <v>20</v>
@@ -9457,26 +9469,26 @@
       </c>
     </row>
     <row r="253" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A253" s="13" t="s">
-        <v>594</v>
+      <c r="A253" s="5" t="s">
+        <v>591</v>
       </c>
       <c r="B253" s="6" t="s">
-        <v>736</v>
+        <v>592</v>
       </c>
       <c r="C253" s="7" t="s">
         <v>581</v>
       </c>
       <c r="D253" s="5" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="E253" s="7" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F253" s="7" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="G253" s="18" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H253" s="18" t="s">
         <v>787</v>
@@ -9484,10 +9496,10 @@
     </row>
     <row r="254" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A254" s="13" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B254" s="6" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C254" s="7" t="s">
         <v>581</v>
@@ -9509,23 +9521,23 @@
       </c>
     </row>
     <row r="255" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A255" s="5" t="s">
-        <v>597</v>
+      <c r="A255" s="13" t="s">
+        <v>595</v>
       </c>
       <c r="B255" s="6" t="s">
-        <v>598</v>
+        <v>737</v>
       </c>
       <c r="C255" s="7" t="s">
         <v>581</v>
       </c>
       <c r="D255" s="5" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="E255" s="7" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F255" s="7" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="G255" s="18" t="s">
         <v>715</v>
@@ -9536,25 +9548,25 @@
     </row>
     <row r="256" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A256" s="5" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="B256" s="6" t="s">
-        <v>738</v>
+        <v>598</v>
       </c>
       <c r="C256" s="7" t="s">
         <v>581</v>
       </c>
       <c r="D256" s="5" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="E256" s="7" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F256" s="7" t="s">
         <v>9</v>
       </c>
       <c r="G256" s="18" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H256" s="18" t="s">
         <v>787</v>
@@ -9562,19 +9574,19 @@
     </row>
     <row r="257" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A257" s="5" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="B257" s="6" t="s">
-        <v>603</v>
+        <v>738</v>
       </c>
       <c r="C257" s="7" t="s">
         <v>581</v>
       </c>
       <c r="D257" s="5" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E257" s="7" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F257" s="7" t="s">
         <v>9</v>
@@ -9588,10 +9600,10 @@
     </row>
     <row r="258" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A258" s="5" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="B258" s="6" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="C258" s="7" t="s">
         <v>581</v>
@@ -9614,10 +9626,10 @@
     </row>
     <row r="259" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A259" s="5" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="B259" s="6" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="C259" s="7" t="s">
         <v>581</v>
@@ -9640,10 +9652,10 @@
     </row>
     <row r="260" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A260" s="5" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="B260" s="6" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="C260" s="7" t="s">
         <v>581</v>
@@ -9666,10 +9678,10 @@
     </row>
     <row r="261" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A261" s="5" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="B261" s="6" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="C261" s="7" t="s">
         <v>581</v>
@@ -9692,25 +9704,25 @@
     </row>
     <row r="262" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A262" s="5" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="B262" s="6" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="C262" s="7" t="s">
         <v>581</v>
       </c>
       <c r="D262" s="5" t="s">
-        <v>612</v>
+        <v>601</v>
       </c>
       <c r="E262" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F262" s="7" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="G262" s="18" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H262" s="18" t="s">
         <v>787</v>
@@ -9718,10 +9730,10 @@
     </row>
     <row r="263" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A263" s="5" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="B263" s="6" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="C263" s="7" t="s">
         <v>581</v>
@@ -9744,16 +9756,16 @@
     </row>
     <row r="264" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A264" s="5" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="B264" s="6" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="C264" s="7" t="s">
         <v>581</v>
       </c>
       <c r="D264" s="5" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="E264" s="7" t="s">
         <v>20</v>
@@ -9762,18 +9774,18 @@
         <v>16</v>
       </c>
       <c r="G264" s="18" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H264" s="18" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="265" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A265" s="5" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="B265" s="6" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="C265" s="7" t="s">
         <v>581</v>
@@ -9796,10 +9808,10 @@
     </row>
     <row r="266" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A266" s="5" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="B266" s="6" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="C266" s="7" t="s">
         <v>581</v>
@@ -9822,10 +9834,10 @@
     </row>
     <row r="267" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A267" s="5" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="B267" s="6" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="C267" s="7" t="s">
         <v>581</v>
@@ -9848,10 +9860,10 @@
     </row>
     <row r="268" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A268" s="5" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="B268" s="6" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="C268" s="7" t="s">
         <v>581</v>
@@ -9874,10 +9886,10 @@
     </row>
     <row r="269" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A269" s="5" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="B269" s="6" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="C269" s="7" t="s">
         <v>581</v>
@@ -9900,10 +9912,10 @@
     </row>
     <row r="270" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A270" s="5" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="B270" s="6" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="C270" s="7" t="s">
         <v>581</v>
@@ -9926,25 +9938,25 @@
     </row>
     <row r="271" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A271" s="5" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="B271" s="6" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="C271" s="7" t="s">
         <v>581</v>
       </c>
       <c r="D271" s="5" t="s">
-        <v>632</v>
+        <v>617</v>
       </c>
       <c r="E271" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F271" s="7" t="s">
-        <v>93</v>
+        <v>16</v>
       </c>
       <c r="G271" s="18" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="H271" s="18" t="s">
         <v>788</v>
@@ -9952,36 +9964,36 @@
     </row>
     <row r="272" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A272" s="5" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="B272" s="6" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="C272" s="7" t="s">
         <v>581</v>
       </c>
       <c r="D272" s="5" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="E272" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F272" s="7" t="s">
-        <v>9</v>
+        <v>93</v>
       </c>
       <c r="G272" s="18" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H272" s="18" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
     </row>
     <row r="273" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A273" s="5" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="B273" s="6" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="C273" s="7" t="s">
         <v>581</v>
@@ -10004,10 +10016,10 @@
     </row>
     <row r="274" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A274" s="5" t="s">
-        <v>640</v>
+        <v>794</v>
       </c>
       <c r="B274" s="6" t="s">
-        <v>641</v>
+        <v>795</v>
       </c>
       <c r="C274" s="7" t="s">
         <v>581</v>
@@ -10030,77 +10042,77 @@
     </row>
     <row r="275" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A275" s="5" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
       <c r="B275" s="6" t="s">
-        <v>644</v>
+        <v>639</v>
       </c>
       <c r="C275" s="7" t="s">
         <v>581</v>
       </c>
       <c r="D275" s="5" t="s">
-        <v>642</v>
+        <v>635</v>
       </c>
       <c r="E275" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F275" s="7" t="s">
-        <v>93</v>
+        <v>9</v>
       </c>
       <c r="G275" s="18" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H275" s="18" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="276" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A276" s="5" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="B276" s="6" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
       <c r="C276" s="7" t="s">
         <v>581</v>
       </c>
       <c r="D276" s="5" t="s">
-        <v>642</v>
+        <v>635</v>
       </c>
       <c r="E276" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F276" s="7" t="s">
-        <v>93</v>
+        <v>9</v>
       </c>
       <c r="G276" s="18" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H276" s="18" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="277" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A277" s="5" t="s">
-        <v>648</v>
+        <v>643</v>
       </c>
       <c r="B277" s="6" t="s">
-        <v>649</v>
+        <v>644</v>
       </c>
       <c r="C277" s="7" t="s">
         <v>581</v>
       </c>
       <c r="D277" s="5" t="s">
-        <v>647</v>
+        <v>642</v>
       </c>
       <c r="E277" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F277" s="7" t="s">
-        <v>13</v>
+        <v>93</v>
       </c>
       <c r="G277" s="18" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="H277" s="18" t="s">
         <v>788</v>
@@ -10108,25 +10120,25 @@
     </row>
     <row r="278" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A278" s="5" t="s">
-        <v>650</v>
+        <v>645</v>
       </c>
       <c r="B278" s="6" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="C278" s="7" t="s">
         <v>581</v>
       </c>
       <c r="D278" s="5" t="s">
-        <v>647</v>
+        <v>642</v>
       </c>
       <c r="E278" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F278" s="7" t="s">
-        <v>13</v>
+        <v>93</v>
       </c>
       <c r="G278" s="18" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="H278" s="18" t="s">
         <v>788</v>
@@ -10134,126 +10146,126 @@
     </row>
     <row r="279" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A279" s="5" t="s">
-        <v>653</v>
+        <v>648</v>
       </c>
       <c r="B279" s="6" t="s">
-        <v>654</v>
+        <v>649</v>
       </c>
       <c r="C279" s="7" t="s">
         <v>581</v>
       </c>
       <c r="D279" s="5" t="s">
-        <v>652</v>
+        <v>647</v>
       </c>
       <c r="E279" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F279" s="7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G279" s="18" t="s">
-        <v>714</v>
+        <v>719</v>
       </c>
       <c r="H279" s="18" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
     </row>
     <row r="280" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A280" s="5" t="s">
-        <v>656</v>
+        <v>650</v>
       </c>
       <c r="B280" s="6" t="s">
-        <v>771</v>
+        <v>651</v>
       </c>
       <c r="C280" s="7" t="s">
         <v>581</v>
       </c>
       <c r="D280" s="5" t="s">
-        <v>655</v>
+        <v>647</v>
       </c>
       <c r="E280" s="7" t="s">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="F280" s="7" t="s">
-        <v>93</v>
+        <v>13</v>
       </c>
       <c r="G280" s="18" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="H280" s="18" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
     </row>
     <row r="281" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A281" s="5" t="s">
-        <v>658</v>
+        <v>653</v>
       </c>
       <c r="B281" s="6" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="C281" s="7" t="s">
         <v>581</v>
       </c>
       <c r="D281" s="5" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
       <c r="E281" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F281" s="7" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="G281" s="18" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="H281" s="18" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="282" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A282" s="5" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="B282" s="6" t="s">
-        <v>662</v>
+        <v>771</v>
       </c>
       <c r="C282" s="7" t="s">
         <v>581</v>
       </c>
       <c r="D282" s="5" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="E282" s="7" t="s">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="F282" s="7" t="s">
-        <v>13</v>
+        <v>93</v>
       </c>
       <c r="G282" s="18" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="H282" s="18" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="283" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A283" s="5" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="B283" s="6" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="C283" s="7" t="s">
         <v>581</v>
       </c>
       <c r="D283" s="5" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="E283" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F283" s="7" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G283" s="18" t="s">
         <v>719</v>
@@ -10264,22 +10276,22 @@
     </row>
     <row r="284" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A284" s="5" t="s">
-        <v>666</v>
+        <v>661</v>
       </c>
       <c r="B284" s="6" t="s">
-        <v>667</v>
+        <v>662</v>
       </c>
       <c r="C284" s="7" t="s">
         <v>581</v>
       </c>
       <c r="D284" s="5" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="E284" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F284" s="7" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G284" s="18" t="s">
         <v>719</v>
@@ -10290,42 +10302,42 @@
     </row>
     <row r="285" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A285" s="5" t="s">
-        <v>669</v>
-      </c>
-      <c r="B285" s="14" t="s">
-        <v>670</v>
+        <v>663</v>
+      </c>
+      <c r="B285" s="6" t="s">
+        <v>664</v>
       </c>
       <c r="C285" s="7" t="s">
         <v>581</v>
       </c>
       <c r="D285" s="5" t="s">
-        <v>668</v>
+        <v>660</v>
       </c>
       <c r="E285" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F285" s="7" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G285" s="18" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H285" s="18" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
     </row>
     <row r="286" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A286" s="5" t="s">
-        <v>671</v>
-      </c>
-      <c r="B286" s="14" t="s">
-        <v>672</v>
+        <v>666</v>
+      </c>
+      <c r="B286" s="6" t="s">
+        <v>667</v>
       </c>
       <c r="C286" s="7" t="s">
         <v>581</v>
       </c>
       <c r="D286" s="5" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="E286" s="7" t="s">
         <v>20</v>
@@ -10334,14 +10346,66 @@
         <v>9</v>
       </c>
       <c r="G286" s="18" t="s">
+        <v>719</v>
+      </c>
+      <c r="H286" s="18" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="287" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A287" s="5" t="s">
+        <v>669</v>
+      </c>
+      <c r="B287" s="14" t="s">
+        <v>670</v>
+      </c>
+      <c r="C287" s="7" t="s">
+        <v>581</v>
+      </c>
+      <c r="D287" s="5" t="s">
+        <v>668</v>
+      </c>
+      <c r="E287" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F287" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G287" s="18" t="s">
         <v>718</v>
       </c>
-      <c r="H286" s="18" t="s">
+      <c r="H287" s="18" t="s">
         <v>787</v>
       </c>
     </row>
+    <row r="288" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A288" s="5" t="s">
+        <v>671</v>
+      </c>
+      <c r="B288" s="14" t="s">
+        <v>672</v>
+      </c>
+      <c r="C288" s="7" t="s">
+        <v>581</v>
+      </c>
+      <c r="D288" s="5" t="s">
+        <v>668</v>
+      </c>
+      <c r="E288" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F288" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G288" s="18" t="s">
+        <v>718</v>
+      </c>
+      <c r="H288" s="18" t="s">
+        <v>787</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H286" xr:uid="{446419A3-BB56-46D4-B296-D3867C4128DB}"/>
+  <autoFilter ref="A1:H288" xr:uid="{446419A3-BB56-46D4-B296-D3867C4128DB}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/source-excel/DATAPLANT.xlsx
+++ b/source-excel/DATAPLANT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI\รายงานการจัดระดับ\newstarrating\source-excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBD0646E-F0BF-4F93-BE54-43C7D6F58240}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD3B8537-A72A-4353-9894-1EDFBC1772AB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="8130" xr2:uid="{22141E00-01BD-4411-8006-614C22989334}"/>
   </bookViews>
@@ -6154,7 +6154,7 @@
         <v>311</v>
       </c>
       <c r="E125" s="7" t="s">
-        <v>20</v>
+        <v>300</v>
       </c>
       <c r="F125" s="7" t="s">
         <v>16</v>
